--- a/タナカホーム株式会社御中_LINEOA施策提案【SIM】ver1.2.xlsx
+++ b/タナカホーム株式会社御中_LINEOA施策提案【SIM】ver1.2.xlsx
@@ -13,11 +13,13 @@
     <workbookView xWindow="-13380" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{02433765-3560-48F5-BC99-B30FC64129A4}"/>
   </bookViews>
   <sheets>
-    <sheet name="SIM_離脱防止＋サンクスLINE" sheetId="1" r:id="rId1"/>
-    <sheet name="SIM_比較" sheetId="2" r:id="rId2"/>
-    <sheet name="SIM考え方" sheetId="3" r:id="rId3"/>
+    <sheet name="A_サンクス有" sheetId="1" r:id="rId1"/>
+    <sheet name="A_比較" sheetId="2" r:id="rId2"/>
+    <sheet name="B_サンクス無" sheetId="3" r:id="rId100"/>
+    <sheet name="B_比較" sheetId="4" r:id="rId101"/>
+    <sheet name="SIM考え方" sheetId="5" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2942,8 +2944,10 @@
       </c>
     </row>
     <row r="4" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="56" t="s">
-        <v>161</v>
+      <c r="A4" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">タナカホーム株式会社御中_LINEOA施策提案【SIM】ver1.2　A_サンクス有（離脱防止＋サイトのボタン＋サンクスLINE誘導）</t>
+        </is>
       </c>
       <c r="N4" s="55"/>
       <c r="O4" s="55"/>
@@ -3187,31 +3191,24 @@
       <c r="C14" s="99"/>
       <c r="D14" s="42">
         <f>+H8</f>
-        <v>13228</v>
       </c>
       <c r="E14" s="43">
         <f>+D14</f>
-        <v>13228</v>
       </c>
       <c r="F14" s="43">
         <f t="shared" ref="F14:J14" si="0">+E14</f>
-        <v>13228</v>
       </c>
       <c r="G14" s="43">
         <f t="shared" si="0"/>
-        <v>13228</v>
       </c>
       <c r="H14" s="43">
         <f t="shared" si="0"/>
-        <v>13228</v>
       </c>
       <c r="I14" s="43">
         <f t="shared" si="0"/>
-        <v>13228</v>
       </c>
       <c r="J14" s="43">
         <f t="shared" si="0"/>
-        <v>13228</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="7"/>
@@ -3224,31 +3221,24 @@
       <c r="C15" s="99"/>
       <c r="D15" s="42">
         <f t="shared" ref="D15" si="1">+H9</f>
-        <v>0</v>
       </c>
       <c r="E15" s="43">
         <f t="shared" ref="E15:J16" si="2">+D15</f>
-        <v>0</v>
       </c>
       <c r="F15" s="43">
         <f t="shared" si="2"/>
-        <v>0</v>
       </c>
       <c r="G15" s="43">
         <f t="shared" si="2"/>
-        <v>0</v>
       </c>
       <c r="H15" s="43">
         <f t="shared" si="2"/>
-        <v>0</v>
       </c>
       <c r="I15" s="43">
         <f t="shared" si="2"/>
-        <v>0</v>
       </c>
       <c r="J15" s="43">
         <f t="shared" si="2"/>
-        <v>0</v>
       </c>
       <c r="K15" s="11"/>
       <c r="L15" s="7"/>
@@ -3273,31 +3263,24 @@
       <c r="C16" s="99"/>
       <c r="D16" s="42">
         <f>H10</f>
-        <v>35</v>
       </c>
       <c r="E16" s="43">
         <f t="shared" si="2"/>
-        <v>35</v>
       </c>
       <c r="F16" s="43">
         <f t="shared" si="2"/>
-        <v>35</v>
       </c>
       <c r="G16" s="43">
         <f t="shared" si="2"/>
-        <v>35</v>
       </c>
       <c r="H16" s="43">
         <f t="shared" si="2"/>
-        <v>35</v>
       </c>
       <c r="I16" s="43">
         <f t="shared" si="2"/>
-        <v>35</v>
       </c>
       <c r="J16" s="43">
         <f t="shared" si="2"/>
-        <v>35</v>
       </c>
       <c r="K16" s="11"/>
       <c r="L16" s="7"/>
@@ -3478,7 +3461,6 @@
       </c>
       <c r="Y19" s="34">
         <f>+U19*2.5</f>
-        <v>37500000</v>
       </c>
       <c r="Z19" s="35">
         <v>2.5</v>
@@ -3619,27 +3601,21 @@
       </c>
       <c r="E23" s="46">
         <f>IF(E18=FALSE,0,E15*$P$18*0.08*0.08+(E14-E15)*$P$19*0.12*0.12)</f>
-        <v>104.76576</v>
       </c>
       <c r="F23" s="46">
         <f>IF(F18=FALSE,0,F15*$P$18*0.08*0.08+(F14-F15)*$P$19*0.12*0.12)</f>
-        <v>104.76576</v>
       </c>
       <c r="G23" s="63">
         <f t="shared" ref="G23:J24" si="3">F23*1.01</f>
-        <v>105.81341760000001</v>
       </c>
       <c r="H23" s="63">
         <f t="shared" si="3"/>
-        <v>106.871551776</v>
       </c>
       <c r="I23" s="63">
         <f t="shared" si="3"/>
-        <v>107.94026729376</v>
       </c>
       <c r="J23" s="63">
         <f t="shared" si="3"/>
-        <v>109.01966996669761</v>
       </c>
       <c r="K23" s="11"/>
       <c r="L23" s="7"/>
@@ -3672,27 +3648,21 @@
       </c>
       <c r="E24" s="46">
         <f>+IF(E19=FALSE,0,SUM(H10:H11)*0.15)</f>
-        <v>6.45</v>
       </c>
       <c r="F24" s="63">
         <f>E24*1.01</f>
-        <v>6.5145</v>
       </c>
       <c r="G24" s="63">
         <f t="shared" si="3"/>
-        <v>6.5796450000000002</v>
       </c>
       <c r="H24" s="63">
         <f t="shared" si="3"/>
-        <v>6.6454414499999999</v>
       </c>
       <c r="I24" s="63">
         <f t="shared" si="3"/>
-        <v>6.7118958644999998</v>
       </c>
       <c r="J24" s="63">
         <f t="shared" si="3"/>
-        <v>6.7790148231449994</v>
       </c>
       <c r="K24" s="11"/>
       <c r="L24" s="7"/>
@@ -3725,27 +3695,21 @@
       </c>
       <c r="E25" s="46">
         <f>+IF(E20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
-        <v>0</v>
       </c>
       <c r="F25" s="46">
         <f t="shared" ref="F25:J25" si="4">+IF(F20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
-        <v>0</v>
       </c>
       <c r="G25" s="46">
         <f t="shared" si="4"/>
-        <v>0</v>
       </c>
       <c r="H25" s="46">
         <f t="shared" si="4"/>
-        <v>0</v>
       </c>
       <c r="I25" s="46">
         <f t="shared" si="4"/>
-        <v>0</v>
       </c>
       <c r="J25" s="46">
         <f t="shared" si="4"/>
-        <v>0</v>
       </c>
       <c r="K25" s="11"/>
       <c r="L25" s="7"/>
@@ -3773,27 +3737,21 @@
       </c>
       <c r="E26" s="46">
         <f>+SUM(E22:E25)+$H$9*$P$16+($H$8-$H$9)*$P$15+IF(P9=FALSE,0,$K$8*0.15*0.08)</f>
-        <v>177.35576</v>
       </c>
       <c r="F26" s="46">
         <f t="shared" ref="F26:J26" si="5">+SUM(F22:F25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
-        <v>177.42025999999998</v>
       </c>
       <c r="G26" s="46">
         <f>+SUM(G22:G25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
-        <v>178.53306259999999</v>
       </c>
       <c r="H26" s="46">
         <f t="shared" si="5"/>
-        <v>179.656993226</v>
       </c>
       <c r="I26" s="46">
         <f t="shared" si="5"/>
-        <v>180.79216315826</v>
       </c>
       <c r="J26" s="46">
         <f t="shared" si="5"/>
-        <v>181.93868478984263</v>
       </c>
       <c r="K26" s="11"/>
       <c r="L26" s="7"/>
@@ -3826,23 +3784,18 @@
       </c>
       <c r="F27" s="47">
         <f>ROUND(E27*1.02,3)</f>
-        <v>0.28599999999999998</v>
       </c>
       <c r="G27" s="47">
         <f>ROUND(F27*1.02,3)</f>
-        <v>0.29199999999999998</v>
       </c>
       <c r="H27" s="47">
         <f>ROUND(G27*1.02,3)</f>
-        <v>0.29799999999999999</v>
       </c>
       <c r="I27" s="47">
         <f>ROUND(H27*1.02,3)</f>
-        <v>0.30399999999999999</v>
       </c>
       <c r="J27" s="47">
         <f>ROUND(I27*1.02,3)</f>
-        <v>0.31</v>
       </c>
       <c r="K27" s="11"/>
       <c r="L27" s="7"/>
@@ -3875,27 +3828,21 @@
       </c>
       <c r="E28" s="49">
         <f>+D28+E26</f>
-        <v>594.35576000000003</v>
       </c>
       <c r="F28" s="49">
         <f t="shared" ref="F28:J28" si="6">+E28+F26</f>
-        <v>771.77602000000002</v>
       </c>
       <c r="G28" s="49">
         <f t="shared" si="6"/>
-        <v>950.30908260000001</v>
       </c>
       <c r="H28" s="49">
         <f t="shared" si="6"/>
-        <v>1129.966075826</v>
       </c>
       <c r="I28" s="49">
         <f t="shared" si="6"/>
-        <v>1310.7582389842601</v>
       </c>
       <c r="J28" s="49">
         <f t="shared" si="6"/>
-        <v>1492.6969237741027</v>
       </c>
       <c r="K28" s="12"/>
       <c r="L28" s="7"/>
@@ -3922,31 +3869,24 @@
       <c r="C29" s="102"/>
       <c r="D29" s="108">
         <f>+D28*(1-D27)</f>
-        <v>300.24</v>
       </c>
       <c r="E29" s="50">
         <f>+E28*(1-E27)</f>
-        <v>427.93614719999999</v>
       </c>
       <c r="F29" s="50">
         <f t="shared" ref="F29:J29" si="7">+F28*(1-F27)</f>
-        <v>551.04807828000003</v>
       </c>
       <c r="G29" s="50">
         <f t="shared" si="7"/>
-        <v>672.81883048079999</v>
       </c>
       <c r="H29" s="50">
         <f t="shared" si="7"/>
-        <v>793.23618522985191</v>
       </c>
       <c r="I29" s="50">
         <f t="shared" si="7"/>
-        <v>912.28773433304491</v>
       </c>
       <c r="J29" s="50">
         <f t="shared" si="7"/>
-        <v>1029.9608774041308</v>
       </c>
       <c r="K29" s="12"/>
       <c r="L29" s="7"/>
@@ -4009,31 +3949,24 @@
       <c r="C31" s="23"/>
       <c r="D31" s="108">
         <f>+D30*D29*0.41*0.07</f>
-        <v>0</v>
       </c>
       <c r="E31" s="63">
         <f>+E29*E30*$P$24*$P$22*$P$23*$P$36</f>
-        <v>135.05952378722924</v>
       </c>
       <c r="F31" s="63">
         <f>+F29*F30*$P$24*$P$22*$P$23*$P$36</f>
-        <v>173.91447654825413</v>
       </c>
       <c r="G31" s="63">
         <f>+G29*G30*$P$24*$P$22*$P$23*$P$36</f>
-        <v>212.34614424228138</v>
       </c>
       <c r="H31" s="63">
         <f>+H29*H30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-        <v>200.28053648456489</v>
       </c>
       <c r="I31" s="63">
         <f>+I29*I30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-        <v>230.33931162326704</v>
       </c>
       <c r="J31" s="63">
         <f>+J29*J30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-        <v>260.05005939667194</v>
       </c>
       <c r="K31" s="11"/>
       <c r="L31" s="7"/>
@@ -4083,7 +4016,6 @@
       </c>
       <c r="Q32" s="73">
         <f>+IF(P32=TRUE,1.1,0.95)</f>
-        <v>1.1000000000000001</v>
       </c>
       <c r="S32" s="34"/>
       <c r="U32" s="34"/>
@@ -4101,27 +4033,21 @@
       </c>
       <c r="E33" s="63">
         <f t="shared" ref="E33:J33" si="8">+E26*E32*$P$26*$P$27*$P$36</f>
-        <v>97.552008468420013</v>
       </c>
       <c r="F33" s="63">
         <f t="shared" si="8"/>
-        <v>97.587485774295004</v>
       </c>
       <c r="G33" s="63">
         <f t="shared" si="8"/>
-        <v>98.199566986987961</v>
       </c>
       <c r="H33" s="63">
         <f t="shared" si="8"/>
-        <v>98.81776901180784</v>
       </c>
       <c r="I33" s="63">
         <f t="shared" si="8"/>
-        <v>99.442153056875924</v>
       </c>
       <c r="J33" s="63">
         <f t="shared" si="8"/>
-        <v>100.07278094239471</v>
       </c>
       <c r="K33" s="11"/>
       <c r="L33" s="7"/>
@@ -4133,7 +4059,6 @@
       </c>
       <c r="Q33" s="73">
         <f t="shared" ref="Q33:Q35" si="9">+IF(P33=TRUE,1.1,0.95)</f>
-        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
@@ -4144,31 +4069,24 @@
       <c r="C34" s="102"/>
       <c r="D34" s="108">
         <f>+D29*D30</f>
-        <v>0</v>
       </c>
       <c r="E34" s="46">
         <f>+E29*E30*$P$24+E26*E32</f>
-        <v>2256.1744710399998</v>
       </c>
       <c r="F34" s="46">
         <f>+F29*F30*$P$24+F26*F32</f>
-        <v>2650.455150496</v>
       </c>
       <c r="G34" s="46">
         <f>+G29*G30*$P$24+G26*G32</f>
-        <v>3045.6855705385601</v>
       </c>
       <c r="H34" s="46">
         <f>+H29*H30*$P$24*$Q$24+H26*H32</f>
-        <v>2928.9696003184208</v>
       </c>
       <c r="I34" s="46">
         <f>+I29*I30*$P$24*$Q$24+I26*I32</f>
-        <v>3239.4174156838949</v>
       </c>
       <c r="J34" s="46">
         <f>+J29*J30*$P$24*$Q$24+J26*J32</f>
-        <v>3546.3932701037884</v>
       </c>
       <c r="K34" s="11"/>
       <c r="L34" s="7"/>
@@ -4180,7 +4098,6 @@
       </c>
       <c r="Q34" s="73">
         <f t="shared" si="9"/>
-        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
@@ -4191,31 +4108,24 @@
       <c r="C35" s="102"/>
       <c r="D35" s="109">
         <f>+D31*1.02</f>
-        <v>0</v>
       </c>
       <c r="E35" s="50">
         <f>+E31+E33+1.05*(E31+E33)</f>
-        <v>476.85364112408098</v>
       </c>
       <c r="F35" s="50">
         <f t="shared" ref="F35:J35" si="10">+F31+F33+1.05*(F31+F33)</f>
-        <v>556.57902276122581</v>
       </c>
       <c r="G35" s="50">
         <f t="shared" si="10"/>
-        <v>636.61870802000215</v>
       </c>
       <c r="H35" s="50">
         <f t="shared" si="10"/>
-        <v>613.15152626756412</v>
       </c>
       <c r="I35" s="50">
         <f t="shared" si="10"/>
-        <v>676.05200259429307</v>
       </c>
       <c r="J35" s="50">
         <f t="shared" si="10"/>
-        <v>738.25182269508673</v>
       </c>
       <c r="K35" s="11"/>
       <c r="L35" s="7"/>
@@ -4227,16 +4137,14 @@
       </c>
       <c r="Q35" s="73">
         <f t="shared" si="9"/>
-        <v>0.95</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="150" t="s">
         <v>6</v>
       </c>
-      <c r="B36" s="6" t="str">
+      <c r="B36" s="6">
         <f>+C8</f>
-        <v>資料請求</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="11">
@@ -4262,7 +4170,6 @@
       </c>
       <c r="K36" s="115">
         <f>SUM(E36:J36)</f>
-        <v>44</v>
       </c>
       <c r="L36" s="7"/>
       <c r="N36" s="69" t="s">
@@ -4273,15 +4180,13 @@
       </c>
       <c r="P36" s="74">
         <f>1*(Q32*Q33*Q34*Q35)</f>
-        <v>1.2644500000000003</v>
       </c>
       <c r="Q36" s="73"/>
     </row>
     <row r="37" spans="1:17" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="151"/>
-      <c r="B37" s="6" t="str">
+      <c r="B37" s="6">
         <f>+C9</f>
-        <v>来場予約</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="11">
@@ -4307,7 +4212,6 @@
       </c>
       <c r="K37" s="115">
         <f>SUM(E37:J37)</f>
-        <v>30</v>
       </c>
       <c r="L37" s="7"/>
       <c r="N37" s="69" t="s">
@@ -4318,9 +4222,8 @@
       <c r="A38" s="150" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="6" t="str">
+      <c r="B38" s="6">
         <f>+C10</f>
-        <v>-</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="11">
@@ -4346,7 +4249,6 @@
       </c>
       <c r="K38" s="115">
         <f>SUM(E38:J38)</f>
-        <v>0</v>
       </c>
       <c r="L38" s="7"/>
       <c r="N38" s="69" t="s">
@@ -4358,9 +4260,8 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="151"/>
-      <c r="B39" s="6" t="str">
+      <c r="B39" s="6">
         <f>+C11</f>
-        <v>-</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="11">
@@ -4386,7 +4287,6 @@
       </c>
       <c r="K39" s="115">
         <f>SUM(E39:J39)</f>
-        <v>0</v>
       </c>
       <c r="L39" s="7"/>
       <c r="N39" s="69" t="s">
@@ -4404,35 +4304,27 @@
       <c r="C40" s="97"/>
       <c r="D40" s="11">
         <f>SUM(D36:D39)</f>
-        <v>0</v>
       </c>
       <c r="E40" s="10">
         <f>SUM(E36:E39)</f>
-        <v>6</v>
       </c>
       <c r="F40" s="10">
         <f t="shared" ref="F40:J40" si="11">SUM(F36:F39)</f>
-        <v>9</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="11"/>
-        <v>10</v>
       </c>
       <c r="H40" s="10">
         <f t="shared" si="11"/>
-        <v>14</v>
       </c>
       <c r="I40" s="10">
         <f t="shared" si="11"/>
-        <v>16</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="11"/>
-        <v>19</v>
       </c>
       <c r="K40" s="115">
         <f>SUM(E40:J40)</f>
-        <v>74</v>
       </c>
       <c r="L40" s="7"/>
       <c r="O40" s="17"/>
@@ -4443,31 +4335,24 @@
       </c>
       <c r="D41" s="18">
         <f t="shared" ref="D41" si="12">+IFERROR(D40/D35,0)</f>
-        <v>0</v>
       </c>
       <c r="E41" s="18">
         <f>IFERROR(E40/E35,0)</f>
-        <v>1.2582477059116665E-2</v>
       </c>
       <c r="F41" s="18">
         <f t="shared" ref="F41:J41" si="13">IFERROR(F40/F35,0)</f>
-        <v>1.6170210575580799E-2</v>
       </c>
       <c r="G41" s="18">
         <f t="shared" si="13"/>
-        <v>1.5707989529716752E-2</v>
       </c>
       <c r="H41" s="18">
         <f t="shared" si="13"/>
-        <v>2.2832855175656443E-2</v>
       </c>
       <c r="I41" s="18">
         <f t="shared" si="13"/>
-        <v>2.3666818437932786E-2</v>
       </c>
       <c r="J41" s="18">
         <f t="shared" si="13"/>
-        <v>2.5736475570948089E-2</v>
       </c>
       <c r="N41" s="69" t="s">
         <v>117</v>
@@ -4505,27 +4390,21 @@
       </c>
       <c r="E44" s="31">
         <f>+E75*E76</f>
-        <v>0</v>
       </c>
       <c r="F44" s="31">
         <f t="shared" ref="F44:J44" si="14">+F75*F76</f>
-        <v>0</v>
       </c>
       <c r="G44" s="31">
         <f t="shared" si="14"/>
-        <v>0</v>
       </c>
       <c r="H44" s="31">
         <f t="shared" si="14"/>
-        <v>0</v>
       </c>
       <c r="I44" s="31">
         <f t="shared" si="14"/>
-        <v>0</v>
       </c>
       <c r="J44" s="31">
         <f t="shared" si="14"/>
-        <v>0</v>
       </c>
       <c r="K44" s="11"/>
       <c r="L44" s="7"/>
@@ -4537,35 +4416,27 @@
       <c r="B45" s="145"/>
       <c r="C45" s="104">
         <f>+SUM(C65:C72)</f>
-        <v>0</v>
       </c>
       <c r="D45" s="80">
         <f>+SUM(D65:D72)</f>
-        <v>265000</v>
       </c>
       <c r="E45" s="27">
         <f>SUM(E65:E69)+SUM(E71:E72)</f>
-        <v>265000</v>
       </c>
       <c r="F45" s="27">
         <f t="shared" ref="F45:J45" si="15">SUM(F65:F69)+SUM(F71:F72)</f>
-        <v>265000</v>
       </c>
       <c r="G45" s="27">
         <f t="shared" si="15"/>
-        <v>265000</v>
       </c>
       <c r="H45" s="27">
         <f t="shared" si="15"/>
-        <v>265000</v>
       </c>
       <c r="I45" s="27">
         <f t="shared" si="15"/>
-        <v>265000</v>
       </c>
       <c r="J45" s="27">
         <f t="shared" si="15"/>
-        <v>265000</v>
       </c>
       <c r="K45" s="11"/>
       <c r="L45" s="7"/>
@@ -4581,27 +4452,21 @@
       </c>
       <c r="E46" s="28">
         <f t="shared" ref="E46:J46" si="16">SUM(E65:E67)/(E28-D28)</f>
-        <v>338.30308076828175</v>
       </c>
       <c r="F46" s="28">
         <f t="shared" si="16"/>
-        <v>338.18009284847182</v>
       </c>
       <c r="G46" s="28">
         <f t="shared" si="16"/>
-        <v>336.07220492502773</v>
       </c>
       <c r="H46" s="28">
         <f t="shared" si="16"/>
-        <v>333.96974380241829</v>
       </c>
       <c r="I46" s="28">
         <f t="shared" si="16"/>
-        <v>331.8727922264959</v>
       </c>
       <c r="J46" s="28">
         <f t="shared" si="16"/>
-        <v>329.78143196597239</v>
       </c>
       <c r="K46" s="11"/>
       <c r="L46" s="7"/>
@@ -4617,27 +4482,21 @@
       </c>
       <c r="E47" s="28">
         <f t="shared" ref="E47:I47" si="17">+E51/E35</f>
-        <v>555.72607011098603</v>
       </c>
       <c r="F47" s="28">
         <f t="shared" si="17"/>
-        <v>476.12286694765686</v>
       </c>
       <c r="G47" s="28">
         <f t="shared" si="17"/>
-        <v>416.26172253749394</v>
       </c>
       <c r="H47" s="28">
         <f t="shared" si="17"/>
-        <v>432.19333011063986</v>
       </c>
       <c r="I47" s="28">
         <f t="shared" si="17"/>
-        <v>391.98168037826179</v>
       </c>
       <c r="J47" s="28">
         <f>+J51/J35</f>
-        <v>358.9561066474339</v>
       </c>
       <c r="K47" s="11"/>
       <c r="L47" s="7"/>
@@ -4653,27 +4512,21 @@
       </c>
       <c r="E48" s="32">
         <f>IFERROR(E40/E35,0)</f>
-        <v>1.2582477059116665E-2</v>
       </c>
       <c r="F48" s="32">
         <f t="shared" ref="F48:J48" si="18">IFERROR(F40/F35,0)</f>
-        <v>1.6170210575580799E-2</v>
       </c>
       <c r="G48" s="32">
         <f t="shared" si="18"/>
-        <v>1.5707989529716752E-2</v>
       </c>
       <c r="H48" s="32">
         <f t="shared" si="18"/>
-        <v>2.2832855175656443E-2</v>
       </c>
       <c r="I48" s="32">
         <f t="shared" si="18"/>
-        <v>2.3666818437932786E-2</v>
       </c>
       <c r="J48" s="32">
         <f t="shared" si="18"/>
-        <v>2.5736475570948089E-2</v>
       </c>
       <c r="K48" s="11"/>
       <c r="L48" s="7"/>
@@ -4689,27 +4542,21 @@
       </c>
       <c r="E49" s="28">
         <f>IFERROR(E51/E40,0)</f>
-        <v>44166.666666666664</v>
       </c>
       <c r="F49" s="28">
         <f t="shared" ref="F49:J49" si="19">IFERROR(F51/F40,0)</f>
-        <v>29444.444444444445</v>
       </c>
       <c r="G49" s="28">
         <f t="shared" si="19"/>
-        <v>26500</v>
       </c>
       <c r="H49" s="28">
         <f t="shared" si="19"/>
-        <v>18928.571428571428</v>
       </c>
       <c r="I49" s="28">
         <f t="shared" si="19"/>
-        <v>16562.5</v>
       </c>
       <c r="J49" s="28">
         <f t="shared" si="19"/>
-        <v>13947.368421052632</v>
       </c>
       <c r="K49" s="11"/>
       <c r="L49" s="7"/>
@@ -4725,27 +4572,21 @@
       </c>
       <c r="E50" s="65">
         <f>+E36*$D$8+E38*$D$10</f>
-        <v>0</v>
       </c>
       <c r="F50" s="65">
         <f t="shared" ref="F50:J50" si="20">+F36*$D$8+F38*$D$10</f>
-        <v>0</v>
       </c>
       <c r="G50" s="65">
         <f t="shared" si="20"/>
-        <v>0</v>
       </c>
       <c r="H50" s="65">
         <f t="shared" si="20"/>
-        <v>0</v>
       </c>
       <c r="I50" s="65">
         <f t="shared" si="20"/>
-        <v>0</v>
       </c>
       <c r="J50" s="65">
         <f t="shared" si="20"/>
-        <v>0</v>
       </c>
       <c r="K50" s="11"/>
       <c r="L50" s="7"/>
@@ -4757,35 +4598,27 @@
       <c r="B51" s="155"/>
       <c r="C51" s="110">
         <f>+C45</f>
-        <v>0</v>
       </c>
       <c r="D51" s="40">
         <f>+D45</f>
-        <v>265000</v>
       </c>
       <c r="E51" s="40">
         <f>SUM(E45,E50)+E44</f>
-        <v>265000</v>
       </c>
       <c r="F51" s="40">
         <f t="shared" ref="F51:I51" si="21">SUM(F45,F50)+F44</f>
-        <v>265000</v>
       </c>
       <c r="G51" s="40">
         <f t="shared" si="21"/>
-        <v>265000</v>
       </c>
       <c r="H51" s="40">
         <f t="shared" si="21"/>
-        <v>265000</v>
       </c>
       <c r="I51" s="40">
         <f t="shared" si="21"/>
-        <v>265000</v>
       </c>
       <c r="J51" s="40">
         <f>SUM(J45,J50)+J44</f>
-        <v>265000</v>
       </c>
       <c r="K51" s="11"/>
       <c r="L51" s="7"/>
@@ -4815,31 +4648,24 @@
       <c r="C54" s="96"/>
       <c r="D54" s="28">
         <f>+D75*D76</f>
-        <v>0</v>
       </c>
       <c r="E54" s="28">
         <f t="shared" ref="E54:J54" si="22">+E75*E76</f>
-        <v>0</v>
       </c>
       <c r="F54" s="28">
         <f t="shared" si="22"/>
-        <v>0</v>
       </c>
       <c r="G54" s="28">
         <f t="shared" si="22"/>
-        <v>0</v>
       </c>
       <c r="H54" s="28">
         <f t="shared" si="22"/>
-        <v>0</v>
       </c>
       <c r="I54" s="28">
         <f t="shared" si="22"/>
-        <v>0</v>
       </c>
       <c r="J54" s="28">
         <f t="shared" si="22"/>
-        <v>0</v>
       </c>
       <c r="K54" s="11"/>
       <c r="L54" s="7"/>
@@ -4852,31 +4678,24 @@
       <c r="C55" s="96"/>
       <c r="D55" s="27">
         <f>+SUM(D65:D72)</f>
-        <v>265000</v>
       </c>
       <c r="E55" s="27">
         <f>SUM(E65:E72)+E54</f>
-        <v>265000</v>
       </c>
       <c r="F55" s="27">
         <f t="shared" ref="F55:J55" si="23">SUM(F65:F72)+F54</f>
-        <v>265000</v>
       </c>
       <c r="G55" s="27">
         <f t="shared" si="23"/>
-        <v>265000</v>
       </c>
       <c r="H55" s="27">
         <f t="shared" si="23"/>
-        <v>265000</v>
       </c>
       <c r="I55" s="27">
         <f t="shared" si="23"/>
-        <v>265000</v>
       </c>
       <c r="J55" s="27">
         <f t="shared" si="23"/>
-        <v>265000</v>
       </c>
       <c r="K55" s="11"/>
       <c r="L55" s="7"/>
@@ -4892,27 +4711,21 @@
       </c>
       <c r="E56" s="28">
         <f t="shared" ref="E56:J56" si="24">SUM(E65:E67)/(E28-D28)</f>
-        <v>338.30308076828175</v>
       </c>
       <c r="F56" s="28">
         <f t="shared" si="24"/>
-        <v>338.18009284847182</v>
       </c>
       <c r="G56" s="28">
         <f t="shared" si="24"/>
-        <v>336.07220492502773</v>
       </c>
       <c r="H56" s="28">
         <f t="shared" si="24"/>
-        <v>333.96974380241829</v>
       </c>
       <c r="I56" s="28">
         <f t="shared" si="24"/>
-        <v>331.8727922264959</v>
       </c>
       <c r="J56" s="28">
         <f t="shared" si="24"/>
-        <v>329.78143196597239</v>
       </c>
       <c r="K56" s="11"/>
       <c r="L56" s="7"/>
@@ -4928,27 +4741,21 @@
       </c>
       <c r="E57" s="28">
         <f>+E61/E35</f>
-        <v>555.72607011098603</v>
       </c>
       <c r="F57" s="28">
         <f t="shared" ref="F57:J57" si="25">+F61/F35</f>
-        <v>476.12286694765686</v>
       </c>
       <c r="G57" s="28">
         <f t="shared" si="25"/>
-        <v>416.26172253749394</v>
       </c>
       <c r="H57" s="28">
         <f t="shared" si="25"/>
-        <v>432.19333011063986</v>
       </c>
       <c r="I57" s="28">
         <f t="shared" si="25"/>
-        <v>391.98168037826179</v>
       </c>
       <c r="J57" s="28">
         <f t="shared" si="25"/>
-        <v>358.9561066474339</v>
       </c>
       <c r="K57" s="11"/>
       <c r="L57" s="7"/>
@@ -4964,27 +4771,21 @@
       </c>
       <c r="E58" s="32">
         <f t="shared" ref="E58:J58" si="26">+IFERROR(E36/E35,0)</f>
-        <v>8.3883180394111103E-3</v>
       </c>
       <c r="F58" s="32">
         <f t="shared" si="26"/>
-        <v>1.0780140383720533E-2</v>
       </c>
       <c r="G58" s="32">
         <f t="shared" si="26"/>
-        <v>9.4247937178300514E-3</v>
       </c>
       <c r="H58" s="32">
         <f t="shared" si="26"/>
-        <v>1.3047345814660825E-2</v>
       </c>
       <c r="I58" s="32">
         <f t="shared" si="26"/>
-        <v>1.3312585371337194E-2</v>
       </c>
       <c r="J58" s="32">
         <f t="shared" si="26"/>
-        <v>1.4900064804233105E-2</v>
       </c>
       <c r="K58" s="11"/>
       <c r="L58" s="7"/>
@@ -4998,27 +4799,21 @@
       <c r="D59" s="28"/>
       <c r="E59" s="28">
         <f t="shared" ref="E59:J59" si="27">+IFERROR(E55/E36,0)</f>
-        <v>66250</v>
       </c>
       <c r="F59" s="28">
         <f t="shared" si="27"/>
-        <v>44166.666666666664</v>
       </c>
       <c r="G59" s="28">
         <f t="shared" si="27"/>
-        <v>44166.666666666664</v>
       </c>
       <c r="H59" s="28">
         <f t="shared" si="27"/>
-        <v>33125</v>
       </c>
       <c r="I59" s="28">
         <f t="shared" si="27"/>
-        <v>29444.444444444445</v>
       </c>
       <c r="J59" s="28">
         <f t="shared" si="27"/>
-        <v>24090.909090909092</v>
       </c>
       <c r="K59" s="11"/>
       <c r="L59" s="7"/>
@@ -5047,31 +4842,24 @@
       <c r="C61" s="98"/>
       <c r="D61" s="40">
         <f>+D55</f>
-        <v>265000</v>
       </c>
       <c r="E61" s="40">
         <f>+SUM(E65:E72)+E54</f>
-        <v>265000</v>
       </c>
       <c r="F61" s="40">
         <f t="shared" ref="F61:J61" si="28">+SUM(F65:F72)+F54</f>
-        <v>265000</v>
       </c>
       <c r="G61" s="40">
         <f t="shared" si="28"/>
-        <v>265000</v>
       </c>
       <c r="H61" s="40">
         <f t="shared" si="28"/>
-        <v>265000</v>
       </c>
       <c r="I61" s="40">
         <f t="shared" si="28"/>
-        <v>265000</v>
       </c>
       <c r="J61" s="40">
         <f t="shared" si="28"/>
-        <v>265000</v>
       </c>
       <c r="K61" s="11"/>
       <c r="L61" s="7"/>
@@ -5200,27 +4988,21 @@
       </c>
       <c r="E68" s="28">
         <f t="shared" ref="E68:J68" si="29">IF(E34&lt;5000,5000,15000)</f>
-        <v>5000</v>
       </c>
       <c r="F68" s="28">
         <f t="shared" si="29"/>
-        <v>5000</v>
       </c>
       <c r="G68" s="28">
         <f t="shared" si="29"/>
-        <v>5000</v>
       </c>
       <c r="H68" s="28">
         <f t="shared" si="29"/>
-        <v>5000</v>
       </c>
       <c r="I68" s="28">
         <f t="shared" si="29"/>
-        <v>5000</v>
       </c>
       <c r="J68" s="28">
         <f t="shared" si="29"/>
-        <v>5000</v>
       </c>
       <c r="N68" s="69" t="s">
         <v>186</v>
@@ -5374,31 +5156,24 @@
       </c>
       <c r="D73" s="114">
         <f>SUM(D65:D72)</f>
-        <v>265000</v>
       </c>
       <c r="E73" s="114">
         <f t="shared" ref="E73:J73" si="30">SUM(E65:E72)+E54</f>
-        <v>265000</v>
       </c>
       <c r="F73" s="114">
         <f t="shared" si="30"/>
-        <v>265000</v>
       </c>
       <c r="G73" s="114">
         <f t="shared" si="30"/>
-        <v>265000</v>
       </c>
       <c r="H73" s="114">
         <f t="shared" si="30"/>
-        <v>265000</v>
       </c>
       <c r="I73" s="114">
         <f t="shared" si="30"/>
-        <v>265000</v>
       </c>
       <c r="J73" s="114">
         <f t="shared" si="30"/>
-        <v>265000</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -5419,31 +5194,24 @@
       </c>
       <c r="D75" s="41">
         <f t="shared" ref="D75:J75" si="31">+IF(D34&lt;30001,0,D34-30000)</f>
-        <v>0</v>
       </c>
       <c r="E75" s="41">
         <f t="shared" si="31"/>
-        <v>0</v>
       </c>
       <c r="F75" s="41">
         <f t="shared" si="31"/>
-        <v>0</v>
       </c>
       <c r="G75" s="41">
         <f t="shared" si="31"/>
-        <v>0</v>
       </c>
       <c r="H75" s="41">
         <f t="shared" si="31"/>
-        <v>0</v>
       </c>
       <c r="I75" s="41">
         <f t="shared" si="31"/>
-        <v>0</v>
       </c>
       <c r="J75" s="41">
         <f t="shared" si="31"/>
-        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -5452,31 +5220,24 @@
       </c>
       <c r="D76" s="5">
         <f t="shared" ref="D76:J76" si="32">+IF(D75&lt;=$U$18,$Z$18,IF(D75&lt;=$U$19,$Z$19,IF(D75&lt;=$U$20,$Z$20,IF(D75&lt;=$U$21,$Z$21,IF(D75&lt;=$U$22,$Z$22,IF(D75&lt;=$U$23,$Z$23,IF(D75&lt;=$U$24,$Z$24,IF(D75&lt;=$U$25,$Z$25,IF(D75&lt;=$U$26,$Z$26,IF(D75&lt;=$U$27,$Z$27,IF(D75&lt;=$U$28,$Z$28,IF(D75&lt;=$U$29,$Z$29,IF(D75&lt;=$U$30,$Z$30,0)))))))))))))</f>
-        <v>3</v>
       </c>
       <c r="E76" s="5">
         <f t="shared" si="32"/>
-        <v>3</v>
       </c>
       <c r="F76" s="5">
         <f t="shared" si="32"/>
-        <v>3</v>
       </c>
       <c r="G76" s="5">
         <f t="shared" si="32"/>
-        <v>3</v>
       </c>
       <c r="H76" s="5">
         <f t="shared" si="32"/>
-        <v>3</v>
       </c>
       <c r="I76" s="5">
         <f t="shared" si="32"/>
-        <v>3</v>
       </c>
       <c r="J76" s="5">
         <f t="shared" si="32"/>
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5566,17 +5327,14 @@
         <v>137</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="86" t="str">
-        <f>+'SIM_離脱防止＋サンクスLINE'!D24</f>
-        <v>--</v>
+      <c r="C4" s="86">
+        <f>+'A_サンクス有'!D24</f>
       </c>
       <c r="D4" s="28">
-        <f>+'SIM_離脱防止＋サンクスLINE'!G51</f>
-        <v>265000</v>
+        <f>+'A_サンクス有'!G51</f>
       </c>
       <c r="E4" s="28">
-        <f>+'SIM_離脱防止＋サンクスLINE'!J51</f>
-        <v>265000</v>
+        <f>+'A_サンクス有'!J51</f>
       </c>
       <c r="F4" s="28"/>
     </row>
@@ -5585,17 +5343,14 @@
         <v>138</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="86" t="str">
-        <f>+'SIM_離脱防止＋サンクスLINE'!D25</f>
-        <v>--</v>
+      <c r="C5" s="86">
+        <f>+'A_サンクス有'!D25</f>
       </c>
       <c r="D5" s="28">
-        <f>+'SIM_離脱防止＋サンクスLINE'!G61</f>
-        <v>265000</v>
+        <f>+'A_サンクス有'!G61</f>
       </c>
       <c r="E5" s="28">
-        <f>+'SIM_離脱防止＋サンクスLINE'!J61</f>
-        <v>265000</v>
+        <f>+'A_サンクス有'!J61</f>
       </c>
       <c r="F5" s="27"/>
     </row>
@@ -5605,16 +5360,13 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="117">
-        <f>+'SIM_離脱防止＋サンクスLINE'!D28</f>
-        <v>417</v>
+        <f>+'A_サンクス有'!D28</f>
       </c>
       <c r="D6" s="87">
-        <f>+'SIM_離脱防止＋サンクスLINE'!G28</f>
-        <v>950.30908260000001</v>
+        <f>+'A_サンクス有'!G28</f>
       </c>
       <c r="E6" s="87">
-        <f>+'SIM_離脱防止＋サンクスLINE'!J28</f>
-        <v>1492.6969237741027</v>
+        <f>+'A_サンクス有'!J28</f>
       </c>
       <c r="F6" s="10"/>
     </row>
@@ -5624,16 +5376,13 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="88">
-        <f>+'SIM_離脱防止＋サンクスLINE'!D27</f>
-        <v>0.28000000000000003</v>
+        <f>+'A_サンクス有'!D27</f>
       </c>
       <c r="D7" s="89">
-        <f>+'SIM_離脱防止＋サンクスLINE'!G27</f>
-        <v>0.29199999999999998</v>
+        <f>+'A_サンクス有'!G27</f>
       </c>
       <c r="E7" s="89">
-        <f>+'SIM_離脱防止＋サンクスLINE'!J27</f>
-        <v>0.31</v>
+        <f>+'A_サンクス有'!J27</f>
       </c>
       <c r="F7" s="89"/>
     </row>
@@ -5643,16 +5392,13 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="117">
-        <f>+'SIM_離脱防止＋サンクスLINE'!D29</f>
-        <v>300.24</v>
+        <f>+'A_サンクス有'!D29</f>
       </c>
       <c r="D8" s="10">
-        <f>+'SIM_離脱防止＋サンクスLINE'!G29</f>
-        <v>672.81883048079999</v>
+        <f>+'A_サンクス有'!G29</f>
       </c>
       <c r="E8" s="10">
-        <f>+'SIM_離脱防止＋サンクスLINE'!J29</f>
-        <v>1029.9608774041308</v>
+        <f>+'A_サンクス有'!J29</f>
       </c>
       <c r="F8" s="10"/>
     </row>
@@ -5670,16 +5416,13 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="117">
-        <f>+'SIM_離脱防止＋サンクスLINE'!D34</f>
-        <v>0</v>
+        <f>+'A_サンクス有'!D34</f>
       </c>
       <c r="D10" s="10">
-        <f>+'SIM_離脱防止＋サンクスLINE'!G34</f>
-        <v>3045.6855705385601</v>
+        <f>+'A_サンクス有'!G34</f>
       </c>
       <c r="E10" s="10">
-        <f>+'SIM_離脱防止＋サンクスLINE'!J34</f>
-        <v>3546.3932701037884</v>
+        <f>+'A_サンクス有'!J34</f>
       </c>
       <c r="F10" s="10"/>
     </row>
@@ -5689,16 +5432,13 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="117">
-        <f>+'SIM_離脱防止＋サンクスLINE'!D35</f>
-        <v>0</v>
+        <f>+'A_サンクス有'!D35</f>
       </c>
       <c r="D11" s="10">
-        <f>+'SIM_離脱防止＋サンクスLINE'!G35</f>
-        <v>636.61870802000215</v>
+        <f>+'A_サンクス有'!G35</f>
       </c>
       <c r="E11" s="10">
-        <f>+'SIM_離脱防止＋サンクスLINE'!J35</f>
-        <v>738.25182269508673</v>
+        <f>+'A_サンクス有'!J35</f>
       </c>
       <c r="F11" s="10"/>
     </row>
@@ -5709,15 +5449,12 @@
       <c r="B12" s="7"/>
       <c r="C12" s="28">
         <f>+IFERROR(C5/C11,0)</f>
-        <v>0</v>
       </c>
       <c r="D12" s="28">
         <f>+D4/D11</f>
-        <v>416.26172253749394</v>
       </c>
       <c r="E12" s="28">
         <f t="shared" ref="E12" si="0">+E4/E11</f>
-        <v>358.9561066474339</v>
       </c>
       <c r="F12" s="28"/>
     </row>
@@ -5728,15 +5465,12 @@
       <c r="B13" s="7"/>
       <c r="C13" s="28">
         <f>+IFERROR(C6/C12,0)</f>
-        <v>0</v>
       </c>
       <c r="D13" s="28">
         <f>+D5/D11</f>
-        <v>416.26172253749394</v>
       </c>
       <c r="E13" s="28">
         <f t="shared" ref="E13" si="1">+E5/E11</f>
-        <v>358.9561066474339</v>
       </c>
       <c r="F13" s="28"/>
     </row>
@@ -5757,16 +5491,13 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="87">
-        <f>+'SIM_離脱防止＋サンクスLINE'!D16</f>
-        <v>35</v>
+        <f>+'A_サンクス有'!D16</f>
       </c>
       <c r="D15" s="87">
-        <f>+'SIM_離脱防止＋サンクスLINE'!G16</f>
-        <v>35</v>
+        <f>+'A_サンクス有'!G16</f>
       </c>
       <c r="E15" s="87">
-        <f>+'SIM_離脱防止＋サンクスLINE'!J16</f>
-        <v>35</v>
+        <f>+'A_サンクス有'!J16</f>
       </c>
       <c r="F15" s="87"/>
       <c r="R15" s="5" t="s">
@@ -5780,15 +5511,12 @@
       <c r="B16" s="7"/>
       <c r="C16" s="87">
         <f>+C17</f>
-        <v>0</v>
       </c>
       <c r="D16" s="87">
         <f>+D17</f>
-        <v>6</v>
       </c>
       <c r="E16" s="87">
         <f>+E17</f>
-        <v>11</v>
       </c>
       <c r="F16" s="87"/>
       <c r="R16" s="5" t="s">
@@ -5807,16 +5535,13 @@
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="87">
-        <f>+'SIM_離脱防止＋サンクスLINE'!D36</f>
-        <v>0</v>
+        <f>+'A_サンクス有'!D36</f>
       </c>
       <c r="D17" s="87">
-        <f>+'SIM_離脱防止＋サンクスLINE'!G36</f>
-        <v>6</v>
+        <f>+'A_サンクス有'!G36</f>
       </c>
       <c r="E17" s="87">
-        <f>+'SIM_離脱防止＋サンクスLINE'!J36</f>
-        <v>11</v>
+        <f>+'A_サンクス有'!J36</f>
       </c>
       <c r="F17" s="10"/>
       <c r="R17" s="5">
@@ -5847,16 +5572,13 @@
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="87">
-        <f>+'SIM_離脱防止＋サンクスLINE'!D37</f>
-        <v>0</v>
+        <f>+'A_サンクス有'!D37</f>
       </c>
       <c r="D18" s="87">
-        <f>+'SIM_離脱防止＋サンクスLINE'!G37</f>
-        <v>4</v>
+        <f>+'A_サンクス有'!G37</f>
       </c>
       <c r="E18" s="87">
-        <f>+'SIM_離脱防止＋サンクスLINE'!J37</f>
-        <v>8</v>
+        <f>+'A_サンクス有'!J37</f>
       </c>
       <c r="F18" s="10"/>
       <c r="R18" s="34">
@@ -5876,7 +5598,6 @@
       </c>
       <c r="X18" s="34">
         <f>+T18*2.5</f>
-        <v>37500000</v>
       </c>
       <c r="Y18" s="35">
         <v>2.5</v>
@@ -5888,16 +5609,13 @@
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="87">
-        <f>+'SIM_離脱防止＋サンクスLINE'!D38</f>
-        <v>0</v>
+        <f>+'A_サンクス有'!D38</f>
       </c>
       <c r="D19" s="87">
-        <f>+'SIM_離脱防止＋サンクスLINE'!G38</f>
-        <v>0</v>
+        <f>+'A_サンクス有'!G38</f>
       </c>
       <c r="E19" s="87">
-        <f>+'SIM_離脱防止＋サンクスLINE'!J38</f>
-        <v>0</v>
+        <f>+'A_サンクス有'!J38</f>
       </c>
       <c r="F19" s="10"/>
       <c r="R19" s="34"/>
@@ -5912,16 +5630,13 @@
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="87">
-        <f>+'SIM_離脱防止＋サンクスLINE'!D39</f>
-        <v>0</v>
+        <f>+'A_サンクス有'!D39</f>
       </c>
       <c r="D20" s="87">
-        <f>+'SIM_離脱防止＋サンクスLINE'!G39</f>
-        <v>0</v>
+        <f>+'A_サンクス有'!G39</f>
       </c>
       <c r="E20" s="87">
-        <f>+'SIM_離脱防止＋サンクスLINE'!J39</f>
-        <v>0</v>
+        <f>+'A_サンクス有'!J39</f>
       </c>
       <c r="F20" s="10"/>
       <c r="R20" s="34"/>
@@ -5948,17 +5663,14 @@
         <v>139</v>
       </c>
       <c r="B22" s="7"/>
-      <c r="C22" s="90" t="str">
+      <c r="C22" s="90">
         <f>+IFERROR(C4/C16,"--")</f>
-        <v>--</v>
       </c>
       <c r="D22" s="90">
         <f t="shared" ref="D22:E22" si="2">+IFERROR(D4/D16,"--")</f>
-        <v>44166.666666666664</v>
       </c>
       <c r="E22" s="90">
         <f t="shared" si="2"/>
-        <v>24090.909090909092</v>
       </c>
       <c r="F22" s="90"/>
       <c r="R22" s="34"/>
@@ -5972,17 +5684,14 @@
         <v>140</v>
       </c>
       <c r="B23" s="7"/>
-      <c r="C23" s="90" t="str">
+      <c r="C23" s="90">
         <f>+IFERROR(C5/C16,"--")</f>
-        <v>--</v>
       </c>
       <c r="D23" s="90">
         <f t="shared" ref="D23" si="3">+IFERROR(D5/D16,"--")</f>
-        <v>44166.666666666664</v>
       </c>
       <c r="E23" s="90">
         <f t="shared" ref="E23" si="4">+IFERROR(E5/E16,"--")</f>
-        <v>24090.909090909092</v>
       </c>
       <c r="F23" s="90"/>
       <c r="R23" s="34"/>
@@ -6010,16 +5719,13 @@
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="10">
-        <f>+'SIM_離脱防止＋サンクスLINE'!E68+C29*C30</f>
-        <v>5000</v>
+        <f>+'A_サンクス有'!E68+C29*C30</f>
       </c>
       <c r="D25" s="10">
-        <f>+'SIM_離脱防止＋サンクスLINE'!G68+D29*D30</f>
-        <v>5000</v>
+        <f>+'A_サンクス有'!G68+D29*D30</f>
       </c>
       <c r="E25" s="10">
-        <f>+'SIM_離脱防止＋サンクスLINE'!J68+E29*E30</f>
-        <v>5000</v>
+        <f>+'A_サンクス有'!J68+E29*E30</f>
       </c>
       <c r="F25" s="10"/>
       <c r="R25" s="34"/>
@@ -6055,15 +5761,12 @@
       </c>
       <c r="C29" s="5">
         <f>+IF(C10&lt;=30000,0,C10-30000)</f>
-        <v>0</v>
       </c>
       <c r="D29" s="91">
         <f>+IF(D10&lt;=30000,0,D10-30000)</f>
-        <v>0</v>
       </c>
       <c r="E29" s="91">
         <f>+IF(E10&lt;=30000,0,E10-30000)</f>
-        <v>0</v>
       </c>
       <c r="F29" s="91"/>
       <c r="R29" s="34"/>
@@ -6078,15 +5781,12 @@
       </c>
       <c r="C30" s="5">
         <f>+IF(C29&lt;=$T$17,$Y$17,IF(C29&lt;=$T$18,$Y$18,IF(C29&lt;=$T$19,$Y$19,IF(C29&lt;=$T$20,$Y$20,IF(C29&lt;=$T$21,$Y$21,IF(C29&lt;=$T$22,$Y$22,IF(C29&lt;=$T$23,$Y$23,IF(C29&lt;=$T$24,$Y$24,IF(C29&lt;=$T$25,$Y$25,IF(C29&lt;=$T$26,$Y$26,IF(C29&lt;=$T$27,$Y$27,IF(C29&lt;=$T$28,$Y$28,IF(C29&lt;=$T$29,$Y$29,0)))))))))))))</f>
-        <v>3</v>
       </c>
       <c r="D30" s="5">
         <f>+IF(D29&lt;=$T$17,$Y$17,IF(D29&lt;=$T$18,$Y$18,IF(D29&lt;=$T$19,$Y$19,IF(D29&lt;=$T$20,$Y$20,IF(D29&lt;=$T$21,$Y$21,IF(D29&lt;=$T$22,$Y$22,IF(D29&lt;=$T$23,$Y$23,IF(D29&lt;=$T$24,$Y$24,IF(D29&lt;=$T$25,$Y$25,IF(D29&lt;=$T$26,$Y$26,IF(D29&lt;=$T$27,$Y$27,IF(D29&lt;=$T$28,$Y$28,IF(D29&lt;=$T$29,$Y$29,0)))))))))))))</f>
-        <v>3</v>
       </c>
       <c r="E30" s="5">
         <f>+IF(E29&lt;=$T$17,$Y$17,IF(E29&lt;=$T$18,$Y$18,IF(E29&lt;=$T$19,$Y$19,IF(E29&lt;=$T$20,$Y$20,IF(E29&lt;=$T$21,$Y$21,IF(E29&lt;=$T$22,$Y$22,IF(E29&lt;=$T$23,$Y$23,IF(E29&lt;=$T$24,$Y$24,IF(E29&lt;=$T$25,$Y$25,IF(E29&lt;=$T$26,$Y$26,IF(E29&lt;=$T$27,$Y$27,IF(E29&lt;=$T$28,$Y$28,IF(E29&lt;=$T$29,$Y$29,0)))))))))))))</f>
-        <v>3</v>
       </c>
       <c r="R30" s="34"/>
       <c r="T30" s="34"/>
@@ -6179,7 +5879,6 @@
     <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="E7">
         <f>+E4*B5*B6</f>
-        <v>6.8</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6217,7 +5916,6 @@
     <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="E12">
         <f>+E9*B10*B11</f>
-        <v>0.4</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -6261,7 +5959,6 @@
     <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="E17">
         <f>+E14*B15*B16</f>
-        <v>315</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -6305,7 +6002,6 @@
     <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="E22">
         <f>+E19*B20*B21</f>
-        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -6510,6 +6206,2923 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="F42" s="61"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA45D6B4-55E6-58DE-A1CF-69AB6EDE5A4B}">
+  <dimension ref="A2:Z76"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.5" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="29.25" style="5" customWidth="1"/>
+    <col min="3" max="12" width="20" style="5" customWidth="1"/>
+    <col min="13" max="13" width="2.58203125" style="5" customWidth="1"/>
+    <col min="14" max="14" width="44.5" style="69" customWidth="1"/>
+    <col min="15" max="17" width="24.08203125" style="5" customWidth="1"/>
+    <col min="18" max="18" width="2.83203125" style="5" customWidth="1"/>
+    <col min="19" max="19" width="12.08203125" style="5" customWidth="1"/>
+    <col min="20" max="20" width="2.58203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.08203125" style="5" customWidth="1"/>
+    <col min="22" max="22" width="2.83203125" style="5" customWidth="1"/>
+    <col min="23" max="23" width="12.08203125" style="5" customWidth="1"/>
+    <col min="24" max="24" width="2.58203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.08203125" style="5" customWidth="1"/>
+    <col min="26" max="16384" width="9" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="133" t="s">
+        <v>160</v>
+      </c>
+      <c r="B2" s="134">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">タナカホーム株式会社御中_LINEOA施策提案【SIM】ver1.2　B_サンクス無（離脱防止＋サイトのボタン）</t>
+        </is>
+      </c>
+      <c r="N4" s="55"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="55"/>
+      <c r="Q4" s="55"/>
+      <c r="R4" s="55"/>
+      <c r="S4" s="55"/>
+      <c r="T4" s="55"/>
+      <c r="U4" s="55"/>
+      <c r="V4" s="55"/>
+      <c r="W4" s="55"/>
+      <c r="X4" s="55"/>
+      <c r="Y4" s="55"/>
+    </row>
+    <row r="5" spans="1:25" s="2" customFormat="1" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="N5" s="55" t="s">
+        <v>156</v>
+      </c>
+      <c r="O5" s="55"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="55"/>
+      <c r="S5" s="55"/>
+      <c r="T5" s="55"/>
+      <c r="U5" s="55"/>
+      <c r="V5" s="55"/>
+      <c r="W5" s="55"/>
+      <c r="X5" s="55"/>
+      <c r="Y5" s="55"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="N6" s="55"/>
+      <c r="O6" s="55"/>
+      <c r="P6" s="55"/>
+      <c r="Q6" s="55"/>
+      <c r="R6" s="55"/>
+      <c r="S6" s="55"/>
+      <c r="T6" s="55"/>
+      <c r="U6" s="55"/>
+      <c r="V6" s="55"/>
+      <c r="W6" s="55"/>
+      <c r="X6" s="55"/>
+      <c r="Y6" s="55"/>
+    </row>
+    <row r="7" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A7" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A8" s="137" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="D8" s="33">
+        <v>0</v>
+      </c>
+      <c r="G8" s="121" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="122">
+        <v>13228</v>
+      </c>
+      <c r="I8" s="123"/>
+      <c r="J8" s="123" t="s">
+        <v>71</v>
+      </c>
+      <c r="K8" s="129">
+        <v>0</v>
+      </c>
+      <c r="N8" s="69" t="s">
+        <v>162</v>
+      </c>
+      <c r="O8" s="35" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A9" s="138"/>
+      <c r="B9" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>193</v>
+      </c>
+      <c r="D9" s="33">
+        <v>0</v>
+      </c>
+      <c r="G9" s="124" t="s">
+        <v>147</v>
+      </c>
+      <c r="H9" s="125">
+        <v>0</v>
+      </c>
+      <c r="I9" s="22"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="118"/>
+      <c r="N9" s="132" t="s">
+        <v>163</v>
+      </c>
+      <c r="O9" s="130" t="s">
+        <v>154</v>
+      </c>
+      <c r="P9" s="131" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="137" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="33">
+        <v>0</v>
+      </c>
+      <c r="G10" s="124" t="s">
+        <v>164</v>
+      </c>
+      <c r="H10" s="125">
+        <v>35</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="J10" s="29"/>
+      <c r="K10" s="118"/>
+      <c r="N10" s="132" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A11" s="138"/>
+      <c r="B11" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="33">
+        <v>0</v>
+      </c>
+      <c r="G11" s="126" t="s">
+        <v>166</v>
+      </c>
+      <c r="H11" s="127">
+        <v>8</v>
+      </c>
+      <c r="I11" s="128" t="s">
+        <v>152</v>
+      </c>
+      <c r="J11" s="119"/>
+      <c r="K11" s="120"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="O12" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="P12" s="55"/>
+      <c r="Q12" s="55"/>
+      <c r="S12" s="55"/>
+      <c r="T12" s="55"/>
+      <c r="U12" s="55"/>
+      <c r="V12" s="55"/>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="139" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="139"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="36" t="s">
+        <v>167</v>
+      </c>
+      <c r="F13" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="G13" s="36" t="s">
+        <v>169</v>
+      </c>
+      <c r="H13" s="36" t="s">
+        <v>170</v>
+      </c>
+      <c r="I13" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="J13" s="36" t="s">
+        <v>172</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="N13" s="71" t="s">
+        <v>122</v>
+      </c>
+      <c r="O13" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="S13" s="23"/>
+      <c r="T13" s="23"/>
+      <c r="U13" s="23"/>
+      <c r="V13" s="23"/>
+    </row>
+    <row r="14" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="99"/>
+      <c r="D14" s="42">
+        <f>+H8</f>
+      </c>
+      <c r="E14" s="43">
+        <f>+D14</f>
+      </c>
+      <c r="F14" s="43">
+        <f t="shared" ref="F14:J14" si="0">+E14</f>
+      </c>
+      <c r="G14" s="43">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="H14" s="43">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="I14" s="43">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="J14" s="43">
+        <f t="shared" si="0"/>
+      </c>
+      <c r="K14" s="11"/>
+      <c r="L14" s="7"/>
+    </row>
+    <row r="15" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="141"/>
+      <c r="B15" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="99"/>
+      <c r="D15" s="42">
+        <f t="shared" ref="D15" si="1">+H9</f>
+      </c>
+      <c r="E15" s="43">
+        <f t="shared" ref="E15:J16" si="2">+D15</f>
+      </c>
+      <c r="F15" s="43">
+        <f t="shared" si="2"/>
+      </c>
+      <c r="G15" s="43">
+        <f t="shared" si="2"/>
+      </c>
+      <c r="H15" s="43">
+        <f t="shared" si="2"/>
+      </c>
+      <c r="I15" s="43">
+        <f t="shared" si="2"/>
+      </c>
+      <c r="J15" s="43">
+        <f t="shared" si="2"/>
+      </c>
+      <c r="K15" s="11"/>
+      <c r="L15" s="7"/>
+      <c r="N15" s="69" t="s">
+        <v>159</v>
+      </c>
+      <c r="O15" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="P15" s="79">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="S15" s="29" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="142"/>
+      <c r="B16" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C16" s="99"/>
+      <c r="D16" s="42">
+        <f>H10</f>
+      </c>
+      <c r="E16" s="43">
+        <f t="shared" si="2"/>
+      </c>
+      <c r="F16" s="43">
+        <f t="shared" si="2"/>
+      </c>
+      <c r="G16" s="43">
+        <f t="shared" si="2"/>
+      </c>
+      <c r="H16" s="43">
+        <f t="shared" si="2"/>
+      </c>
+      <c r="I16" s="43">
+        <f t="shared" si="2"/>
+      </c>
+      <c r="J16" s="43">
+        <f t="shared" si="2"/>
+      </c>
+      <c r="K16" s="11"/>
+      <c r="L16" s="7"/>
+      <c r="N16" s="69" t="s">
+        <v>158</v>
+      </c>
+      <c r="O16" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="P16" s="79">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="S16" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="140" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="100"/>
+      <c r="D17" s="58" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="F17" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="S17" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="W17" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z17" s="35" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="141"/>
+      <c r="B18" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="100"/>
+      <c r="D18" s="58" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="57" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="57" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="57" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="57" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" s="57" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="N18" s="69" t="s">
+        <v>157</v>
+      </c>
+      <c r="O18" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="P18" s="78">
+        <v>0.65</v>
+      </c>
+      <c r="S18" s="5">
+        <v>0</v>
+      </c>
+      <c r="T18" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="U18" s="34">
+        <v>200000</v>
+      </c>
+      <c r="W18" s="5">
+        <v>0</v>
+      </c>
+      <c r="X18" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y18" s="34">
+        <v>600000</v>
+      </c>
+      <c r="Z18" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="141"/>
+      <c r="B19" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" s="100"/>
+      <c r="D19" s="58" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" s="14"/>
+      <c r="L19" s="9"/>
+      <c r="N19" s="69" t="s">
+        <v>157</v>
+      </c>
+      <c r="O19" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="P19" s="78">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="S19" s="34">
+        <v>200000</v>
+      </c>
+      <c r="T19" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="U19" s="34">
+        <v>15000000</v>
+      </c>
+      <c r="W19" s="34">
+        <v>600000</v>
+      </c>
+      <c r="X19" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y19" s="34">
+        <f>+U19*2.5</f>
+      </c>
+      <c r="Z19" s="35">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="141"/>
+      <c r="B20" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="100"/>
+      <c r="D20" s="58" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" s="14"/>
+      <c r="L20" s="9"/>
+      <c r="S20" s="34"/>
+      <c r="U20" s="34"/>
+      <c r="W20" s="34"/>
+      <c r="Y20" s="34"/>
+      <c r="Z20" s="35"/>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="142"/>
+      <c r="B21" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" s="100"/>
+      <c r="D21" s="58" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="O21" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="P21" s="26"/>
+      <c r="S21" s="34"/>
+      <c r="U21" s="34"/>
+      <c r="W21" s="34"/>
+      <c r="Y21" s="34"/>
+      <c r="Z21" s="35"/>
+    </row>
+    <row r="22" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="143" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="63">
+        <v>0</v>
+      </c>
+      <c r="F22" s="63">
+        <v>0</v>
+      </c>
+      <c r="G22" s="63">
+        <v>0</v>
+      </c>
+      <c r="H22" s="63">
+        <v>0</v>
+      </c>
+      <c r="I22" s="63">
+        <v>0</v>
+      </c>
+      <c r="J22" s="63">
+        <v>0</v>
+      </c>
+      <c r="K22" s="11"/>
+      <c r="L22" s="7"/>
+      <c r="N22" s="69" t="s">
+        <v>173</v>
+      </c>
+      <c r="O22" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="P22" s="24">
+        <v>0.78</v>
+      </c>
+      <c r="S22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="Y22" s="34"/>
+      <c r="Z22" s="35"/>
+    </row>
+    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="141"/>
+      <c r="B23" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="17"/>
+      <c r="D23" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="46">
+        <f>IF(E18=FALSE,0,E15*$P$18*0.08*0.08+(E14-E15)*$P$19*0.12*0.12)</f>
+      </c>
+      <c r="F23" s="46">
+        <f>IF(F18=FALSE,0,F15*$P$18*0.08*0.08+(F14-F15)*$P$19*0.12*0.12)</f>
+      </c>
+      <c r="G23" s="63">
+        <f t="shared" ref="G23:J24" si="3">F23*1.01</f>
+      </c>
+      <c r="H23" s="63">
+        <f t="shared" si="3"/>
+      </c>
+      <c r="I23" s="63">
+        <f t="shared" si="3"/>
+      </c>
+      <c r="J23" s="63">
+        <f t="shared" si="3"/>
+      </c>
+      <c r="K23" s="11"/>
+      <c r="L23" s="7"/>
+      <c r="N23" s="69" t="s">
+        <v>174</v>
+      </c>
+      <c r="O23" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="P23" s="24">
+        <v>0.1</v>
+      </c>
+      <c r="Q23" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="S23" s="34"/>
+      <c r="U23" s="34"/>
+      <c r="W23" s="34"/>
+      <c r="Y23" s="34"/>
+      <c r="Z23" s="35"/>
+    </row>
+    <row r="24" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="141"/>
+      <c r="B24" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="17"/>
+      <c r="D24" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="46">
+        <f>+IF(E19=FALSE,0,SUM(H10:H11)*0.15)</f>
+      </c>
+      <c r="F24" s="63">
+        <f>E24*1.01</f>
+      </c>
+      <c r="G24" s="63">
+        <f t="shared" si="3"/>
+      </c>
+      <c r="H24" s="63">
+        <f t="shared" si="3"/>
+      </c>
+      <c r="I24" s="63">
+        <f t="shared" si="3"/>
+      </c>
+      <c r="J24" s="63">
+        <f t="shared" si="3"/>
+      </c>
+      <c r="K24" s="11"/>
+      <c r="L24" s="7"/>
+      <c r="N24" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B_サンクス無：サンクスLINE誘導は入れない（オプション。Aのシートを参照）</t>
+        </is>
+      </c>
+      <c r="O24" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="P24" s="77">
+        <v>0.8</v>
+      </c>
+      <c r="Q24" s="70">
+        <v>0.8</v>
+      </c>
+      <c r="S24" s="34"/>
+      <c r="U24" s="34"/>
+      <c r="W24" s="34"/>
+      <c r="Y24" s="34"/>
+      <c r="Z24" s="35"/>
+    </row>
+    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="142"/>
+      <c r="B25" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="46">
+        <f>+IF(E20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
+      </c>
+      <c r="F25" s="46">
+        <f t="shared" ref="F25:J25" si="4">+IF(F20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
+      </c>
+      <c r="G25" s="46">
+        <f t="shared" si="4"/>
+      </c>
+      <c r="H25" s="46">
+        <f t="shared" si="4"/>
+      </c>
+      <c r="I25" s="46">
+        <f t="shared" si="4"/>
+      </c>
+      <c r="J25" s="46">
+        <f t="shared" si="4"/>
+      </c>
+      <c r="K25" s="11"/>
+      <c r="L25" s="7"/>
+      <c r="N25" s="69" t="s">
+        <v>121</v>
+      </c>
+      <c r="O25" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P25" s="26"/>
+      <c r="S25" s="34"/>
+      <c r="U25" s="34"/>
+      <c r="W25" s="34"/>
+      <c r="Y25" s="34"/>
+      <c r="Z25" s="35"/>
+    </row>
+    <row r="26" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="144" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="145"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="46">
+        <f>+SUM(E22:E25)+$H$9*$P$16+($H$8-$H$9)*$P$15+IF(P9=FALSE,0,$K$8*0.15*0.08)</f>
+      </c>
+      <c r="F26" s="46">
+        <f t="shared" ref="F26:J26" si="5">+SUM(F22:F25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
+      </c>
+      <c r="G26" s="46">
+        <f>+SUM(G22:G25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
+      </c>
+      <c r="H26" s="46">
+        <f t="shared" si="5"/>
+      </c>
+      <c r="I26" s="46">
+        <f t="shared" si="5"/>
+      </c>
+      <c r="J26" s="46">
+        <f t="shared" si="5"/>
+      </c>
+      <c r="K26" s="11"/>
+      <c r="L26" s="7"/>
+      <c r="N26" s="72" t="s">
+        <v>176</v>
+      </c>
+      <c r="O26" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="P26" s="24">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="S26" s="34"/>
+      <c r="U26" s="34"/>
+      <c r="W26" s="34"/>
+      <c r="Y26" s="34"/>
+      <c r="Z26" s="35"/>
+    </row>
+    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="145"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="107">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E27" s="47">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="F27" s="47">
+        <f>ROUND(E27*1.02,3)</f>
+      </c>
+      <c r="G27" s="47">
+        <f>ROUND(F27*1.02,3)</f>
+      </c>
+      <c r="H27" s="47">
+        <f>ROUND(G27*1.02,3)</f>
+      </c>
+      <c r="I27" s="47">
+        <f>ROUND(H27*1.02,3)</f>
+      </c>
+      <c r="J27" s="47">
+        <f>ROUND(I27*1.02,3)</f>
+      </c>
+      <c r="K27" s="11"/>
+      <c r="L27" s="7"/>
+      <c r="N27" t="s">
+        <v>177</v>
+      </c>
+      <c r="O27" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="P27" s="24">
+        <v>0.12</v>
+      </c>
+      <c r="Q27" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="S27" s="34"/>
+      <c r="U27" s="34"/>
+      <c r="W27" s="34"/>
+      <c r="Y27" s="34"/>
+      <c r="Z27" s="35"/>
+    </row>
+    <row r="28" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="146" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" s="147"/>
+      <c r="C28" s="101"/>
+      <c r="D28" s="106">
+        <v>417</v>
+      </c>
+      <c r="E28" s="49">
+        <f>+D28+E26</f>
+      </c>
+      <c r="F28" s="49">
+        <f t="shared" ref="F28:J28" si="6">+E28+F26</f>
+      </c>
+      <c r="G28" s="49">
+        <f t="shared" si="6"/>
+      </c>
+      <c r="H28" s="49">
+        <f t="shared" si="6"/>
+      </c>
+      <c r="I28" s="49">
+        <f t="shared" si="6"/>
+      </c>
+      <c r="J28" s="49">
+        <f t="shared" si="6"/>
+      </c>
+      <c r="K28" s="12"/>
+      <c r="L28" s="7"/>
+      <c r="O28" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="P28" s="77">
+        <v>0.2</v>
+      </c>
+      <c r="Q28" s="70">
+        <v>0.8</v>
+      </c>
+      <c r="S28" s="34"/>
+      <c r="U28" s="34"/>
+      <c r="W28" s="34"/>
+      <c r="Y28" s="34"/>
+      <c r="Z28" s="35"/>
+    </row>
+    <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="148" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="149"/>
+      <c r="C29" s="102"/>
+      <c r="D29" s="108">
+        <f>+D28*(1-D27)</f>
+      </c>
+      <c r="E29" s="50">
+        <f>+E28*(1-E27)</f>
+      </c>
+      <c r="F29" s="50">
+        <f t="shared" ref="F29:J29" si="7">+F28*(1-F27)</f>
+      </c>
+      <c r="G29" s="50">
+        <f t="shared" si="7"/>
+      </c>
+      <c r="H29" s="50">
+        <f t="shared" si="7"/>
+      </c>
+      <c r="I29" s="50">
+        <f t="shared" si="7"/>
+      </c>
+      <c r="J29" s="50">
+        <f t="shared" si="7"/>
+      </c>
+      <c r="K29" s="12"/>
+      <c r="L29" s="7"/>
+      <c r="N29" s="69" t="s">
+        <v>130</v>
+      </c>
+      <c r="S29" s="34"/>
+      <c r="U29" s="34"/>
+      <c r="W29" s="34"/>
+      <c r="Y29" s="34"/>
+      <c r="Z29" s="35"/>
+    </row>
+    <row r="30" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="135" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="136"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="48">
+        <v>0</v>
+      </c>
+      <c r="E30" s="45">
+        <v>4</v>
+      </c>
+      <c r="F30" s="45">
+        <v>4</v>
+      </c>
+      <c r="G30" s="45">
+        <v>4</v>
+      </c>
+      <c r="H30" s="45">
+        <v>4</v>
+      </c>
+      <c r="I30" s="45">
+        <v>4</v>
+      </c>
+      <c r="J30" s="45">
+        <v>4</v>
+      </c>
+      <c r="K30" s="11"/>
+      <c r="L30" s="7"/>
+      <c r="N30" s="69" t="s">
+        <v>178</v>
+      </c>
+      <c r="O30" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="P30" s="76"/>
+      <c r="S30" s="34"/>
+      <c r="U30" s="34"/>
+      <c r="W30" s="34"/>
+      <c r="Y30" s="34"/>
+      <c r="Z30" s="35"/>
+    </row>
+    <row r="31" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="144" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="145"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="108">
+        <f>+D30*D29*0.41*0.07</f>
+      </c>
+      <c r="E31" s="63">
+        <f>+E29*E30*$P$24*$P$22*$P$23*$P$36</f>
+      </c>
+      <c r="F31" s="63">
+        <f>+F29*F30*$P$24*$P$22*$P$23*$P$36</f>
+      </c>
+      <c r="G31" s="63">
+        <f>+G29*G30*$P$24*$P$22*$P$23*$P$36</f>
+      </c>
+      <c r="H31" s="63">
+        <f>+H29*H30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+      </c>
+      <c r="I31" s="63">
+        <f>+I29*I30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+      </c>
+      <c r="J31" s="63">
+        <f>+J29*J30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+      </c>
+      <c r="K31" s="11"/>
+      <c r="L31" s="7"/>
+      <c r="S31" s="34"/>
+      <c r="U31" s="34"/>
+      <c r="W31" s="34"/>
+      <c r="Y31" s="34"/>
+      <c r="Z31" s="35"/>
+    </row>
+    <row r="32" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="135" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="136"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="48">
+        <v>0</v>
+      </c>
+      <c r="E32" s="45">
+        <v>5</v>
+      </c>
+      <c r="F32" s="45">
+        <v>5</v>
+      </c>
+      <c r="G32" s="45">
+        <v>5</v>
+      </c>
+      <c r="H32" s="45">
+        <v>5</v>
+      </c>
+      <c r="I32" s="45">
+        <v>5</v>
+      </c>
+      <c r="J32" s="45">
+        <v>5</v>
+      </c>
+      <c r="K32" s="11"/>
+      <c r="L32" s="7"/>
+      <c r="N32" s="69" t="s">
+        <v>179</v>
+      </c>
+      <c r="O32" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="P32" s="75" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="73">
+        <f>+IF(P32=TRUE,1.1,0.95)</f>
+      </c>
+      <c r="S32" s="34"/>
+      <c r="U32" s="34"/>
+      <c r="W32" s="34"/>
+      <c r="Z32" s="35"/>
+    </row>
+    <row r="33" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="144" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="145"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="44">
+        <v>0</v>
+      </c>
+      <c r="E33" s="63">
+        <f t="shared" ref="E33:J33" si="8">+E26*E32*$P$26*$P$27*$P$36</f>
+      </c>
+      <c r="F33" s="63">
+        <f t="shared" si="8"/>
+      </c>
+      <c r="G33" s="63">
+        <f t="shared" si="8"/>
+      </c>
+      <c r="H33" s="63">
+        <f t="shared" si="8"/>
+      </c>
+      <c r="I33" s="63">
+        <f t="shared" si="8"/>
+      </c>
+      <c r="J33" s="63">
+        <f t="shared" si="8"/>
+      </c>
+      <c r="K33" s="11"/>
+      <c r="L33" s="7"/>
+      <c r="O33" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="P33" s="75" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="73">
+        <f t="shared" ref="Q33:Q35" si="9">+IF(P33=TRUE,1.1,0.95)</f>
+      </c>
+    </row>
+    <row r="34" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="148" t="s">
+        <v>26</v>
+      </c>
+      <c r="B34" s="149"/>
+      <c r="C34" s="102"/>
+      <c r="D34" s="108">
+        <f>+D29*D30</f>
+      </c>
+      <c r="E34" s="46">
+        <f>+E29*E30*$P$24+E26*E32</f>
+      </c>
+      <c r="F34" s="46">
+        <f>+F29*F30*$P$24+F26*F32</f>
+      </c>
+      <c r="G34" s="46">
+        <f>+G29*G30*$P$24+G26*G32</f>
+      </c>
+      <c r="H34" s="46">
+        <f>+H29*H30*$P$24*$Q$24+H26*H32</f>
+      </c>
+      <c r="I34" s="46">
+        <f>+I29*I30*$P$24*$Q$24+I26*I32</f>
+      </c>
+      <c r="J34" s="46">
+        <f>+J29*J30*$P$24*$Q$24+J26*J32</f>
+      </c>
+      <c r="K34" s="11"/>
+      <c r="L34" s="7"/>
+      <c r="O34" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="P34" s="75" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="73">
+        <f t="shared" si="9"/>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="148" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" s="149"/>
+      <c r="C35" s="102"/>
+      <c r="D35" s="109">
+        <f>+D31*1.02</f>
+      </c>
+      <c r="E35" s="50">
+        <f>+E31+E33+1.05*(E31+E33)</f>
+      </c>
+      <c r="F35" s="50">
+        <f t="shared" ref="F35:J35" si="10">+F31+F33+1.05*(F31+F33)</f>
+      </c>
+      <c r="G35" s="50">
+        <f t="shared" si="10"/>
+      </c>
+      <c r="H35" s="50">
+        <f t="shared" si="10"/>
+      </c>
+      <c r="I35" s="50">
+        <f t="shared" si="10"/>
+      </c>
+      <c r="J35" s="50">
+        <f t="shared" si="10"/>
+      </c>
+      <c r="K35" s="11"/>
+      <c r="L35" s="7"/>
+      <c r="O35" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="P35" s="75" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="73">
+        <f t="shared" si="9"/>
+      </c>
+    </row>
+    <row r="36" spans="1:17" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="150" t="s">
+        <v>6</v>
+      </c>
+      <c r="B36" s="6">
+        <f>+C8</f>
+      </c>
+      <c r="C36" s="6"/>
+      <c r="D36" s="11">
+        <v>0</v>
+      </c>
+      <c r="E36" s="156">
+        <v>4</v>
+      </c>
+      <c r="F36" s="156">
+        <v>6</v>
+      </c>
+      <c r="G36" s="156">
+        <v>6</v>
+      </c>
+      <c r="H36" s="156">
+        <v>8</v>
+      </c>
+      <c r="I36" s="156">
+        <v>9</v>
+      </c>
+      <c r="J36" s="156">
+        <v>11</v>
+      </c>
+      <c r="K36" s="115">
+        <f>SUM(E36:J36)</f>
+      </c>
+      <c r="L36" s="7"/>
+      <c r="N36" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CVの件数はAと同じ（サンクスLINEで友だちになる方は資料請求・来場予約済みなので、LINE経由のCVに数えていない）</t>
+        </is>
+      </c>
+      <c r="O36" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="P36" s="74">
+        <f>1*(Q32*Q33*Q34*Q35)</f>
+      </c>
+      <c r="Q36" s="73"/>
+    </row>
+    <row r="37" spans="1:17" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="151"/>
+      <c r="B37" s="6">
+        <f>+C9</f>
+      </c>
+      <c r="C37" s="6"/>
+      <c r="D37" s="11">
+        <v>0</v>
+      </c>
+      <c r="E37" s="156">
+        <v>2</v>
+      </c>
+      <c r="F37" s="156">
+        <v>3</v>
+      </c>
+      <c r="G37" s="156">
+        <v>4</v>
+      </c>
+      <c r="H37" s="156">
+        <v>6</v>
+      </c>
+      <c r="I37" s="156">
+        <v>7</v>
+      </c>
+      <c r="J37" s="156">
+        <v>8</v>
+      </c>
+      <c r="K37" s="115">
+        <f>SUM(E37:J37)</f>
+      </c>
+      <c r="L37" s="7"/>
+      <c r="N37" s="69" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="150" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="6">
+        <f>+C10</f>
+      </c>
+      <c r="C38" s="6"/>
+      <c r="D38" s="11">
+        <v>0</v>
+      </c>
+      <c r="E38" s="111">
+        <v>0</v>
+      </c>
+      <c r="F38" s="111">
+        <v>0</v>
+      </c>
+      <c r="G38" s="111">
+        <v>0</v>
+      </c>
+      <c r="H38" s="111">
+        <v>0</v>
+      </c>
+      <c r="I38" s="111">
+        <v>0</v>
+      </c>
+      <c r="J38" s="111">
+        <v>0</v>
+      </c>
+      <c r="K38" s="115">
+        <f>SUM(E38:J38)</f>
+      </c>
+      <c r="L38" s="7"/>
+      <c r="N38" s="69" t="s">
+        <v>118</v>
+      </c>
+      <c r="O38" s="21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="151"/>
+      <c r="B39" s="6">
+        <f>+C11</f>
+      </c>
+      <c r="C39" s="6"/>
+      <c r="D39" s="11">
+        <v>0</v>
+      </c>
+      <c r="E39" s="111">
+        <v>0</v>
+      </c>
+      <c r="F39" s="111">
+        <v>0</v>
+      </c>
+      <c r="G39" s="111">
+        <v>0</v>
+      </c>
+      <c r="H39" s="111">
+        <v>0</v>
+      </c>
+      <c r="I39" s="111">
+        <v>0</v>
+      </c>
+      <c r="J39" s="111">
+        <v>0</v>
+      </c>
+      <c r="K39" s="115">
+        <f>SUM(E39:J39)</f>
+      </c>
+      <c r="L39" s="7"/>
+      <c r="N39" s="69" t="s">
+        <v>118</v>
+      </c>
+      <c r="O39" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="152" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" s="153"/>
+      <c r="C40" s="97"/>
+      <c r="D40" s="11">
+        <f>SUM(D36:D39)</f>
+      </c>
+      <c r="E40" s="10">
+        <f>SUM(E36:E39)</f>
+      </c>
+      <c r="F40" s="10">
+        <f t="shared" ref="F40:J40" si="11">SUM(F36:F39)</f>
+      </c>
+      <c r="G40" s="10">
+        <f t="shared" si="11"/>
+      </c>
+      <c r="H40" s="10">
+        <f t="shared" si="11"/>
+      </c>
+      <c r="I40" s="10">
+        <f t="shared" si="11"/>
+      </c>
+      <c r="J40" s="10">
+        <f t="shared" si="11"/>
+      </c>
+      <c r="K40" s="115">
+        <f>SUM(E40:J40)</f>
+      </c>
+      <c r="L40" s="7"/>
+      <c r="O40" s="17"/>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D41" s="18">
+        <f t="shared" ref="D41" si="12">+IFERROR(D40/D35,0)</f>
+      </c>
+      <c r="E41" s="18">
+        <f>IFERROR(E40/E35,0)</f>
+      </c>
+      <c r="F41" s="18">
+        <f t="shared" ref="F41:J41" si="13">IFERROR(F40/F35,0)</f>
+      </c>
+      <c r="G41" s="18">
+        <f t="shared" si="13"/>
+      </c>
+      <c r="H41" s="18">
+        <f t="shared" si="13"/>
+      </c>
+      <c r="I41" s="18">
+        <f t="shared" si="13"/>
+      </c>
+      <c r="J41" s="18">
+        <f t="shared" si="13"/>
+      </c>
+      <c r="N41" s="69" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" s="29"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="116"/>
+      <c r="F42" s="116"/>
+      <c r="G42" s="116"/>
+      <c r="H42" s="116"/>
+      <c r="I42" s="116"/>
+      <c r="J42" s="116"/>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="B44" s="145"/>
+      <c r="C44" s="103"/>
+      <c r="D44" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E44" s="31">
+        <f>+E75*E76</f>
+      </c>
+      <c r="F44" s="31">
+        <f t="shared" ref="F44:J44" si="14">+F75*F76</f>
+      </c>
+      <c r="G44" s="31">
+        <f t="shared" si="14"/>
+      </c>
+      <c r="H44" s="31">
+        <f t="shared" si="14"/>
+      </c>
+      <c r="I44" s="31">
+        <f t="shared" si="14"/>
+      </c>
+      <c r="J44" s="31">
+        <f t="shared" si="14"/>
+      </c>
+      <c r="K44" s="11"/>
+      <c r="L44" s="7"/>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="144" t="s">
+        <v>129</v>
+      </c>
+      <c r="B45" s="145"/>
+      <c r="C45" s="104">
+        <f>+SUM(C65:C72)</f>
+      </c>
+      <c r="D45" s="80">
+        <f>+SUM(D65:D72)</f>
+      </c>
+      <c r="E45" s="27">
+        <f>SUM(E65:E69)+SUM(E71:E72)</f>
+      </c>
+      <c r="F45" s="27">
+        <f t="shared" ref="F45:J45" si="15">SUM(F65:F69)+SUM(F71:F72)</f>
+      </c>
+      <c r="G45" s="27">
+        <f t="shared" si="15"/>
+      </c>
+      <c r="H45" s="27">
+        <f t="shared" si="15"/>
+      </c>
+      <c r="I45" s="27">
+        <f t="shared" si="15"/>
+      </c>
+      <c r="J45" s="27">
+        <f t="shared" si="15"/>
+      </c>
+      <c r="K45" s="11"/>
+      <c r="L45" s="7"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="144" t="s">
+        <v>17</v>
+      </c>
+      <c r="B46" s="145"/>
+      <c r="C46" s="103"/>
+      <c r="D46" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" s="28">
+        <f t="shared" ref="E46:J46" si="16">SUM(E65:E67)/(E28-D28)</f>
+      </c>
+      <c r="F46" s="28">
+        <f t="shared" si="16"/>
+      </c>
+      <c r="G46" s="28">
+        <f t="shared" si="16"/>
+      </c>
+      <c r="H46" s="28">
+        <f t="shared" si="16"/>
+      </c>
+      <c r="I46" s="28">
+        <f t="shared" si="16"/>
+      </c>
+      <c r="J46" s="28">
+        <f t="shared" si="16"/>
+      </c>
+      <c r="K46" s="11"/>
+      <c r="L46" s="7"/>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="144" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47" s="145"/>
+      <c r="C47" s="103"/>
+      <c r="D47" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E47" s="28">
+        <f t="shared" ref="E47:I47" si="17">+E51/E35</f>
+      </c>
+      <c r="F47" s="28">
+        <f t="shared" si="17"/>
+      </c>
+      <c r="G47" s="28">
+        <f t="shared" si="17"/>
+      </c>
+      <c r="H47" s="28">
+        <f t="shared" si="17"/>
+      </c>
+      <c r="I47" s="28">
+        <f t="shared" si="17"/>
+      </c>
+      <c r="J47" s="28">
+        <f>+J51/J35</f>
+      </c>
+      <c r="K47" s="11"/>
+      <c r="L47" s="7"/>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="144" t="s">
+        <v>20</v>
+      </c>
+      <c r="B48" s="145"/>
+      <c r="C48" s="103"/>
+      <c r="D48" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E48" s="32">
+        <f>IFERROR(E40/E35,0)</f>
+      </c>
+      <c r="F48" s="32">
+        <f t="shared" ref="F48:J48" si="18">IFERROR(F40/F35,0)</f>
+      </c>
+      <c r="G48" s="32">
+        <f t="shared" si="18"/>
+      </c>
+      <c r="H48" s="32">
+        <f t="shared" si="18"/>
+      </c>
+      <c r="I48" s="32">
+        <f t="shared" si="18"/>
+      </c>
+      <c r="J48" s="32">
+        <f t="shared" si="18"/>
+      </c>
+      <c r="K48" s="11"/>
+      <c r="L48" s="7"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="152" t="s">
+        <v>19</v>
+      </c>
+      <c r="B49" s="153"/>
+      <c r="C49" s="105"/>
+      <c r="D49" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E49" s="28">
+        <f>IFERROR(E51/E40,0)</f>
+      </c>
+      <c r="F49" s="28">
+        <f t="shared" ref="F49:J49" si="19">IFERROR(F51/F40,0)</f>
+      </c>
+      <c r="G49" s="28">
+        <f t="shared" si="19"/>
+      </c>
+      <c r="H49" s="28">
+        <f t="shared" si="19"/>
+      </c>
+      <c r="I49" s="28">
+        <f t="shared" si="19"/>
+      </c>
+      <c r="J49" s="28">
+        <f t="shared" si="19"/>
+      </c>
+      <c r="K49" s="11"/>
+      <c r="L49" s="7"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="152" t="s">
+        <v>116</v>
+      </c>
+      <c r="B50" s="153"/>
+      <c r="C50" s="105"/>
+      <c r="D50" s="64" t="s">
+        <v>22</v>
+      </c>
+      <c r="E50" s="65">
+        <f>+E36*$D$8+E38*$D$10</f>
+      </c>
+      <c r="F50" s="65">
+        <f t="shared" ref="F50:J50" si="20">+F36*$D$8+F38*$D$10</f>
+      </c>
+      <c r="G50" s="65">
+        <f t="shared" si="20"/>
+      </c>
+      <c r="H50" s="65">
+        <f t="shared" si="20"/>
+      </c>
+      <c r="I50" s="65">
+        <f t="shared" si="20"/>
+      </c>
+      <c r="J50" s="65">
+        <f t="shared" si="20"/>
+      </c>
+      <c r="K50" s="11"/>
+      <c r="L50" s="7"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="154" t="s">
+        <v>70</v>
+      </c>
+      <c r="B51" s="155"/>
+      <c r="C51" s="110">
+        <f>+C45</f>
+      </c>
+      <c r="D51" s="40">
+        <f>+D45</f>
+      </c>
+      <c r="E51" s="40">
+        <f>SUM(E45,E50)+E44</f>
+      </c>
+      <c r="F51" s="40">
+        <f t="shared" ref="F51:I51" si="21">SUM(F45,F50)+F44</f>
+      </c>
+      <c r="G51" s="40">
+        <f t="shared" si="21"/>
+      </c>
+      <c r="H51" s="40">
+        <f t="shared" si="21"/>
+      </c>
+      <c r="I51" s="40">
+        <f t="shared" si="21"/>
+      </c>
+      <c r="J51" s="40">
+        <f>SUM(J45,J50)+J44</f>
+      </c>
+      <c r="K51" s="11"/>
+      <c r="L51" s="7"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="22"/>
+      <c r="B52" s="22"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="37"/>
+      <c r="F52" s="37"/>
+      <c r="G52" s="37"/>
+      <c r="H52" s="37"/>
+      <c r="I52" s="37"/>
+      <c r="J52" s="37"/>
+    </row>
+    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="29" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="B54" s="145"/>
+      <c r="C54" s="96"/>
+      <c r="D54" s="28">
+        <f>+D75*D76</f>
+      </c>
+      <c r="E54" s="28">
+        <f t="shared" ref="E54:J54" si="22">+E75*E76</f>
+      </c>
+      <c r="F54" s="28">
+        <f t="shared" si="22"/>
+      </c>
+      <c r="G54" s="28">
+        <f t="shared" si="22"/>
+      </c>
+      <c r="H54" s="28">
+        <f t="shared" si="22"/>
+      </c>
+      <c r="I54" s="28">
+        <f t="shared" si="22"/>
+      </c>
+      <c r="J54" s="28">
+        <f t="shared" si="22"/>
+      </c>
+      <c r="K54" s="11"/>
+      <c r="L54" s="7"/>
+    </row>
+    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="144" t="s">
+        <v>129</v>
+      </c>
+      <c r="B55" s="145"/>
+      <c r="C55" s="96"/>
+      <c r="D55" s="27">
+        <f>+SUM(D65:D72)</f>
+      </c>
+      <c r="E55" s="27">
+        <f>SUM(E65:E72)+E54</f>
+      </c>
+      <c r="F55" s="27">
+        <f t="shared" ref="F55:J55" si="23">SUM(F65:F72)+F54</f>
+      </c>
+      <c r="G55" s="27">
+        <f t="shared" si="23"/>
+      </c>
+      <c r="H55" s="27">
+        <f t="shared" si="23"/>
+      </c>
+      <c r="I55" s="27">
+        <f t="shared" si="23"/>
+      </c>
+      <c r="J55" s="27">
+        <f t="shared" si="23"/>
+      </c>
+      <c r="K55" s="11"/>
+      <c r="L55" s="7"/>
+    </row>
+    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="144" t="s">
+        <v>17</v>
+      </c>
+      <c r="B56" s="145"/>
+      <c r="C56" s="96"/>
+      <c r="D56" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E56" s="28">
+        <f t="shared" ref="E56:J56" si="24">SUM(E65:E67)/(E28-D28)</f>
+      </c>
+      <c r="F56" s="28">
+        <f t="shared" si="24"/>
+      </c>
+      <c r="G56" s="28">
+        <f t="shared" si="24"/>
+      </c>
+      <c r="H56" s="28">
+        <f t="shared" si="24"/>
+      </c>
+      <c r="I56" s="28">
+        <f t="shared" si="24"/>
+      </c>
+      <c r="J56" s="28">
+        <f t="shared" si="24"/>
+      </c>
+      <c r="K56" s="11"/>
+      <c r="L56" s="7"/>
+    </row>
+    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="144" t="s">
+        <v>18</v>
+      </c>
+      <c r="B57" s="145"/>
+      <c r="C57" s="96"/>
+      <c r="D57" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E57" s="28">
+        <f>+E61/E35</f>
+      </c>
+      <c r="F57" s="28">
+        <f t="shared" ref="F57:J57" si="25">+F61/F35</f>
+      </c>
+      <c r="G57" s="28">
+        <f t="shared" si="25"/>
+      </c>
+      <c r="H57" s="28">
+        <f t="shared" si="25"/>
+      </c>
+      <c r="I57" s="28">
+        <f t="shared" si="25"/>
+      </c>
+      <c r="J57" s="28">
+        <f t="shared" si="25"/>
+      </c>
+      <c r="K57" s="11"/>
+      <c r="L57" s="7"/>
+    </row>
+    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="144" t="s">
+        <v>20</v>
+      </c>
+      <c r="B58" s="145"/>
+      <c r="C58" s="96"/>
+      <c r="D58" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E58" s="32">
+        <f t="shared" ref="E58:J58" si="26">+IFERROR(E36/E35,0)</f>
+      </c>
+      <c r="F58" s="32">
+        <f t="shared" si="26"/>
+      </c>
+      <c r="G58" s="32">
+        <f t="shared" si="26"/>
+      </c>
+      <c r="H58" s="32">
+        <f t="shared" si="26"/>
+      </c>
+      <c r="I58" s="32">
+        <f t="shared" si="26"/>
+      </c>
+      <c r="J58" s="32">
+        <f t="shared" si="26"/>
+      </c>
+      <c r="K58" s="11"/>
+      <c r="L58" s="7"/>
+    </row>
+    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="152" t="s">
+        <v>19</v>
+      </c>
+      <c r="B59" s="153"/>
+      <c r="C59" s="97"/>
+      <c r="D59" s="28"/>
+      <c r="E59" s="28">
+        <f t="shared" ref="E59:J59" si="27">+IFERROR(E55/E36,0)</f>
+      </c>
+      <c r="F59" s="28">
+        <f t="shared" si="27"/>
+      </c>
+      <c r="G59" s="28">
+        <f t="shared" si="27"/>
+      </c>
+      <c r="H59" s="28">
+        <f t="shared" si="27"/>
+      </c>
+      <c r="I59" s="28">
+        <f t="shared" si="27"/>
+      </c>
+      <c r="J59" s="28">
+        <f t="shared" si="27"/>
+      </c>
+      <c r="K59" s="11"/>
+      <c r="L59" s="7"/>
+    </row>
+    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="152" t="s">
+        <v>116</v>
+      </c>
+      <c r="B60" s="153"/>
+      <c r="C60" s="97"/>
+      <c r="D60" s="28"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="28"/>
+      <c r="G60" s="28"/>
+      <c r="H60" s="28"/>
+      <c r="I60" s="28"/>
+      <c r="J60" s="28"/>
+      <c r="K60" s="11"/>
+      <c r="L60" s="7"/>
+    </row>
+    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="154" t="s">
+        <v>70</v>
+      </c>
+      <c r="B61" s="155"/>
+      <c r="C61" s="98"/>
+      <c r="D61" s="40">
+        <f>+D55</f>
+      </c>
+      <c r="E61" s="40">
+        <f>+SUM(E65:E72)+E54</f>
+      </c>
+      <c r="F61" s="40">
+        <f t="shared" ref="F61:J61" si="28">+SUM(F65:F72)+F54</f>
+      </c>
+      <c r="G61" s="40">
+        <f t="shared" si="28"/>
+      </c>
+      <c r="H61" s="40">
+        <f t="shared" si="28"/>
+      </c>
+      <c r="I61" s="40">
+        <f t="shared" si="28"/>
+      </c>
+      <c r="J61" s="40">
+        <f t="shared" si="28"/>
+      </c>
+      <c r="K61" s="11"/>
+      <c r="L61" s="7"/>
+    </row>
+    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="C64" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C65" s="90">
+        <v>0</v>
+      </c>
+      <c r="D65" s="51">
+        <v>0</v>
+      </c>
+      <c r="E65" s="28">
+        <v>0</v>
+      </c>
+      <c r="F65" s="28">
+        <v>0</v>
+      </c>
+      <c r="G65" s="28">
+        <v>0</v>
+      </c>
+      <c r="H65" s="28">
+        <v>0</v>
+      </c>
+      <c r="I65" s="28">
+        <v>0</v>
+      </c>
+      <c r="J65" s="28">
+        <v>0</v>
+      </c>
+      <c r="N65" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" s="90">
+        <v>0</v>
+      </c>
+      <c r="D66" s="51">
+        <v>15000</v>
+      </c>
+      <c r="E66" s="28">
+        <v>30000</v>
+      </c>
+      <c r="F66" s="28">
+        <v>30000</v>
+      </c>
+      <c r="G66" s="28">
+        <v>30000</v>
+      </c>
+      <c r="H66" s="28">
+        <v>30000</v>
+      </c>
+      <c r="I66" s="28">
+        <v>30000</v>
+      </c>
+      <c r="J66" s="28">
+        <v>30000</v>
+      </c>
+      <c r="N66" s="69" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="B67" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C67" s="90">
+        <v>0</v>
+      </c>
+      <c r="D67" s="51">
+        <v>0</v>
+      </c>
+      <c r="E67" s="28">
+        <v>0</v>
+      </c>
+      <c r="F67" s="28">
+        <v>0</v>
+      </c>
+      <c r="G67" s="28">
+        <v>0</v>
+      </c>
+      <c r="H67" s="28">
+        <v>0</v>
+      </c>
+      <c r="I67" s="28">
+        <v>0</v>
+      </c>
+      <c r="J67" s="28">
+        <v>0</v>
+      </c>
+      <c r="N67" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サンクスLINE誘導：入れない（オプション：初期15万・月3万〜）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" s="15"/>
+      <c r="B68" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C68" s="90">
+        <v>0</v>
+      </c>
+      <c r="D68" s="51">
+        <v>0</v>
+      </c>
+      <c r="E68" s="28">
+        <f t="shared" ref="E68:J68" si="29">IF(E34&lt;5000,5000,15000)</f>
+      </c>
+      <c r="F68" s="28">
+        <f t="shared" si="29"/>
+      </c>
+      <c r="G68" s="28">
+        <f t="shared" si="29"/>
+      </c>
+      <c r="H68" s="28">
+        <f t="shared" si="29"/>
+      </c>
+      <c r="I68" s="28">
+        <f t="shared" si="29"/>
+      </c>
+      <c r="J68" s="28">
+        <f t="shared" si="29"/>
+      </c>
+      <c r="N68" s="69" t="s">
+        <v>186</v>
+      </c>
+      <c r="O68" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="P68" s="75">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="15"/>
+      <c r="B69" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C69" s="90">
+        <v>0</v>
+      </c>
+      <c r="D69" s="51">
+        <v>100000</v>
+      </c>
+      <c r="E69" s="28">
+        <v>200000</v>
+      </c>
+      <c r="F69" s="28">
+        <v>200000</v>
+      </c>
+      <c r="G69" s="28">
+        <v>200000</v>
+      </c>
+      <c r="H69" s="28">
+        <v>200000</v>
+      </c>
+      <c r="I69" s="28">
+        <v>200000</v>
+      </c>
+      <c r="J69" s="28">
+        <v>200000</v>
+      </c>
+      <c r="N69" s="69" t="s">
+        <v>188</v>
+      </c>
+      <c r="O69" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="15"/>
+      <c r="B70" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C70" s="90">
+        <v>0</v>
+      </c>
+      <c r="D70" s="51">
+        <v>0</v>
+      </c>
+      <c r="E70" s="28">
+        <v>0</v>
+      </c>
+      <c r="F70" s="28">
+        <v>0</v>
+      </c>
+      <c r="G70" s="28">
+        <v>0</v>
+      </c>
+      <c r="H70" s="28">
+        <v>0</v>
+      </c>
+      <c r="I70" s="28">
+        <v>0</v>
+      </c>
+      <c r="J70" s="28">
+        <v>0</v>
+      </c>
+      <c r="N70" s="69" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" s="15"/>
+      <c r="B71" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C71" s="90">
+        <v>0</v>
+      </c>
+      <c r="D71" s="51">
+        <v>0</v>
+      </c>
+      <c r="E71" s="28">
+        <v>0</v>
+      </c>
+      <c r="F71" s="28">
+        <v>0</v>
+      </c>
+      <c r="G71" s="28">
+        <v>0</v>
+      </c>
+      <c r="H71" s="28">
+        <v>0</v>
+      </c>
+      <c r="I71" s="28">
+        <v>0</v>
+      </c>
+      <c r="J71" s="28">
+        <v>0</v>
+      </c>
+      <c r="N71" s="69" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="15"/>
+      <c r="B72" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C72" s="90">
+        <v>0</v>
+      </c>
+      <c r="D72" s="51">
+        <v>0</v>
+      </c>
+      <c r="E72" s="28">
+        <v>0</v>
+      </c>
+      <c r="F72" s="28">
+        <v>0</v>
+      </c>
+      <c r="G72" s="28">
+        <v>0</v>
+      </c>
+      <c r="H72" s="28">
+        <v>0</v>
+      </c>
+      <c r="I72" s="28">
+        <v>0</v>
+      </c>
+      <c r="J72" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="15"/>
+      <c r="B73" s="112" t="s">
+        <v>151</v>
+      </c>
+      <c r="C73" s="113">
+        <v>0</v>
+      </c>
+      <c r="D73" s="114">
+        <f>SUM(D65:D72)</f>
+      </c>
+      <c r="E73" s="114">
+        <f t="shared" ref="E73:J73" si="30">SUM(E65:E72)+E54</f>
+      </c>
+      <c r="F73" s="114">
+        <f t="shared" si="30"/>
+      </c>
+      <c r="G73" s="114">
+        <f t="shared" si="30"/>
+      </c>
+      <c r="H73" s="114">
+        <f t="shared" si="30"/>
+      </c>
+      <c r="I73" s="114">
+        <f t="shared" si="30"/>
+      </c>
+      <c r="J73" s="114">
+        <f t="shared" si="30"/>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="15"/>
+      <c r="B74" s="15"/>
+      <c r="C74" s="15"/>
+      <c r="D74" s="15"/>
+      <c r="E74" s="15"/>
+      <c r="F74" s="15"/>
+      <c r="G74" s="15"/>
+      <c r="H74" s="15"/>
+      <c r="I74" s="15"/>
+      <c r="J74" s="15"/>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="B75" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D75" s="41">
+        <f t="shared" ref="D75:J75" si="31">+IF(D34&lt;30001,0,D34-30000)</f>
+      </c>
+      <c r="E75" s="41">
+        <f t="shared" si="31"/>
+      </c>
+      <c r="F75" s="41">
+        <f t="shared" si="31"/>
+      </c>
+      <c r="G75" s="41">
+        <f t="shared" si="31"/>
+      </c>
+      <c r="H75" s="41">
+        <f t="shared" si="31"/>
+      </c>
+      <c r="I75" s="41">
+        <f t="shared" si="31"/>
+      </c>
+      <c r="J75" s="41">
+        <f t="shared" si="31"/>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="B76" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D76" s="5">
+        <f t="shared" ref="D76:J76" si="32">+IF(D75&lt;=$U$18,$Z$18,IF(D75&lt;=$U$19,$Z$19,IF(D75&lt;=$U$20,$Z$20,IF(D75&lt;=$U$21,$Z$21,IF(D75&lt;=$U$22,$Z$22,IF(D75&lt;=$U$23,$Z$23,IF(D75&lt;=$U$24,$Z$24,IF(D75&lt;=$U$25,$Z$25,IF(D75&lt;=$U$26,$Z$26,IF(D75&lt;=$U$27,$Z$27,IF(D75&lt;=$U$28,$Z$28,IF(D75&lt;=$U$29,$Z$29,IF(D75&lt;=$U$30,$Z$30,0)))))))))))))</f>
+      </c>
+      <c r="E76" s="5">
+        <f t="shared" si="32"/>
+      </c>
+      <c r="F76" s="5">
+        <f t="shared" si="32"/>
+      </c>
+      <c r="G76" s="5">
+        <f t="shared" si="32"/>
+      </c>
+      <c r="H76" s="5">
+        <f t="shared" si="32"/>
+      </c>
+      <c r="I76" s="5">
+        <f t="shared" si="32"/>
+      </c>
+      <c r="J76" s="5">
+        <f t="shared" si="32"/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="35">
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+  </mergeCells>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3D322F6-2076-57E9-875D-3D967EDA726D}">
+  <dimension ref="A1:Y35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.5" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="41.75" style="29" customWidth="1"/>
+    <col min="2" max="2" width="3" style="5" customWidth="1"/>
+    <col min="3" max="6" width="26.08203125" style="5" customWidth="1"/>
+    <col min="7" max="17" width="9" style="5"/>
+    <col min="18" max="18" width="10.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9" style="5"/>
+    <col min="20" max="27" width="14.83203125" style="5" customWidth="1"/>
+    <col min="28" max="16384" width="9" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="E1" s="81" t="s">
+        <v>142</v>
+      </c>
+      <c r="F1" s="81">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="82" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="82"/>
+      <c r="C3" s="83" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="84" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" s="84" t="s">
+        <v>75</v>
+      </c>
+      <c r="F3" s="84"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="85" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="86">
+        <f>+'B_サンクス無'!D24</f>
+      </c>
+      <c r="D4" s="28">
+        <f>+'B_サンクス無'!G51</f>
+      </c>
+      <c r="E4" s="28">
+        <f>+'B_サンクス無'!J51</f>
+      </c>
+      <c r="F4" s="28"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="85" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="86">
+        <f>+'B_サンクス無'!D25</f>
+      </c>
+      <c r="D5" s="28">
+        <f>+'B_サンクス無'!G61</f>
+      </c>
+      <c r="E5" s="28">
+        <f>+'B_サンクス無'!J61</f>
+      </c>
+      <c r="F5" s="27"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="117">
+        <f>+'B_サンクス無'!D28</f>
+      </c>
+      <c r="D6" s="87">
+        <f>+'B_サンクス無'!G28</f>
+      </c>
+      <c r="E6" s="87">
+        <f>+'B_サンクス無'!J28</f>
+      </c>
+      <c r="F6" s="10"/>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="85" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="88">
+        <f>+'B_サンクス無'!D27</f>
+      </c>
+      <c r="D7" s="89">
+        <f>+'B_サンクス無'!G27</f>
+      </c>
+      <c r="E7" s="89">
+        <f>+'B_サンクス無'!J27</f>
+      </c>
+      <c r="F7" s="89"/>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="85" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="117">
+        <f>+'B_サンクス無'!D29</f>
+      </c>
+      <c r="D8" s="10">
+        <f>+'B_サンクス無'!G29</f>
+      </c>
+      <c r="E8" s="10">
+        <f>+'B_サンクス無'!J29</f>
+      </c>
+      <c r="F8" s="10"/>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="85"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="85" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="117">
+        <f>+'B_サンクス無'!D34</f>
+      </c>
+      <c r="D10" s="10">
+        <f>+'B_サンクス無'!G34</f>
+      </c>
+      <c r="E10" s="10">
+        <f>+'B_サンクス無'!J34</f>
+      </c>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="85" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="117">
+        <f>+'B_サンクス無'!D35</f>
+      </c>
+      <c r="D11" s="10">
+        <f>+'B_サンクス無'!G35</f>
+      </c>
+      <c r="E11" s="10">
+        <f>+'B_サンクス無'!J35</f>
+      </c>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="85" t="s">
+        <v>144</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="28">
+        <f>+IFERROR(C5/C11,0)</f>
+      </c>
+      <c r="D12" s="28">
+        <f>+D4/D11</f>
+      </c>
+      <c r="E12" s="28">
+        <f t="shared" ref="E12" si="0">+E4/E11</f>
+      </c>
+      <c r="F12" s="28"/>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="85" t="s">
+        <v>145</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="28">
+        <f>+IFERROR(C6/C12,0)</f>
+      </c>
+      <c r="D13" s="28">
+        <f>+D5/D11</f>
+      </c>
+      <c r="E13" s="28">
+        <f t="shared" ref="E13" si="1">+E5/E11</f>
+      </c>
+      <c r="F13" s="28"/>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="85"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="R14" s="29" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="85" t="s">
+        <v>189</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="87">
+        <f>+'B_サンクス無'!D16</f>
+      </c>
+      <c r="D15" s="87">
+        <f>+'B_サンクス無'!G16</f>
+      </c>
+      <c r="E15" s="87">
+        <f>+'B_サンクス無'!J16</f>
+      </c>
+      <c r="F15" s="87"/>
+      <c r="R15" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="85" t="s">
+        <v>190</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="87">
+        <f>+C17</f>
+      </c>
+      <c r="D16" s="87">
+        <f>+D17</f>
+      </c>
+      <c r="E16" s="87">
+        <f>+E17</f>
+      </c>
+      <c r="F16" s="87"/>
+      <c r="R16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="V16" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y16" s="35" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="85" t="s">
+        <v>191</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="87">
+        <f>+'B_サンクス無'!D36</f>
+      </c>
+      <c r="D17" s="87">
+        <f>+'B_サンクス無'!G36</f>
+      </c>
+      <c r="E17" s="87">
+        <f>+'B_サンクス無'!J36</f>
+      </c>
+      <c r="F17" s="10"/>
+      <c r="R17" s="5">
+        <v>0</v>
+      </c>
+      <c r="S17" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="T17" s="34">
+        <v>200000</v>
+      </c>
+      <c r="V17" s="5">
+        <v>0</v>
+      </c>
+      <c r="W17" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="X17" s="34">
+        <v>600000</v>
+      </c>
+      <c r="Y17" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="85" t="s">
+        <v>192</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="87">
+        <f>+'B_サンクス無'!D37</f>
+      </c>
+      <c r="D18" s="87">
+        <f>+'B_サンクス無'!G37</f>
+      </c>
+      <c r="E18" s="87">
+        <f>+'B_サンクス無'!J37</f>
+      </c>
+      <c r="F18" s="10"/>
+      <c r="R18" s="34">
+        <v>200000</v>
+      </c>
+      <c r="S18" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="T18" s="34">
+        <v>15000000</v>
+      </c>
+      <c r="V18" s="34">
+        <v>600000</v>
+      </c>
+      <c r="W18" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="X18" s="34">
+        <f>+T18*2.5</f>
+      </c>
+      <c r="Y18" s="35">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="85" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="7"/>
+      <c r="C19" s="87">
+        <f>+'B_サンクス無'!D38</f>
+      </c>
+      <c r="D19" s="87">
+        <f>+'B_サンクス無'!G38</f>
+      </c>
+      <c r="E19" s="87">
+        <f>+'B_サンクス無'!J38</f>
+      </c>
+      <c r="F19" s="10"/>
+      <c r="R19" s="34"/>
+      <c r="T19" s="34"/>
+      <c r="V19" s="34"/>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="35"/>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="85" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="87">
+        <f>+'B_サンクス無'!D39</f>
+      </c>
+      <c r="D20" s="87">
+        <f>+'B_サンクス無'!G39</f>
+      </c>
+      <c r="E20" s="87">
+        <f>+'B_サンクス無'!J39</f>
+      </c>
+      <c r="F20" s="10"/>
+      <c r="R20" s="34"/>
+      <c r="T20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="35"/>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="85"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="R21" s="34"/>
+      <c r="T21" s="34"/>
+      <c r="V21" s="34"/>
+      <c r="X21" s="34"/>
+      <c r="Y21" s="35"/>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="85" t="s">
+        <v>139</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="C22" s="90">
+        <f>+IFERROR(C4/C16,"--")</f>
+      </c>
+      <c r="D22" s="90">
+        <f t="shared" ref="D22:E22" si="2">+IFERROR(D4/D16,"--")</f>
+      </c>
+      <c r="E22" s="90">
+        <f t="shared" si="2"/>
+      </c>
+      <c r="F22" s="90"/>
+      <c r="R22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="35"/>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="85" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" s="7"/>
+      <c r="C23" s="90">
+        <f>+IFERROR(C5/C16,"--")</f>
+      </c>
+      <c r="D23" s="90">
+        <f t="shared" ref="D23" si="3">+IFERROR(D5/D16,"--")</f>
+      </c>
+      <c r="E23" s="90">
+        <f t="shared" ref="E23" si="4">+IFERROR(E5/E16,"--")</f>
+      </c>
+      <c r="F23" s="90"/>
+      <c r="R23" s="34"/>
+      <c r="T23" s="34"/>
+      <c r="V23" s="34"/>
+      <c r="X23" s="34"/>
+      <c r="Y23" s="35"/>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="85"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="R24" s="34"/>
+      <c r="T24" s="34"/>
+      <c r="V24" s="34"/>
+      <c r="X24" s="34"/>
+      <c r="Y24" s="35"/>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="85" t="s">
+        <v>146</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="10">
+        <f>+'B_サンクス無'!E68+C29*C30</f>
+      </c>
+      <c r="D25" s="10">
+        <f>+'B_サンクス無'!G68+D29*D30</f>
+      </c>
+      <c r="E25" s="10">
+        <f>+'B_サンクス無'!J68+E29*E30</f>
+      </c>
+      <c r="F25" s="10"/>
+      <c r="R25" s="34"/>
+      <c r="T25" s="34"/>
+      <c r="V25" s="34"/>
+      <c r="X25" s="34"/>
+      <c r="Y25" s="35"/>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="R26" s="34"/>
+      <c r="T26" s="34"/>
+      <c r="V26" s="34"/>
+      <c r="X26" s="34"/>
+      <c r="Y26" s="35"/>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="R27" s="34"/>
+      <c r="T27" s="34"/>
+      <c r="V27" s="34"/>
+      <c r="X27" s="34"/>
+      <c r="Y27" s="35"/>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="R28" s="34"/>
+      <c r="T28" s="34"/>
+      <c r="V28" s="34"/>
+      <c r="X28" s="34"/>
+      <c r="Y28" s="35"/>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="C29" s="5">
+        <f>+IF(C10&lt;=30000,0,C10-30000)</f>
+      </c>
+      <c r="D29" s="91">
+        <f>+IF(D10&lt;=30000,0,D10-30000)</f>
+      </c>
+      <c r="E29" s="91">
+        <f>+IF(E10&lt;=30000,0,E10-30000)</f>
+      </c>
+      <c r="F29" s="91"/>
+      <c r="R29" s="34"/>
+      <c r="T29" s="34"/>
+      <c r="V29" s="34"/>
+      <c r="X29" s="34"/>
+      <c r="Y29" s="35"/>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="C30" s="5">
+        <f>+IF(C29&lt;=$T$17,$Y$17,IF(C29&lt;=$T$18,$Y$18,IF(C29&lt;=$T$19,$Y$19,IF(C29&lt;=$T$20,$Y$20,IF(C29&lt;=$T$21,$Y$21,IF(C29&lt;=$T$22,$Y$22,IF(C29&lt;=$T$23,$Y$23,IF(C29&lt;=$T$24,$Y$24,IF(C29&lt;=$T$25,$Y$25,IF(C29&lt;=$T$26,$Y$26,IF(C29&lt;=$T$27,$Y$27,IF(C29&lt;=$T$28,$Y$28,IF(C29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+      </c>
+      <c r="D30" s="5">
+        <f>+IF(D29&lt;=$T$17,$Y$17,IF(D29&lt;=$T$18,$Y$18,IF(D29&lt;=$T$19,$Y$19,IF(D29&lt;=$T$20,$Y$20,IF(D29&lt;=$T$21,$Y$21,IF(D29&lt;=$T$22,$Y$22,IF(D29&lt;=$T$23,$Y$23,IF(D29&lt;=$T$24,$Y$24,IF(D29&lt;=$T$25,$Y$25,IF(D29&lt;=$T$26,$Y$26,IF(D29&lt;=$T$27,$Y$27,IF(D29&lt;=$T$28,$Y$28,IF(D29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+      </c>
+      <c r="E30" s="5">
+        <f>+IF(E29&lt;=$T$17,$Y$17,IF(E29&lt;=$T$18,$Y$18,IF(E29&lt;=$T$19,$Y$19,IF(E29&lt;=$T$20,$Y$20,IF(E29&lt;=$T$21,$Y$21,IF(E29&lt;=$T$22,$Y$22,IF(E29&lt;=$T$23,$Y$23,IF(E29&lt;=$T$24,$Y$24,IF(E29&lt;=$T$25,$Y$25,IF(E29&lt;=$T$26,$Y$26,IF(E29&lt;=$T$27,$Y$27,IF(E29&lt;=$T$28,$Y$28,IF(E29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+      </c>
+      <c r="R30" s="34"/>
+      <c r="T30" s="34"/>
+      <c r="V30" s="34"/>
+      <c r="X30" s="34"/>
+      <c r="Y30" s="35"/>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="R31" s="34"/>
+      <c r="T31" s="34"/>
+      <c r="V31" s="34"/>
+      <c r="Y31" s="35"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="92" t="s">
+        <v>112</v>
+      </c>
+      <c r="B35" s="92"/>
+      <c r="C35" s="93" t="s">
+        <v>134</v>
+      </c>
+      <c r="D35" s="94" t="s">
+        <v>135</v>
+      </c>
+      <c r="E35" s="94" t="s">
+        <v>136</v>
+      </c>
+      <c r="F35" s="94" t="s">
+        <v>136</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/タナカホーム株式会社御中_LINEOA施策提案【SIM】ver1.2.xlsx
+++ b/タナカホーム株式会社御中_LINEOA施策提案【SIM】ver1.2.xlsx
@@ -3647,27 +3647,29 @@
         <v>21</v>
       </c>
       <c r="E24" s="46">
-        <f>+IF(E19=FALSE,0,SUM(H10:H11)*0.15)</f>
+        <f>IF(E19=FALSE,0,SUM($H$10:$H$11)*0.8*0.4)</f>
       </c>
       <c r="F24" s="63">
-        <f>E24*1.01</f>
+        <f>IF(F19=FALSE,0,SUM($H$10:$H$11)*0.8*0.4)</f>
       </c>
       <c r="G24" s="63">
-        <f t="shared" si="3"/>
+        <f>IF(G19=FALSE,0,SUM($H$10:$H$11)*0.8*0.4)</f>
       </c>
       <c r="H24" s="63">
-        <f t="shared" si="3"/>
+        <f>IF(H19=FALSE,0,SUM($H$10:$H$11)*0.8*0.4)</f>
       </c>
       <c r="I24" s="63">
-        <f t="shared" si="3"/>
+        <f>IF(I19=FALSE,0,SUM($H$10:$H$11)*0.8*0.4)</f>
       </c>
       <c r="J24" s="63">
-        <f t="shared" si="3"/>
+        <f>IF(J19=FALSE,0,SUM($H$10:$H$11)*0.8*0.4)</f>
       </c>
       <c r="K24" s="11"/>
       <c r="L24" s="7"/>
-      <c r="N24" s="69" t="s">
-        <v>175</v>
+      <c r="N24" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サンクスLINE誘導＝（来場予約 月35件＋資料請求 月8件。全部フォームの想定）×遷移80%×追加40%＝月約14人。資料請求・来場予約の件数はBと同じ（来場予約した方のキャンセルを減らす効果は「来場」の数なのでSIMに出さない）</t>
+        </is>
       </c>
       <c r="O24" s="22" t="s">
         <v>44</v>
@@ -7476,7 +7478,7 @@
       <c r="L36" s="7"/>
       <c r="N36" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve">CVの件数はAと同じ（サンクスLINEで友だちになる方は資料請求・来場予約済みなので、LINE経由のCVに数えていない）</t>
+          <t xml:space="preserve">CVの件数はAと同じ（サンクスLINEの効果＝来場予約した方のキャンセルを減らす＝「来場」の数なので、SIMには出さない）</t>
         </is>
       </c>
       <c r="O36" s="17" t="s">

--- a/タナカホーム株式会社御中_LINEOA施策提案【SIM】ver1.2.xlsx
+++ b/タナカホーム株式会社御中_LINEOA施策提案【SIM】ver1.2.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tonomura-r\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE05BB34-E479-40B4-B536-863DE4397AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB21B46-FE3E-46E9-9CCF-3DD4F5FF060B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13380" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{02433765-3560-48F5-BC99-B30FC64129A4}"/>
+    <workbookView xWindow="-13380" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{02433765-3560-48F5-BC99-B30FC64129A4}"/>
   </bookViews>
   <sheets>
     <sheet name="A_サンクス有" sheetId="1" r:id="rId1"/>
     <sheet name="A_比較" sheetId="2" r:id="rId2"/>
-    <sheet name="B_サンクス無" sheetId="3" r:id="rId100"/>
-    <sheet name="B_比較" sheetId="4" r:id="rId101"/>
-    <sheet name="SIM考え方" sheetId="5" r:id="rId3"/>
+    <sheet name="B_サンクス無" sheetId="3" r:id="rId3"/>
+    <sheet name="B_比較" sheetId="4" r:id="rId4"/>
+    <sheet name="SIM考え方" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="199">
   <si>
     <t>項目</t>
     <rPh sb="0" eb="2">
@@ -1464,9 +1464,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>タナカホーム株式会社御中_LINEOA施策提案【SIM】（離脱防止＋サイトのボタン＋サンクスLINE）</t>
-  </si>
-  <si>
     <t>サイトUU 13,228／友だち417人（2026-10-15〜16 殿村さん）。CVは来場予約（資料の軸＝資料請求の時点から来場・契約まで追う）</t>
   </si>
   <si>
@@ -1504,9 +1501,6 @@
   </si>
   <si>
     <t>離脱防止＝UU×表示55%×クリック12%×追加12%（FMTの式）＝月約105人。今の来場特典のポップアップに加えて、来場前の方向けに情報で追加してもらう案内に作り直す想定</t>
-  </si>
-  <si>
-    <t>サンクスLINE誘導＝（来場予約＋資料請求）×15%（FMTの式）＝月約6人。資料請求・来場予約の完了ページからLINEへ</t>
   </si>
   <si>
     <t>サイトのLINEボタン＝UU×0.5%（FMTのP15）＝月約66人。今はサイトにLINEの導線が無いので新しく置く</t>
@@ -1569,6 +1563,24 @@
       <t>シリョウセイキュウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タナカホーム株式会社御中_LINEOA施策提案【SIM】ver1.2　A_サンクス有（離脱防止＋サイトのボタン＋サンクスLINE誘導）</t>
+  </si>
+  <si>
+    <t>サンクスLINE誘導＝（来場予約 月35件＋資料請求 月8件。全部フォームの想定）×遷移80%×追加40%＝月約14人。資料請求・来場予約の件数はBと同じ（来場予約した方のキャンセルを減らす効果は「来場」の数なのでSIMに出さない）</t>
+  </si>
+  <si>
+    <t>タナカホーム株式会社御中_LINEOA施策提案【SIM】ver1.2　B_サンクス無（離脱防止＋サイトのボタン）</t>
+  </si>
+  <si>
+    <t>B_サンクス無：サンクスLINE誘導は入れない（オプション。Aのシートを参照）</t>
+  </si>
+  <si>
+    <t>CVの件数はAと同じ（サンクスLINEの効果＝来場予約した方のキャンセルを減らす＝「来場」の数なので、SIMには出さない）</t>
+  </si>
+  <si>
+    <t>サンクスLINE誘導：入れない（オプション：初期15万・月3万〜）</t>
   </si>
 </sst>
 </file>
@@ -2495,12 +2507,45 @@
     <xf numFmtId="14" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2522,44 +2567,11 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2944,10 +2956,8 @@
       </c>
     </row>
     <row r="4" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">タナカホーム株式会社御中_LINEOA施策提案【SIM】ver1.2　A_サンクス有（離脱防止＋サイトのボタン＋サンクスLINE誘導）</t>
-        </is>
+      <c r="A4" s="56" t="s">
+        <v>193</v>
       </c>
       <c r="N4" s="55"/>
       <c r="O4" s="55"/>
@@ -3011,14 +3021,14 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="137" t="s">
+      <c r="A8" s="148" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D8" s="33">
         <v>0</v>
@@ -3037,19 +3047,19 @@
         <v>0</v>
       </c>
       <c r="N8" s="69" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O8" s="35" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="138"/>
+      <c r="A9" s="149"/>
       <c r="B9" s="19" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D9" s="33">
         <v>0</v>
@@ -3064,7 +3074,7 @@
       <c r="J9" s="29"/>
       <c r="K9" s="118"/>
       <c r="N9" s="132" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O9" s="130" t="s">
         <v>154</v>
@@ -3074,7 +3084,7 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="137" t="s">
+      <c r="A10" s="148" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="19" t="s">
@@ -3087,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="124" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H10" s="125">
         <v>35</v>
@@ -3098,11 +3108,11 @@
       <c r="J10" s="29"/>
       <c r="K10" s="118"/>
       <c r="N10" s="132" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="138"/>
+      <c r="A11" s="149"/>
       <c r="B11" s="19" t="s">
         <v>11</v>
       </c>
@@ -3113,7 +3123,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="126" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H11" s="127">
         <v>8</v>
@@ -3136,31 +3146,31 @@
       <c r="V12" s="55"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="139" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="139"/>
+      <c r="A13" s="150" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="150"/>
       <c r="C13" s="95"/>
       <c r="D13" s="13" t="s">
         <v>29</v>
       </c>
       <c r="E13" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="F13" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="F13" s="36" t="s">
+      <c r="G13" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="G13" s="36" t="s">
+      <c r="H13" s="36" t="s">
         <v>169</v>
       </c>
-      <c r="H13" s="36" t="s">
+      <c r="I13" s="36" t="s">
         <v>170</v>
       </c>
-      <c r="I13" s="36" t="s">
+      <c r="J13" s="36" t="s">
         <v>171</v>
-      </c>
-      <c r="J13" s="36" t="s">
-        <v>172</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>1</v>
@@ -3182,7 +3192,7 @@
       <c r="V13" s="23"/>
     </row>
     <row r="14" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="140" t="s">
+      <c r="A14" s="151" t="s">
         <v>32</v>
       </c>
       <c r="B14" s="20" t="s">
@@ -3191,54 +3201,68 @@
       <c r="C14" s="99"/>
       <c r="D14" s="42">
         <f>+H8</f>
+        <v>13228</v>
       </c>
       <c r="E14" s="43">
         <f>+D14</f>
+        <v>13228</v>
       </c>
       <c r="F14" s="43">
         <f t="shared" ref="F14:J14" si="0">+E14</f>
+        <v>13228</v>
       </c>
       <c r="G14" s="43">
         <f t="shared" si="0"/>
+        <v>13228</v>
       </c>
       <c r="H14" s="43">
         <f t="shared" si="0"/>
+        <v>13228</v>
       </c>
       <c r="I14" s="43">
         <f t="shared" si="0"/>
+        <v>13228</v>
       </c>
       <c r="J14" s="43">
         <f t="shared" si="0"/>
+        <v>13228</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="7"/>
     </row>
     <row r="15" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="141"/>
+      <c r="A15" s="152"/>
       <c r="B15" s="20" t="s">
         <v>35</v>
       </c>
       <c r="C15" s="99"/>
       <c r="D15" s="42">
         <f t="shared" ref="D15" si="1">+H9</f>
+        <v>0</v>
       </c>
       <c r="E15" s="43">
         <f t="shared" ref="E15:J16" si="2">+D15</f>
+        <v>0</v>
       </c>
       <c r="F15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="G15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="H15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="J15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="K15" s="11"/>
       <c r="L15" s="7"/>
@@ -3256,31 +3280,38 @@
       </c>
     </row>
     <row r="16" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="142"/>
+      <c r="A16" s="153"/>
       <c r="B16" s="20" t="s">
         <v>150</v>
       </c>
       <c r="C16" s="99"/>
       <c r="D16" s="42">
         <f>H10</f>
+        <v>35</v>
       </c>
       <c r="E16" s="43">
         <f t="shared" si="2"/>
+        <v>35</v>
       </c>
       <c r="F16" s="43">
         <f t="shared" si="2"/>
+        <v>35</v>
       </c>
       <c r="G16" s="43">
         <f t="shared" si="2"/>
+        <v>35</v>
       </c>
       <c r="H16" s="43">
         <f t="shared" si="2"/>
+        <v>35</v>
       </c>
       <c r="I16" s="43">
         <f t="shared" si="2"/>
+        <v>35</v>
       </c>
       <c r="J16" s="43">
         <f t="shared" si="2"/>
+        <v>35</v>
       </c>
       <c r="K16" s="11"/>
       <c r="L16" s="7"/>
@@ -3298,7 +3329,7 @@
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="140" t="s">
+      <c r="A17" s="151" t="s">
         <v>3</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -3343,7 +3374,7 @@
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="141"/>
+      <c r="A18" s="152"/>
       <c r="B18" s="8" t="s">
         <v>5</v>
       </c>
@@ -3407,7 +3438,7 @@
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="141"/>
+      <c r="A19" s="152"/>
       <c r="B19" s="8" t="s">
         <v>115</v>
       </c>
@@ -3461,13 +3492,14 @@
       </c>
       <c r="Y19" s="34">
         <f>+U19*2.5</f>
+        <v>37500000</v>
       </c>
       <c r="Z19" s="35">
         <v>2.5</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="141"/>
+      <c r="A20" s="152"/>
       <c r="B20" s="8" t="s">
         <v>113</v>
       </c>
@@ -3502,7 +3534,7 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="142"/>
+      <c r="A21" s="153"/>
       <c r="B21" s="8" t="s">
         <v>114</v>
       </c>
@@ -3545,7 +3577,7 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="143" t="s">
+      <c r="A22" s="154" t="s">
         <v>12</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -3576,7 +3608,7 @@
       <c r="K22" s="11"/>
       <c r="L22" s="7"/>
       <c r="N22" s="69" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O22" s="17" t="s">
         <v>41</v>
@@ -3591,7 +3623,7 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="141"/>
+      <c r="A23" s="152"/>
       <c r="B23" s="6" t="s">
         <v>5</v>
       </c>
@@ -3601,26 +3633,32 @@
       </c>
       <c r="E23" s="46">
         <f>IF(E18=FALSE,0,E15*$P$18*0.08*0.08+(E14-E15)*$P$19*0.12*0.12)</f>
+        <v>104.76576</v>
       </c>
       <c r="F23" s="46">
         <f>IF(F18=FALSE,0,F15*$P$18*0.08*0.08+(F14-F15)*$P$19*0.12*0.12)</f>
+        <v>104.76576</v>
       </c>
       <c r="G23" s="63">
-        <f t="shared" ref="G23:J24" si="3">F23*1.01</f>
+        <f t="shared" ref="G23:J23" si="3">F23*1.01</f>
+        <v>105.81341760000001</v>
       </c>
       <c r="H23" s="63">
         <f t="shared" si="3"/>
+        <v>106.871551776</v>
       </c>
       <c r="I23" s="63">
         <f t="shared" si="3"/>
+        <v>107.94026729376</v>
       </c>
       <c r="J23" s="63">
         <f t="shared" si="3"/>
+        <v>109.01966996669761</v>
       </c>
       <c r="K23" s="11"/>
       <c r="L23" s="7"/>
       <c r="N23" s="69" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O23" s="17" t="s">
         <v>42</v>
@@ -3638,7 +3676,7 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="141"/>
+      <c r="A24" s="152"/>
       <c r="B24" s="6" t="s">
         <v>115</v>
       </c>
@@ -3647,29 +3685,33 @@
         <v>21</v>
       </c>
       <c r="E24" s="46">
-        <f>IF(E19=FALSE,0,SUM($H$10:$H$11)*0.8*0.4)</f>
+        <f t="shared" ref="E24:J24" si="4">IF(E19=FALSE,0,SUM($H$10:$H$11)*0.8*0.4)</f>
+        <v>13.76</v>
       </c>
       <c r="F24" s="63">
-        <f>IF(F19=FALSE,0,SUM($H$10:$H$11)*0.8*0.4)</f>
+        <f t="shared" si="4"/>
+        <v>13.76</v>
       </c>
       <c r="G24" s="63">
-        <f>IF(G19=FALSE,0,SUM($H$10:$H$11)*0.8*0.4)</f>
+        <f t="shared" si="4"/>
+        <v>13.76</v>
       </c>
       <c r="H24" s="63">
-        <f>IF(H19=FALSE,0,SUM($H$10:$H$11)*0.8*0.4)</f>
+        <f t="shared" si="4"/>
+        <v>13.76</v>
       </c>
       <c r="I24" s="63">
-        <f>IF(I19=FALSE,0,SUM($H$10:$H$11)*0.8*0.4)</f>
+        <f t="shared" si="4"/>
+        <v>13.76</v>
       </c>
       <c r="J24" s="63">
-        <f>IF(J19=FALSE,0,SUM($H$10:$H$11)*0.8*0.4)</f>
+        <f t="shared" si="4"/>
+        <v>13.76</v>
       </c>
       <c r="K24" s="11"/>
       <c r="L24" s="7"/>
-      <c r="N24" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サンクスLINE誘導＝（来場予約 月35件＋資料請求 月8件。全部フォームの想定）×遷移80%×追加40%＝月約14人。資料請求・来場予約の件数はBと同じ（来場予約した方のキャンセルを減らす効果は「来場」の数なのでSIMに出さない）</t>
-        </is>
+      <c r="N24" s="69" t="s">
+        <v>194</v>
       </c>
       <c r="O24" s="22" t="s">
         <v>44</v>
@@ -3687,7 +3729,7 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="142"/>
+      <c r="A25" s="153"/>
       <c r="B25" s="6" t="s">
         <v>69</v>
       </c>
@@ -3697,21 +3739,27 @@
       </c>
       <c r="E25" s="46">
         <f>+IF(E20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
+        <v>0</v>
       </c>
       <c r="F25" s="46">
-        <f t="shared" ref="F25:J25" si="4">+IF(F20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
+        <f t="shared" ref="F25:J25" si="5">+IF(F20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
+        <v>0</v>
       </c>
       <c r="G25" s="46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="H25" s="46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="I25" s="46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="J25" s="46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="K25" s="11"/>
       <c r="L25" s="7"/>
@@ -3729,36 +3777,42 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="144" t="s">
+      <c r="A26" s="138" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="145"/>
+      <c r="B26" s="139"/>
       <c r="C26" s="23"/>
       <c r="D26" s="44" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="46">
         <f>+SUM(E22:E25)+$H$9*$P$16+($H$8-$H$9)*$P$15+IF(P9=FALSE,0,$K$8*0.15*0.08)</f>
+        <v>184.66576000000001</v>
       </c>
       <c r="F26" s="46">
-        <f t="shared" ref="F26:J26" si="5">+SUM(F22:F25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
+        <f t="shared" ref="F26:J26" si="6">+SUM(F22:F25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
+        <v>184.66576000000001</v>
       </c>
       <c r="G26" s="46">
         <f>+SUM(G22:G25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
+        <v>185.71341760000001</v>
       </c>
       <c r="H26" s="46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
+        <v>186.77155177600002</v>
       </c>
       <c r="I26" s="46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
+        <v>187.84026729376001</v>
       </c>
       <c r="J26" s="46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
+        <v>188.9196699666976</v>
       </c>
       <c r="K26" s="11"/>
       <c r="L26" s="7"/>
       <c r="N26" s="72" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="O26" s="17" t="s">
         <v>41</v>
@@ -3773,10 +3827,10 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="144" t="s">
+      <c r="A27" s="138" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="145"/>
+      <c r="B27" s="139"/>
       <c r="C27" s="23"/>
       <c r="D27" s="107">
         <v>0.28000000000000003</v>
@@ -3786,23 +3840,28 @@
       </c>
       <c r="F27" s="47">
         <f>ROUND(E27*1.02,3)</f>
+        <v>0.28599999999999998</v>
       </c>
       <c r="G27" s="47">
         <f>ROUND(F27*1.02,3)</f>
+        <v>0.29199999999999998</v>
       </c>
       <c r="H27" s="47">
         <f>ROUND(G27*1.02,3)</f>
+        <v>0.29799999999999999</v>
       </c>
       <c r="I27" s="47">
         <f>ROUND(H27*1.02,3)</f>
+        <v>0.30399999999999999</v>
       </c>
       <c r="J27" s="47">
         <f>ROUND(I27*1.02,3)</f>
+        <v>0.31</v>
       </c>
       <c r="K27" s="11"/>
       <c r="L27" s="7"/>
       <c r="N27" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O27" s="17" t="s">
         <v>42</v>
@@ -3820,31 +3879,37 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="146" t="s">
+      <c r="A28" s="155" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="147"/>
+      <c r="B28" s="156"/>
       <c r="C28" s="101"/>
       <c r="D28" s="106">
         <v>417</v>
       </c>
       <c r="E28" s="49">
         <f>+D28+E26</f>
+        <v>601.66575999999998</v>
       </c>
       <c r="F28" s="49">
-        <f t="shared" ref="F28:J28" si="6">+E28+F26</f>
+        <f t="shared" ref="F28:J28" si="7">+E28+F26</f>
+        <v>786.33151999999995</v>
       </c>
       <c r="G28" s="49">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
+        <v>972.04493759999991</v>
       </c>
       <c r="H28" s="49">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
+        <v>1158.8164893759999</v>
       </c>
       <c r="I28" s="49">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
+        <v>1346.6567566697599</v>
       </c>
       <c r="J28" s="49">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
+        <v>1535.5764266364577</v>
       </c>
       <c r="K28" s="12"/>
       <c r="L28" s="7"/>
@@ -3864,31 +3929,38 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="148" t="s">
+      <c r="A29" s="144" t="s">
         <v>14</v>
       </c>
-      <c r="B29" s="149"/>
+      <c r="B29" s="145"/>
       <c r="C29" s="102"/>
       <c r="D29" s="108">
         <f>+D28*(1-D27)</f>
+        <v>300.24</v>
       </c>
       <c r="E29" s="50">
         <f>+E28*(1-E27)</f>
+        <v>433.19934719999998</v>
       </c>
       <c r="F29" s="50">
-        <f t="shared" ref="F29:J29" si="7">+F28*(1-F27)</f>
+        <f t="shared" ref="F29:J29" si="8">+F28*(1-F27)</f>
+        <v>561.44070527999997</v>
       </c>
       <c r="G29" s="50">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>688.20781582079985</v>
       </c>
       <c r="H29" s="50">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>813.48917554195191</v>
       </c>
       <c r="I29" s="50">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>937.27310264215282</v>
       </c>
       <c r="J29" s="50">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>1059.5477343791556</v>
       </c>
       <c r="K29" s="12"/>
       <c r="L29" s="7"/>
@@ -3902,10 +3974,10 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="135" t="s">
+      <c r="A30" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="B30" s="136"/>
+      <c r="B30" s="143"/>
       <c r="C30" s="30"/>
       <c r="D30" s="48">
         <v>0</v>
@@ -3931,7 +4003,7 @@
       <c r="K30" s="11"/>
       <c r="L30" s="7"/>
       <c r="N30" s="69" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="O30" s="17" t="s">
         <v>120</v>
@@ -3944,31 +4016,38 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="144" t="s">
+      <c r="A31" s="138" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="145"/>
+      <c r="B31" s="139"/>
       <c r="C31" s="23"/>
       <c r="D31" s="108">
         <f>+D30*D29*0.41*0.07</f>
+        <v>0</v>
       </c>
       <c r="E31" s="63">
         <f>+E29*E30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>136.72062507593324</v>
       </c>
       <c r="F31" s="63">
         <f>+F29*F30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>177.19445946790751</v>
       </c>
       <c r="G31" s="63">
         <f>+G29*G30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>217.20301142956683</v>
       </c>
       <c r="H31" s="63">
         <f>+H29*H30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>205.39412035863981</v>
       </c>
       <c r="I31" s="63">
         <f>+I29*I30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>236.64775173529065</v>
       </c>
       <c r="J31" s="63">
         <f>+J29*J30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>267.52030810466937</v>
       </c>
       <c r="K31" s="11"/>
       <c r="L31" s="7"/>
@@ -3979,10 +4058,10 @@
       <c r="Z31" s="35"/>
     </row>
     <row r="32" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="135" t="s">
+      <c r="A32" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="136"/>
+      <c r="B32" s="143"/>
       <c r="C32" s="30"/>
       <c r="D32" s="48">
         <v>0</v>
@@ -4008,7 +4087,7 @@
       <c r="K32" s="11"/>
       <c r="L32" s="7"/>
       <c r="N32" s="69" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="O32" s="17" t="s">
         <v>123</v>
@@ -4018,6 +4097,7 @@
       </c>
       <c r="Q32" s="73">
         <f>+IF(P32=TRUE,1.1,0.95)</f>
+        <v>1.1000000000000001</v>
       </c>
       <c r="S32" s="34"/>
       <c r="U32" s="34"/>
@@ -4025,31 +4105,37 @@
       <c r="Z32" s="35"/>
     </row>
     <row r="33" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="144" t="s">
+      <c r="A33" s="138" t="s">
         <v>31</v>
       </c>
-      <c r="B33" s="145"/>
+      <c r="B33" s="139"/>
       <c r="C33" s="23"/>
       <c r="D33" s="44">
         <v>0</v>
       </c>
       <c r="E33" s="63">
-        <f t="shared" ref="E33:J33" si="8">+E26*E32*$P$26*$P$27*$P$36</f>
+        <f t="shared" ref="E33:J33" si="9">+E26*E32*$P$26*$P$27*$P$36</f>
+        <v>101.57276980092001</v>
       </c>
       <c r="F33" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>101.57276980092001</v>
       </c>
       <c r="G33" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>102.14901893467922</v>
       </c>
       <c r="H33" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>102.73103055977603</v>
       </c>
       <c r="I33" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>103.31886230112377</v>
       </c>
       <c r="J33" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>103.912572359885</v>
       </c>
       <c r="K33" s="11"/>
       <c r="L33" s="7"/>
@@ -4060,35 +4146,43 @@
         <v>1</v>
       </c>
       <c r="Q33" s="73">
-        <f t="shared" ref="Q33:Q35" si="9">+IF(P33=TRUE,1.1,0.95)</f>
+        <f t="shared" ref="Q33:Q35" si="10">+IF(P33=TRUE,1.1,0.95)</f>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="148" t="s">
+      <c r="A34" s="144" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="149"/>
+      <c r="B34" s="145"/>
       <c r="C34" s="102"/>
       <c r="D34" s="108">
         <f>+D29*D30</f>
+        <v>0</v>
       </c>
       <c r="E34" s="46">
         <f>+E29*E30*$P$24+E26*E32</f>
+        <v>2309.56671104</v>
       </c>
       <c r="F34" s="46">
         <f>+F29*F30*$P$24+F26*F32</f>
+        <v>2719.9390568959998</v>
       </c>
       <c r="G34" s="46">
         <f>+G29*G30*$P$24+G26*G32</f>
+        <v>3130.8320986265599</v>
       </c>
       <c r="H34" s="46">
         <f>+H29*H30*$P$24*$Q$24+H26*H32</f>
+        <v>3016.3900482673971</v>
       </c>
       <c r="I34" s="46">
         <f>+I29*I30*$P$24*$Q$24+I26*I32</f>
+        <v>3338.6204792327117</v>
       </c>
       <c r="J34" s="46">
         <f>+J29*J30*$P$24*$Q$24+J26*J32</f>
+        <v>3657.0405498441269</v>
       </c>
       <c r="K34" s="11"/>
       <c r="L34" s="7"/>
@@ -4099,35 +4193,43 @@
         <v>1</v>
       </c>
       <c r="Q34" s="73">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="148" t="s">
+      <c r="A35" s="144" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="149"/>
+      <c r="B35" s="145"/>
       <c r="C35" s="102"/>
       <c r="D35" s="109">
         <f>+D31*1.02</f>
+        <v>0</v>
       </c>
       <c r="E35" s="50">
         <f>+E31+E33+1.05*(E31+E33)</f>
+        <v>488.50145949754915</v>
       </c>
       <c r="F35" s="50">
-        <f t="shared" ref="F35:J35" si="10">+F31+F33+1.05*(F31+F33)</f>
+        <f t="shared" ref="F35:J35" si="11">+F31+F33+1.05*(F31+F33)</f>
+        <v>571.47282000109635</v>
       </c>
       <c r="G35" s="50">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
+        <v>654.67166224670439</v>
       </c>
       <c r="H35" s="50">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
+        <v>631.65655938275245</v>
       </c>
       <c r="I35" s="50">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
+        <v>696.9315587746496</v>
       </c>
       <c r="J35" s="50">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
+        <v>761.43740495233646</v>
       </c>
       <c r="K35" s="11"/>
       <c r="L35" s="7"/>
@@ -4138,94 +4240,101 @@
         <v>0</v>
       </c>
       <c r="Q35" s="73">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
+        <v>0.95</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="150" t="s">
+      <c r="A36" s="146" t="s">
         <v>6</v>
       </c>
-      <c r="B36" s="6">
+      <c r="B36" s="6" t="str">
         <f>+C8</f>
+        <v>資料請求</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="11">
         <v>0</v>
       </c>
-      <c r="E36" s="156">
+      <c r="E36" s="135">
         <v>4</v>
       </c>
-      <c r="F36" s="156">
+      <c r="F36" s="135">
         <v>6</v>
       </c>
-      <c r="G36" s="156">
+      <c r="G36" s="135">
         <v>6</v>
       </c>
-      <c r="H36" s="156">
+      <c r="H36" s="135">
         <v>8</v>
       </c>
-      <c r="I36" s="156">
+      <c r="I36" s="135">
         <v>9</v>
       </c>
-      <c r="J36" s="156">
+      <c r="J36" s="135">
         <v>11</v>
       </c>
       <c r="K36" s="115">
         <f>SUM(E36:J36)</f>
+        <v>44</v>
       </c>
       <c r="L36" s="7"/>
       <c r="N36" s="69" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="O36" s="17" t="s">
         <v>124</v>
       </c>
       <c r="P36" s="74">
         <f>1*(Q32*Q33*Q34*Q35)</f>
+        <v>1.2644500000000003</v>
       </c>
       <c r="Q36" s="73"/>
     </row>
     <row r="37" spans="1:17" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="151"/>
-      <c r="B37" s="6">
+      <c r="A37" s="147"/>
+      <c r="B37" s="6" t="str">
         <f>+C9</f>
+        <v>来場予約</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="11">
         <v>0</v>
       </c>
-      <c r="E37" s="156">
+      <c r="E37" s="135">
         <v>2</v>
       </c>
-      <c r="F37" s="156">
+      <c r="F37" s="135">
         <v>3</v>
       </c>
-      <c r="G37" s="156">
+      <c r="G37" s="135">
         <v>4</v>
       </c>
-      <c r="H37" s="156">
+      <c r="H37" s="135">
         <v>6</v>
       </c>
-      <c r="I37" s="156">
+      <c r="I37" s="135">
         <v>7</v>
       </c>
-      <c r="J37" s="156">
+      <c r="J37" s="135">
         <v>8</v>
       </c>
       <c r="K37" s="115">
         <f>SUM(E37:J37)</f>
+        <v>30</v>
       </c>
       <c r="L37" s="7"/>
       <c r="N37" s="69" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="150" t="s">
+      <c r="A38" s="146" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="6">
+      <c r="B38" s="6" t="str">
         <f>+C10</f>
+        <v>-</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="11">
@@ -4251,6 +4360,7 @@
       </c>
       <c r="K38" s="115">
         <f>SUM(E38:J38)</f>
+        <v>0</v>
       </c>
       <c r="L38" s="7"/>
       <c r="N38" s="69" t="s">
@@ -4261,9 +4371,10 @@
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="151"/>
-      <c r="B39" s="6">
+      <c r="A39" s="147"/>
+      <c r="B39" s="6" t="str">
         <f>+C11</f>
+        <v>-</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="11">
@@ -4289,6 +4400,7 @@
       </c>
       <c r="K39" s="115">
         <f>SUM(E39:J39)</f>
+        <v>0</v>
       </c>
       <c r="L39" s="7"/>
       <c r="N39" s="69" t="s">
@@ -4299,34 +4411,42 @@
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="152" t="s">
+      <c r="A40" s="140" t="s">
         <v>53</v>
       </c>
-      <c r="B40" s="153"/>
+      <c r="B40" s="141"/>
       <c r="C40" s="97"/>
       <c r="D40" s="11">
         <f>SUM(D36:D39)</f>
+        <v>0</v>
       </c>
       <c r="E40" s="10">
         <f>SUM(E36:E39)</f>
+        <v>6</v>
       </c>
       <c r="F40" s="10">
-        <f t="shared" ref="F40:J40" si="11">SUM(F36:F39)</f>
+        <f t="shared" ref="F40:J40" si="12">SUM(F36:F39)</f>
+        <v>9</v>
       </c>
       <c r="G40" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
+        <v>10</v>
       </c>
       <c r="H40" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
+        <v>14</v>
       </c>
       <c r="I40" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
+        <v>16</v>
       </c>
       <c r="J40" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
+        <v>19</v>
       </c>
       <c r="K40" s="115">
         <f>SUM(E40:J40)</f>
+        <v>74</v>
       </c>
       <c r="L40" s="7"/>
       <c r="O40" s="17"/>
@@ -4336,25 +4456,32 @@
         <v>67</v>
       </c>
       <c r="D41" s="18">
-        <f t="shared" ref="D41" si="12">+IFERROR(D40/D35,0)</f>
+        <f t="shared" ref="D41" si="13">+IFERROR(D40/D35,0)</f>
+        <v>0</v>
       </c>
       <c r="E41" s="18">
         <f>IFERROR(E40/E35,0)</f>
+        <v>1.2282460744685047E-2</v>
       </c>
       <c r="F41" s="18">
-        <f t="shared" ref="F41:J41" si="13">IFERROR(F40/F35,0)</f>
+        <f t="shared" ref="F41:J41" si="14">IFERROR(F40/F35,0)</f>
+        <v>1.5748780493152297E-2</v>
       </c>
       <c r="G41" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
+        <v>1.5274832525486084E-2</v>
       </c>
       <c r="H41" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
+        <v>2.2163943035247886E-2</v>
       </c>
       <c r="I41" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
+        <v>2.2957777989177763E-2</v>
       </c>
       <c r="J41" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
+        <v>2.4952806201042014E-2</v>
       </c>
       <c r="N41" s="69" t="s">
         <v>117</v>
@@ -4382,245 +4509,297 @@
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="144" t="s">
+      <c r="A44" s="138" t="s">
         <v>27</v>
       </c>
-      <c r="B44" s="145"/>
+      <c r="B44" s="139"/>
       <c r="C44" s="103"/>
       <c r="D44" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E44" s="31">
         <f>+E75*E76</f>
+        <v>0</v>
       </c>
       <c r="F44" s="31">
-        <f t="shared" ref="F44:J44" si="14">+F75*F76</f>
+        <f t="shared" ref="F44:J44" si="15">+F75*F76</f>
+        <v>0</v>
       </c>
       <c r="G44" s="31">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="H44" s="31">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="I44" s="31">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="J44" s="31">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="K44" s="11"/>
       <c r="L44" s="7"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="144" t="s">
+      <c r="A45" s="138" t="s">
         <v>129</v>
       </c>
-      <c r="B45" s="145"/>
+      <c r="B45" s="139"/>
       <c r="C45" s="104">
         <f>+SUM(C65:C72)</f>
+        <v>0</v>
       </c>
       <c r="D45" s="80">
         <f>+SUM(D65:D72)</f>
+        <v>265000</v>
       </c>
       <c r="E45" s="27">
         <f>SUM(E65:E69)+SUM(E71:E72)</f>
+        <v>265000</v>
       </c>
       <c r="F45" s="27">
-        <f t="shared" ref="F45:J45" si="15">SUM(F65:F69)+SUM(F71:F72)</f>
+        <f t="shared" ref="F45:J45" si="16">SUM(F65:F69)+SUM(F71:F72)</f>
+        <v>265000</v>
       </c>
       <c r="G45" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
+        <v>265000</v>
       </c>
       <c r="H45" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
+        <v>265000</v>
       </c>
       <c r="I45" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
+        <v>265000</v>
       </c>
       <c r="J45" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
+        <v>265000</v>
       </c>
       <c r="K45" s="11"/>
       <c r="L45" s="7"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="144" t="s">
+      <c r="A46" s="138" t="s">
         <v>17</v>
       </c>
-      <c r="B46" s="145"/>
+      <c r="B46" s="139"/>
       <c r="C46" s="103"/>
       <c r="D46" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E46" s="28">
-        <f t="shared" ref="E46:J46" si="16">SUM(E65:E67)/(E28-D28)</f>
+        <f t="shared" ref="E46:J46" si="17">SUM(E65:E67)/(E28-D28)</f>
+        <v>324.91134252500308</v>
       </c>
       <c r="F46" s="28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
+        <v>324.91134252500308</v>
       </c>
       <c r="G46" s="28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
+        <v>323.0784332946335</v>
       </c>
       <c r="H46" s="28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
+        <v>321.24806711441556</v>
       </c>
       <c r="I46" s="28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
+        <v>319.42032911488081</v>
       </c>
       <c r="J46" s="28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
+        <v>317.59530392243778</v>
       </c>
       <c r="K46" s="11"/>
       <c r="L46" s="7"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="144" t="s">
+      <c r="A47" s="138" t="s">
         <v>18</v>
       </c>
-      <c r="B47" s="145"/>
+      <c r="B47" s="139"/>
       <c r="C47" s="103"/>
       <c r="D47" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E47" s="28">
-        <f t="shared" ref="E47:I47" si="17">+E51/E35</f>
+        <f t="shared" ref="E47:I47" si="18">+E51/E35</f>
+        <v>542.47534955692288</v>
       </c>
       <c r="F47" s="28">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
+        <v>463.7140922983732</v>
       </c>
       <c r="G47" s="28">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
+        <v>404.78306192538122</v>
       </c>
       <c r="H47" s="28">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
+        <v>419.53177888147786</v>
       </c>
       <c r="I47" s="28">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
+        <v>380.23819794575672</v>
       </c>
       <c r="J47" s="28">
         <f>+J51/J35</f>
+        <v>348.02598122505964</v>
       </c>
       <c r="K47" s="11"/>
       <c r="L47" s="7"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="144" t="s">
+      <c r="A48" s="138" t="s">
         <v>20</v>
       </c>
-      <c r="B48" s="145"/>
+      <c r="B48" s="139"/>
       <c r="C48" s="103"/>
       <c r="D48" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E48" s="32">
         <f>IFERROR(E40/E35,0)</f>
+        <v>1.2282460744685047E-2</v>
       </c>
       <c r="F48" s="32">
-        <f t="shared" ref="F48:J48" si="18">IFERROR(F40/F35,0)</f>
+        <f t="shared" ref="F48:J48" si="19">IFERROR(F40/F35,0)</f>
+        <v>1.5748780493152297E-2</v>
       </c>
       <c r="G48" s="32">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
+        <v>1.5274832525486084E-2</v>
       </c>
       <c r="H48" s="32">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
+        <v>2.2163943035247886E-2</v>
       </c>
       <c r="I48" s="32">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
+        <v>2.2957777989177763E-2</v>
       </c>
       <c r="J48" s="32">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
+        <v>2.4952806201042014E-2</v>
       </c>
       <c r="K48" s="11"/>
       <c r="L48" s="7"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="152" t="s">
+      <c r="A49" s="140" t="s">
         <v>19</v>
       </c>
-      <c r="B49" s="153"/>
+      <c r="B49" s="141"/>
       <c r="C49" s="105"/>
       <c r="D49" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E49" s="28">
         <f>IFERROR(E51/E40,0)</f>
+        <v>44166.666666666664</v>
       </c>
       <c r="F49" s="28">
-        <f t="shared" ref="F49:J49" si="19">IFERROR(F51/F40,0)</f>
+        <f t="shared" ref="F49:J49" si="20">IFERROR(F51/F40,0)</f>
+        <v>29444.444444444445</v>
       </c>
       <c r="G49" s="28">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
+        <v>26500</v>
       </c>
       <c r="H49" s="28">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
+        <v>18928.571428571428</v>
       </c>
       <c r="I49" s="28">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
+        <v>16562.5</v>
       </c>
       <c r="J49" s="28">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
+        <v>13947.368421052632</v>
       </c>
       <c r="K49" s="11"/>
       <c r="L49" s="7"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="152" t="s">
+      <c r="A50" s="140" t="s">
         <v>116</v>
       </c>
-      <c r="B50" s="153"/>
+      <c r="B50" s="141"/>
       <c r="C50" s="105"/>
       <c r="D50" s="64" t="s">
         <v>22</v>
       </c>
       <c r="E50" s="65">
         <f>+E36*$D$8+E38*$D$10</f>
+        <v>0</v>
       </c>
       <c r="F50" s="65">
-        <f t="shared" ref="F50:J50" si="20">+F36*$D$8+F38*$D$10</f>
+        <f t="shared" ref="F50:J50" si="21">+F36*$D$8+F38*$D$10</f>
+        <v>0</v>
       </c>
       <c r="G50" s="65">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="H50" s="65">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="I50" s="65">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="J50" s="65">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="K50" s="11"/>
       <c r="L50" s="7"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="154" t="s">
+      <c r="A51" s="136" t="s">
         <v>70</v>
       </c>
-      <c r="B51" s="155"/>
+      <c r="B51" s="137"/>
       <c r="C51" s="110">
         <f>+C45</f>
+        <v>0</v>
       </c>
       <c r="D51" s="40">
         <f>+D45</f>
+        <v>265000</v>
       </c>
       <c r="E51" s="40">
         <f>SUM(E45,E50)+E44</f>
+        <v>265000</v>
       </c>
       <c r="F51" s="40">
-        <f t="shared" ref="F51:I51" si="21">SUM(F45,F50)+F44</f>
+        <f t="shared" ref="F51:I51" si="22">SUM(F45,F50)+F44</f>
+        <v>265000</v>
       </c>
       <c r="G51" s="40">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
+        <v>265000</v>
       </c>
       <c r="H51" s="40">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
+        <v>265000</v>
       </c>
       <c r="I51" s="40">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
+        <v>265000</v>
       </c>
       <c r="J51" s="40">
         <f>SUM(J45,J50)+J44</f>
+        <v>265000</v>
       </c>
       <c r="K51" s="11"/>
       <c r="L51" s="7"/>
@@ -4643,188 +4822,226 @@
       </c>
     </row>
     <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="144" t="s">
+      <c r="A54" s="138" t="s">
         <v>27</v>
       </c>
-      <c r="B54" s="145"/>
+      <c r="B54" s="139"/>
       <c r="C54" s="96"/>
       <c r="D54" s="28">
         <f>+D75*D76</f>
+        <v>0</v>
       </c>
       <c r="E54" s="28">
-        <f t="shared" ref="E54:J54" si="22">+E75*E76</f>
+        <f t="shared" ref="E54:J54" si="23">+E75*E76</f>
+        <v>0</v>
       </c>
       <c r="F54" s="28">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="G54" s="28">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="H54" s="28">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="I54" s="28">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="J54" s="28">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="K54" s="11"/>
       <c r="L54" s="7"/>
     </row>
     <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="144" t="s">
+      <c r="A55" s="138" t="s">
         <v>129</v>
       </c>
-      <c r="B55" s="145"/>
+      <c r="B55" s="139"/>
       <c r="C55" s="96"/>
       <c r="D55" s="27">
         <f>+SUM(D65:D72)</f>
+        <v>265000</v>
       </c>
       <c r="E55" s="27">
         <f>SUM(E65:E72)+E54</f>
+        <v>265000</v>
       </c>
       <c r="F55" s="27">
-        <f t="shared" ref="F55:J55" si="23">SUM(F65:F72)+F54</f>
+        <f t="shared" ref="F55:J55" si="24">SUM(F65:F72)+F54</f>
+        <v>265000</v>
       </c>
       <c r="G55" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
+        <v>265000</v>
       </c>
       <c r="H55" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
+        <v>265000</v>
       </c>
       <c r="I55" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
+        <v>265000</v>
       </c>
       <c r="J55" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
+        <v>265000</v>
       </c>
       <c r="K55" s="11"/>
       <c r="L55" s="7"/>
     </row>
     <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="144" t="s">
+      <c r="A56" s="138" t="s">
         <v>17</v>
       </c>
-      <c r="B56" s="145"/>
+      <c r="B56" s="139"/>
       <c r="C56" s="96"/>
       <c r="D56" s="39" t="s">
         <v>22</v>
       </c>
       <c r="E56" s="28">
-        <f t="shared" ref="E56:J56" si="24">SUM(E65:E67)/(E28-D28)</f>
+        <f t="shared" ref="E56:J56" si="25">SUM(E65:E67)/(E28-D28)</f>
+        <v>324.91134252500308</v>
       </c>
       <c r="F56" s="28">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
+        <v>324.91134252500308</v>
       </c>
       <c r="G56" s="28">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
+        <v>323.0784332946335</v>
       </c>
       <c r="H56" s="28">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
+        <v>321.24806711441556</v>
       </c>
       <c r="I56" s="28">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
+        <v>319.42032911488081</v>
       </c>
       <c r="J56" s="28">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
+        <v>317.59530392243778</v>
       </c>
       <c r="K56" s="11"/>
       <c r="L56" s="7"/>
     </row>
     <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="144" t="s">
+      <c r="A57" s="138" t="s">
         <v>18</v>
       </c>
-      <c r="B57" s="145"/>
+      <c r="B57" s="139"/>
       <c r="C57" s="96"/>
       <c r="D57" s="39" t="s">
         <v>22</v>
       </c>
       <c r="E57" s="28">
         <f>+E61/E35</f>
+        <v>542.47534955692288</v>
       </c>
       <c r="F57" s="28">
-        <f t="shared" ref="F57:J57" si="25">+F61/F35</f>
+        <f t="shared" ref="F57:J57" si="26">+F61/F35</f>
+        <v>463.7140922983732</v>
       </c>
       <c r="G57" s="28">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
+        <v>404.78306192538122</v>
       </c>
       <c r="H57" s="28">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
+        <v>419.53177888147786</v>
       </c>
       <c r="I57" s="28">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
+        <v>380.23819794575672</v>
       </c>
       <c r="J57" s="28">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
+        <v>348.02598122505964</v>
       </c>
       <c r="K57" s="11"/>
       <c r="L57" s="7"/>
     </row>
     <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="144" t="s">
+      <c r="A58" s="138" t="s">
         <v>20</v>
       </c>
-      <c r="B58" s="145"/>
+      <c r="B58" s="139"/>
       <c r="C58" s="96"/>
       <c r="D58" s="39" t="s">
         <v>22</v>
       </c>
       <c r="E58" s="32">
-        <f t="shared" ref="E58:J58" si="26">+IFERROR(E36/E35,0)</f>
+        <f t="shared" ref="E58:J58" si="27">+IFERROR(E36/E35,0)</f>
+        <v>8.1883071631233643E-3</v>
       </c>
       <c r="F58" s="32">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
+        <v>1.0499186995434865E-2</v>
       </c>
       <c r="G58" s="32">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
+        <v>9.1648995152916503E-3</v>
       </c>
       <c r="H58" s="32">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
+        <v>1.2665110305855936E-2</v>
       </c>
       <c r="I58" s="32">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
+        <v>1.2913750118912493E-2</v>
       </c>
       <c r="J58" s="32">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
+        <v>1.4446361484813798E-2</v>
       </c>
       <c r="K58" s="11"/>
       <c r="L58" s="7"/>
     </row>
     <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="152" t="s">
+      <c r="A59" s="140" t="s">
         <v>19</v>
       </c>
-      <c r="B59" s="153"/>
+      <c r="B59" s="141"/>
       <c r="C59" s="97"/>
       <c r="D59" s="28"/>
       <c r="E59" s="28">
-        <f t="shared" ref="E59:J59" si="27">+IFERROR(E55/E36,0)</f>
+        <f t="shared" ref="E59:J59" si="28">+IFERROR(E55/E36,0)</f>
+        <v>66250</v>
       </c>
       <c r="F59" s="28">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
+        <v>44166.666666666664</v>
       </c>
       <c r="G59" s="28">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
+        <v>44166.666666666664</v>
       </c>
       <c r="H59" s="28">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
+        <v>33125</v>
       </c>
       <c r="I59" s="28">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
+        <v>29444.444444444445</v>
       </c>
       <c r="J59" s="28">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
+        <v>24090.909090909092</v>
       </c>
       <c r="K59" s="11"/>
       <c r="L59" s="7"/>
     </row>
     <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="152" t="s">
+      <c r="A60" s="140" t="s">
         <v>116</v>
       </c>
-      <c r="B60" s="153"/>
+      <c r="B60" s="141"/>
       <c r="C60" s="97"/>
       <c r="D60" s="28"/>
       <c r="E60" s="28"/>
@@ -4837,31 +5054,38 @@
       <c r="L60" s="7"/>
     </row>
     <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="154" t="s">
+      <c r="A61" s="136" t="s">
         <v>70</v>
       </c>
-      <c r="B61" s="155"/>
+      <c r="B61" s="137"/>
       <c r="C61" s="98"/>
       <c r="D61" s="40">
         <f>+D55</f>
+        <v>265000</v>
       </c>
       <c r="E61" s="40">
         <f>+SUM(E65:E72)+E54</f>
+        <v>265000</v>
       </c>
       <c r="F61" s="40">
-        <f t="shared" ref="F61:J61" si="28">+SUM(F65:F72)+F54</f>
+        <f t="shared" ref="F61:J61" si="29">+SUM(F65:F72)+F54</f>
+        <v>265000</v>
       </c>
       <c r="G61" s="40">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
+        <v>265000</v>
       </c>
       <c r="H61" s="40">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
+        <v>265000</v>
       </c>
       <c r="I61" s="40">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
+        <v>265000</v>
       </c>
       <c r="J61" s="40">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
+        <v>265000</v>
       </c>
       <c r="K61" s="11"/>
       <c r="L61" s="7"/>
@@ -4907,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="N65" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -4942,12 +5166,12 @@
         <v>30000</v>
       </c>
       <c r="N66" s="69" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C67" s="90">
         <v>0</v>
@@ -4974,7 +5198,7 @@
         <v>30000</v>
       </c>
       <c r="N67" s="69" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -4989,25 +5213,31 @@
         <v>0</v>
       </c>
       <c r="E68" s="28">
-        <f t="shared" ref="E68:J68" si="29">IF(E34&lt;5000,5000,15000)</f>
+        <f t="shared" ref="E68:J68" si="30">IF(E34&lt;5000,5000,15000)</f>
+        <v>5000</v>
       </c>
       <c r="F68" s="28">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
+        <v>5000</v>
       </c>
       <c r="G68" s="28">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
+        <v>5000</v>
       </c>
       <c r="H68" s="28">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
+        <v>5000</v>
       </c>
       <c r="I68" s="28">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
+        <v>5000</v>
       </c>
       <c r="J68" s="28">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
+        <v>5000</v>
       </c>
       <c r="N68" s="69" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="O68" s="17" t="s">
         <v>128</v>
@@ -5019,7 +5249,7 @@
     <row r="69" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="15"/>
       <c r="B69" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C69" s="90">
         <v>0</v>
@@ -5046,7 +5276,7 @@
         <v>200000</v>
       </c>
       <c r="N69" s="69" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="O69" s="5" t="s">
         <v>52</v>
@@ -5158,24 +5388,31 @@
       </c>
       <c r="D73" s="114">
         <f>SUM(D65:D72)</f>
+        <v>265000</v>
       </c>
       <c r="E73" s="114">
-        <f t="shared" ref="E73:J73" si="30">SUM(E65:E72)+E54</f>
+        <f t="shared" ref="E73:J73" si="31">SUM(E65:E72)+E54</f>
+        <v>265000</v>
       </c>
       <c r="F73" s="114">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
+        <v>265000</v>
       </c>
       <c r="G73" s="114">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
+        <v>265000</v>
       </c>
       <c r="H73" s="114">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
+        <v>265000</v>
       </c>
       <c r="I73" s="114">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
+        <v>265000</v>
       </c>
       <c r="J73" s="114">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
+        <v>265000</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -5195,25 +5432,32 @@
         <v>64</v>
       </c>
       <c r="D75" s="41">
-        <f t="shared" ref="D75:J75" si="31">+IF(D34&lt;30001,0,D34-30000)</f>
+        <f t="shared" ref="D75:J75" si="32">+IF(D34&lt;30001,0,D34-30000)</f>
+        <v>0</v>
       </c>
       <c r="E75" s="41">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
+        <v>0</v>
       </c>
       <c r="F75" s="41">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
+        <v>0</v>
       </c>
       <c r="G75" s="41">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
+        <v>0</v>
       </c>
       <c r="H75" s="41">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
+        <v>0</v>
       </c>
       <c r="I75" s="41">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
+        <v>0</v>
       </c>
       <c r="J75" s="41">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -5221,29 +5465,59 @@
         <v>65</v>
       </c>
       <c r="D76" s="5">
-        <f t="shared" ref="D76:J76" si="32">+IF(D75&lt;=$U$18,$Z$18,IF(D75&lt;=$U$19,$Z$19,IF(D75&lt;=$U$20,$Z$20,IF(D75&lt;=$U$21,$Z$21,IF(D75&lt;=$U$22,$Z$22,IF(D75&lt;=$U$23,$Z$23,IF(D75&lt;=$U$24,$Z$24,IF(D75&lt;=$U$25,$Z$25,IF(D75&lt;=$U$26,$Z$26,IF(D75&lt;=$U$27,$Z$27,IF(D75&lt;=$U$28,$Z$28,IF(D75&lt;=$U$29,$Z$29,IF(D75&lt;=$U$30,$Z$30,0)))))))))))))</f>
+        <f t="shared" ref="D76:J76" si="33">+IF(D75&lt;=$U$18,$Z$18,IF(D75&lt;=$U$19,$Z$19,IF(D75&lt;=$U$20,$Z$20,IF(D75&lt;=$U$21,$Z$21,IF(D75&lt;=$U$22,$Z$22,IF(D75&lt;=$U$23,$Z$23,IF(D75&lt;=$U$24,$Z$24,IF(D75&lt;=$U$25,$Z$25,IF(D75&lt;=$U$26,$Z$26,IF(D75&lt;=$U$27,$Z$27,IF(D75&lt;=$U$28,$Z$28,IF(D75&lt;=$U$29,$Z$29,IF(D75&lt;=$U$30,$Z$30,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="E76" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
+        <v>3</v>
       </c>
       <c r="F76" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
+        <v>3</v>
       </c>
       <c r="G76" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
+        <v>3</v>
       </c>
       <c r="H76" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
+        <v>3</v>
       </c>
       <c r="I76" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
+        <v>3</v>
       </c>
       <c r="J76" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A49:B49"/>
@@ -5256,29 +5530,6 @@
     <mergeCell ref="A58:B58"/>
     <mergeCell ref="A59:B59"/>
     <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5329,14 +5580,17 @@
         <v>137</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="86">
-        <f>+'A_サンクス有'!D24</f>
+      <c r="C4" s="86" t="str">
+        <f>+A_サンクス有!D24</f>
+        <v>--</v>
       </c>
       <c r="D4" s="28">
-        <f>+'A_サンクス有'!G51</f>
+        <f>+A_サンクス有!G51</f>
+        <v>265000</v>
       </c>
       <c r="E4" s="28">
-        <f>+'A_サンクス有'!J51</f>
+        <f>+A_サンクス有!J51</f>
+        <v>265000</v>
       </c>
       <c r="F4" s="28"/>
     </row>
@@ -5345,14 +5599,17 @@
         <v>138</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="86">
-        <f>+'A_サンクス有'!D25</f>
+      <c r="C5" s="86" t="str">
+        <f>+A_サンクス有!D25</f>
+        <v>--</v>
       </c>
       <c r="D5" s="28">
-        <f>+'A_サンクス有'!G61</f>
+        <f>+A_サンクス有!G61</f>
+        <v>265000</v>
       </c>
       <c r="E5" s="28">
-        <f>+'A_サンクス有'!J61</f>
+        <f>+A_サンクス有!J61</f>
+        <v>265000</v>
       </c>
       <c r="F5" s="27"/>
     </row>
@@ -5362,13 +5619,16 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="117">
-        <f>+'A_サンクス有'!D28</f>
+        <f>+A_サンクス有!D28</f>
+        <v>417</v>
       </c>
       <c r="D6" s="87">
-        <f>+'A_サンクス有'!G28</f>
+        <f>+A_サンクス有!G28</f>
+        <v>972.04493759999991</v>
       </c>
       <c r="E6" s="87">
-        <f>+'A_サンクス有'!J28</f>
+        <f>+A_サンクス有!J28</f>
+        <v>1535.5764266364577</v>
       </c>
       <c r="F6" s="10"/>
     </row>
@@ -5378,13 +5638,16 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="88">
-        <f>+'A_サンクス有'!D27</f>
+        <f>+A_サンクス有!D27</f>
+        <v>0.28000000000000003</v>
       </c>
       <c r="D7" s="89">
-        <f>+'A_サンクス有'!G27</f>
+        <f>+A_サンクス有!G27</f>
+        <v>0.29199999999999998</v>
       </c>
       <c r="E7" s="89">
-        <f>+'A_サンクス有'!J27</f>
+        <f>+A_サンクス有!J27</f>
+        <v>0.31</v>
       </c>
       <c r="F7" s="89"/>
     </row>
@@ -5394,13 +5657,16 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="117">
-        <f>+'A_サンクス有'!D29</f>
+        <f>+A_サンクス有!D29</f>
+        <v>300.24</v>
       </c>
       <c r="D8" s="10">
-        <f>+'A_サンクス有'!G29</f>
+        <f>+A_サンクス有!G29</f>
+        <v>688.20781582079985</v>
       </c>
       <c r="E8" s="10">
-        <f>+'A_サンクス有'!J29</f>
+        <f>+A_サンクス有!J29</f>
+        <v>1059.5477343791556</v>
       </c>
       <c r="F8" s="10"/>
     </row>
@@ -5418,13 +5684,16 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="117">
-        <f>+'A_サンクス有'!D34</f>
+        <f>+A_サンクス有!D34</f>
+        <v>0</v>
       </c>
       <c r="D10" s="10">
-        <f>+'A_サンクス有'!G34</f>
+        <f>+A_サンクス有!G34</f>
+        <v>3130.8320986265599</v>
       </c>
       <c r="E10" s="10">
-        <f>+'A_サンクス有'!J34</f>
+        <f>+A_サンクス有!J34</f>
+        <v>3657.0405498441269</v>
       </c>
       <c r="F10" s="10"/>
     </row>
@@ -5434,13 +5703,16 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="117">
-        <f>+'A_サンクス有'!D35</f>
+        <f>+A_サンクス有!D35</f>
+        <v>0</v>
       </c>
       <c r="D11" s="10">
-        <f>+'A_サンクス有'!G35</f>
+        <f>+A_サンクス有!G35</f>
+        <v>654.67166224670439</v>
       </c>
       <c r="E11" s="10">
-        <f>+'A_サンクス有'!J35</f>
+        <f>+A_サンクス有!J35</f>
+        <v>761.43740495233646</v>
       </c>
       <c r="F11" s="10"/>
     </row>
@@ -5451,12 +5723,15 @@
       <c r="B12" s="7"/>
       <c r="C12" s="28">
         <f>+IFERROR(C5/C11,0)</f>
+        <v>0</v>
       </c>
       <c r="D12" s="28">
         <f>+D4/D11</f>
+        <v>404.78306192538122</v>
       </c>
       <c r="E12" s="28">
         <f t="shared" ref="E12" si="0">+E4/E11</f>
+        <v>348.02598122505964</v>
       </c>
       <c r="F12" s="28"/>
     </row>
@@ -5467,12 +5742,15 @@
       <c r="B13" s="7"/>
       <c r="C13" s="28">
         <f>+IFERROR(C6/C12,0)</f>
+        <v>0</v>
       </c>
       <c r="D13" s="28">
         <f>+D5/D11</f>
+        <v>404.78306192538122</v>
       </c>
       <c r="E13" s="28">
         <f t="shared" ref="E13" si="1">+E5/E11</f>
+        <v>348.02598122505964</v>
       </c>
       <c r="F13" s="28"/>
     </row>
@@ -5489,17 +5767,20 @@
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="85" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="87">
-        <f>+'A_サンクス有'!D16</f>
+        <f>+A_サンクス有!D16</f>
+        <v>35</v>
       </c>
       <c r="D15" s="87">
-        <f>+'A_サンクス有'!G16</f>
+        <f>+A_サンクス有!G16</f>
+        <v>35</v>
       </c>
       <c r="E15" s="87">
-        <f>+'A_サンクス有'!J16</f>
+        <f>+A_サンクス有!J16</f>
+        <v>35</v>
       </c>
       <c r="F15" s="87"/>
       <c r="R15" s="5" t="s">
@@ -5508,17 +5789,20 @@
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="85" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="87">
         <f>+C17</f>
+        <v>0</v>
       </c>
       <c r="D16" s="87">
         <f>+D17</f>
+        <v>6</v>
       </c>
       <c r="E16" s="87">
         <f>+E17</f>
+        <v>11</v>
       </c>
       <c r="F16" s="87"/>
       <c r="R16" s="5" t="s">
@@ -5533,17 +5817,20 @@
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="85" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="87">
-        <f>+'A_サンクス有'!D36</f>
+        <f>+A_サンクス有!D36</f>
+        <v>0</v>
       </c>
       <c r="D17" s="87">
-        <f>+'A_サンクス有'!G36</f>
+        <f>+A_サンクス有!G36</f>
+        <v>6</v>
       </c>
       <c r="E17" s="87">
-        <f>+'A_サンクス有'!J36</f>
+        <f>+A_サンクス有!J36</f>
+        <v>11</v>
       </c>
       <c r="F17" s="10"/>
       <c r="R17" s="5">
@@ -5570,17 +5857,20 @@
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="85" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="87">
-        <f>+'A_サンクス有'!D37</f>
+        <f>+A_サンクス有!D37</f>
+        <v>0</v>
       </c>
       <c r="D18" s="87">
-        <f>+'A_サンクス有'!G37</f>
+        <f>+A_サンクス有!G37</f>
+        <v>4</v>
       </c>
       <c r="E18" s="87">
-        <f>+'A_サンクス有'!J37</f>
+        <f>+A_サンクス有!J37</f>
+        <v>8</v>
       </c>
       <c r="F18" s="10"/>
       <c r="R18" s="34">
@@ -5600,6 +5890,7 @@
       </c>
       <c r="X18" s="34">
         <f>+T18*2.5</f>
+        <v>37500000</v>
       </c>
       <c r="Y18" s="35">
         <v>2.5</v>
@@ -5611,13 +5902,16 @@
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="87">
-        <f>+'A_サンクス有'!D38</f>
+        <f>+A_サンクス有!D38</f>
+        <v>0</v>
       </c>
       <c r="D19" s="87">
-        <f>+'A_サンクス有'!G38</f>
+        <f>+A_サンクス有!G38</f>
+        <v>0</v>
       </c>
       <c r="E19" s="87">
-        <f>+'A_サンクス有'!J38</f>
+        <f>+A_サンクス有!J38</f>
+        <v>0</v>
       </c>
       <c r="F19" s="10"/>
       <c r="R19" s="34"/>
@@ -5632,13 +5926,16 @@
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="87">
-        <f>+'A_サンクス有'!D39</f>
+        <f>+A_サンクス有!D39</f>
+        <v>0</v>
       </c>
       <c r="D20" s="87">
-        <f>+'A_サンクス有'!G39</f>
+        <f>+A_サンクス有!G39</f>
+        <v>0</v>
       </c>
       <c r="E20" s="87">
-        <f>+'A_サンクス有'!J39</f>
+        <f>+A_サンクス有!J39</f>
+        <v>0</v>
       </c>
       <c r="F20" s="10"/>
       <c r="R20" s="34"/>
@@ -5665,14 +5962,17 @@
         <v>139</v>
       </c>
       <c r="B22" s="7"/>
-      <c r="C22" s="90">
+      <c r="C22" s="90" t="str">
         <f>+IFERROR(C4/C16,"--")</f>
+        <v>--</v>
       </c>
       <c r="D22" s="90">
         <f t="shared" ref="D22:E22" si="2">+IFERROR(D4/D16,"--")</f>
+        <v>44166.666666666664</v>
       </c>
       <c r="E22" s="90">
         <f t="shared" si="2"/>
+        <v>24090.909090909092</v>
       </c>
       <c r="F22" s="90"/>
       <c r="R22" s="34"/>
@@ -5686,14 +5986,17 @@
         <v>140</v>
       </c>
       <c r="B23" s="7"/>
-      <c r="C23" s="90">
+      <c r="C23" s="90" t="str">
         <f>+IFERROR(C5/C16,"--")</f>
+        <v>--</v>
       </c>
       <c r="D23" s="90">
         <f t="shared" ref="D23" si="3">+IFERROR(D5/D16,"--")</f>
+        <v>44166.666666666664</v>
       </c>
       <c r="E23" s="90">
         <f t="shared" ref="E23" si="4">+IFERROR(E5/E16,"--")</f>
+        <v>24090.909090909092</v>
       </c>
       <c r="F23" s="90"/>
       <c r="R23" s="34"/>
@@ -5721,13 +6024,16 @@
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="10">
-        <f>+'A_サンクス有'!E68+C29*C30</f>
+        <f>+A_サンクス有!E68+C29*C30</f>
+        <v>5000</v>
       </c>
       <c r="D25" s="10">
-        <f>+'A_サンクス有'!G68+D29*D30</f>
+        <f>+A_サンクス有!G68+D29*D30</f>
+        <v>5000</v>
       </c>
       <c r="E25" s="10">
-        <f>+'A_サンクス有'!J68+E29*E30</f>
+        <f>+A_サンクス有!J68+E29*E30</f>
+        <v>5000</v>
       </c>
       <c r="F25" s="10"/>
       <c r="R25" s="34"/>
@@ -5763,12 +6069,15 @@
       </c>
       <c r="C29" s="5">
         <f>+IF(C10&lt;=30000,0,C10-30000)</f>
+        <v>0</v>
       </c>
       <c r="D29" s="91">
         <f>+IF(D10&lt;=30000,0,D10-30000)</f>
+        <v>0</v>
       </c>
       <c r="E29" s="91">
         <f>+IF(E10&lt;=30000,0,E10-30000)</f>
+        <v>0</v>
       </c>
       <c r="F29" s="91"/>
       <c r="R29" s="34"/>
@@ -5783,12 +6092,15 @@
       </c>
       <c r="C30" s="5">
         <f>+IF(C29&lt;=$T$17,$Y$17,IF(C29&lt;=$T$18,$Y$18,IF(C29&lt;=$T$19,$Y$19,IF(C29&lt;=$T$20,$Y$20,IF(C29&lt;=$T$21,$Y$21,IF(C29&lt;=$T$22,$Y$22,IF(C29&lt;=$T$23,$Y$23,IF(C29&lt;=$T$24,$Y$24,IF(C29&lt;=$T$25,$Y$25,IF(C29&lt;=$T$26,$Y$26,IF(C29&lt;=$T$27,$Y$27,IF(C29&lt;=$T$28,$Y$28,IF(C29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="D30" s="5">
         <f>+IF(D29&lt;=$T$17,$Y$17,IF(D29&lt;=$T$18,$Y$18,IF(D29&lt;=$T$19,$Y$19,IF(D29&lt;=$T$20,$Y$20,IF(D29&lt;=$T$21,$Y$21,IF(D29&lt;=$T$22,$Y$22,IF(D29&lt;=$T$23,$Y$23,IF(D29&lt;=$T$24,$Y$24,IF(D29&lt;=$T$25,$Y$25,IF(D29&lt;=$T$26,$Y$26,IF(D29&lt;=$T$27,$Y$27,IF(D29&lt;=$T$28,$Y$28,IF(D29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="E30" s="5">
         <f>+IF(E29&lt;=$T$17,$Y$17,IF(E29&lt;=$T$18,$Y$18,IF(E29&lt;=$T$19,$Y$19,IF(E29&lt;=$T$20,$Y$20,IF(E29&lt;=$T$21,$Y$21,IF(E29&lt;=$T$22,$Y$22,IF(E29&lt;=$T$23,$Y$23,IF(E29&lt;=$T$24,$Y$24,IF(E29&lt;=$T$25,$Y$25,IF(E29&lt;=$T$26,$Y$26,IF(E29&lt;=$T$27,$Y$27,IF(E29&lt;=$T$28,$Y$28,IF(E29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="R30" s="34"/>
       <c r="T30" s="34"/>
@@ -5827,395 +6139,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1CA14B7-1E76-4B86-9C33-BD8F21953694}">
-  <dimension ref="A2:J42"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="1" max="1" width="14.25" customWidth="1"/>
-    <col min="5" max="5" width="14.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="54" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E4">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="60">
-        <v>8.5000000000000006E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B6" s="60">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="E7">
-        <f>+E4*B5*B6</f>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="54" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="60">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B11" s="60">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="E12">
-        <f>+E9*B10*B11</f>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="54" t="s">
-        <v>92</v>
-      </c>
-      <c r="D13" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" t="s">
-        <v>93</v>
-      </c>
-      <c r="B14" t="s">
-        <v>88</v>
-      </c>
-      <c r="E14">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="60">
-        <v>0.9</v>
-      </c>
-      <c r="C15" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B16" s="60">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E17">
-        <f>+E14*B15*B16</f>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="54" t="s">
-        <v>96</v>
-      </c>
-      <c r="D18" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" t="s">
-        <v>87</v>
-      </c>
-      <c r="B19" s="60">
-        <v>0.7</v>
-      </c>
-      <c r="C19" t="s">
-        <v>88</v>
-      </c>
-      <c r="E19">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" t="s">
-        <v>91</v>
-      </c>
-      <c r="B21" s="60">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E22">
-        <f>+E19*B20*B21</f>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="59" t="s">
-        <v>83</v>
-      </c>
-      <c r="B23" s="59"/>
-      <c r="C23" s="59" t="s">
-        <v>86</v>
-      </c>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="I23" s="67" t="s">
-        <v>102</v>
-      </c>
-      <c r="J23" s="68"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="54" t="s">
-        <v>84</v>
-      </c>
-      <c r="I24" s="66">
-        <v>1</v>
-      </c>
-      <c r="J24" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="61">
-        <v>0.8</v>
-      </c>
-      <c r="I25" s="66">
-        <v>2</v>
-      </c>
-      <c r="J25" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="61">
-        <v>0.06</v>
-      </c>
-      <c r="I26" s="66">
-        <v>3</v>
-      </c>
-      <c r="J26" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" t="s">
-        <v>85</v>
-      </c>
-      <c r="B27" s="61">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="I27" s="66">
-        <v>4</v>
-      </c>
-      <c r="J27" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="I29" s="67" t="s">
-        <v>107</v>
-      </c>
-      <c r="J29" s="68"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="61">
-        <v>0.75</v>
-      </c>
-      <c r="I30" s="66">
-        <v>1</v>
-      </c>
-      <c r="J30" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="61">
-        <v>0.08</v>
-      </c>
-      <c r="I31" s="66">
-        <v>2</v>
-      </c>
-      <c r="J31" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" t="s">
-        <v>85</v>
-      </c>
-      <c r="B32" s="61">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="I32" s="66">
-        <v>3</v>
-      </c>
-      <c r="J32" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="I33" s="66">
-        <v>4</v>
-      </c>
-      <c r="J33" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="54" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="62" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="61">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" t="s">
-        <v>85</v>
-      </c>
-      <c r="B37" s="61">
-        <v>4.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="54" t="s">
-        <v>98</v>
-      </c>
-      <c r="E39" s="54" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="62">
-        <v>1</v>
-      </c>
-      <c r="E40" t="s">
-        <v>41</v>
-      </c>
-      <c r="F40" s="62" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="61">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="E41" t="s">
-        <v>100</v>
-      </c>
-      <c r="F41" s="61">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" t="s">
-        <v>85</v>
-      </c>
-      <c r="B42" s="61">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="F42" s="61"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA45D6B4-55E6-58DE-A1CF-69AB6EDE5A4B}">
   <dimension ref="A2:Z76"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.5" x14ac:dyDescent="0.55000000000000004"/>
@@ -6246,10 +6169,8 @@
       </c>
     </row>
     <row r="4" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">タナカホーム株式会社御中_LINEOA施策提案【SIM】ver1.2　B_サンクス無（離脱防止＋サイトのボタン）</t>
-        </is>
+      <c r="A4" s="56" t="s">
+        <v>195</v>
       </c>
       <c r="N4" s="55"/>
       <c r="O4" s="55"/>
@@ -6313,14 +6234,14 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="137" t="s">
+      <c r="A8" s="148" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D8" s="33">
         <v>0</v>
@@ -6339,19 +6260,19 @@
         <v>0</v>
       </c>
       <c r="N8" s="69" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O8" s="35" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="138"/>
+      <c r="A9" s="149"/>
       <c r="B9" s="19" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D9" s="33">
         <v>0</v>
@@ -6366,7 +6287,7 @@
       <c r="J9" s="29"/>
       <c r="K9" s="118"/>
       <c r="N9" s="132" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O9" s="130" t="s">
         <v>154</v>
@@ -6376,7 +6297,7 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="137" t="s">
+      <c r="A10" s="148" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="19" t="s">
@@ -6389,7 +6310,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="124" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H10" s="125">
         <v>35</v>
@@ -6400,11 +6321,11 @@
       <c r="J10" s="29"/>
       <c r="K10" s="118"/>
       <c r="N10" s="132" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="138"/>
+      <c r="A11" s="149"/>
       <c r="B11" s="19" t="s">
         <v>11</v>
       </c>
@@ -6415,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="126" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H11" s="127">
         <v>8</v>
@@ -6438,31 +6359,31 @@
       <c r="V12" s="55"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="139" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="139"/>
+      <c r="A13" s="150" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="150"/>
       <c r="C13" s="95"/>
       <c r="D13" s="13" t="s">
         <v>29</v>
       </c>
       <c r="E13" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="F13" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="F13" s="36" t="s">
+      <c r="G13" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="G13" s="36" t="s">
+      <c r="H13" s="36" t="s">
         <v>169</v>
       </c>
-      <c r="H13" s="36" t="s">
+      <c r="I13" s="36" t="s">
         <v>170</v>
       </c>
-      <c r="I13" s="36" t="s">
+      <c r="J13" s="36" t="s">
         <v>171</v>
-      </c>
-      <c r="J13" s="36" t="s">
-        <v>172</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>1</v>
@@ -6484,7 +6405,7 @@
       <c r="V13" s="23"/>
     </row>
     <row r="14" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="140" t="s">
+      <c r="A14" s="151" t="s">
         <v>32</v>
       </c>
       <c r="B14" s="20" t="s">
@@ -6493,54 +6414,68 @@
       <c r="C14" s="99"/>
       <c r="D14" s="42">
         <f>+H8</f>
+        <v>13228</v>
       </c>
       <c r="E14" s="43">
         <f>+D14</f>
+        <v>13228</v>
       </c>
       <c r="F14" s="43">
         <f t="shared" ref="F14:J14" si="0">+E14</f>
+        <v>13228</v>
       </c>
       <c r="G14" s="43">
         <f t="shared" si="0"/>
+        <v>13228</v>
       </c>
       <c r="H14" s="43">
         <f t="shared" si="0"/>
+        <v>13228</v>
       </c>
       <c r="I14" s="43">
         <f t="shared" si="0"/>
+        <v>13228</v>
       </c>
       <c r="J14" s="43">
         <f t="shared" si="0"/>
+        <v>13228</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="7"/>
     </row>
     <row r="15" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="141"/>
+      <c r="A15" s="152"/>
       <c r="B15" s="20" t="s">
         <v>35</v>
       </c>
       <c r="C15" s="99"/>
       <c r="D15" s="42">
         <f t="shared" ref="D15" si="1">+H9</f>
+        <v>0</v>
       </c>
       <c r="E15" s="43">
         <f t="shared" ref="E15:J16" si="2">+D15</f>
+        <v>0</v>
       </c>
       <c r="F15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="G15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="H15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="J15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="K15" s="11"/>
       <c r="L15" s="7"/>
@@ -6558,31 +6493,38 @@
       </c>
     </row>
     <row r="16" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="142"/>
+      <c r="A16" s="153"/>
       <c r="B16" s="20" t="s">
         <v>150</v>
       </c>
       <c r="C16" s="99"/>
       <c r="D16" s="42">
         <f>H10</f>
+        <v>35</v>
       </c>
       <c r="E16" s="43">
         <f t="shared" si="2"/>
+        <v>35</v>
       </c>
       <c r="F16" s="43">
         <f t="shared" si="2"/>
+        <v>35</v>
       </c>
       <c r="G16" s="43">
         <f t="shared" si="2"/>
+        <v>35</v>
       </c>
       <c r="H16" s="43">
         <f t="shared" si="2"/>
+        <v>35</v>
       </c>
       <c r="I16" s="43">
         <f t="shared" si="2"/>
+        <v>35</v>
       </c>
       <c r="J16" s="43">
         <f t="shared" si="2"/>
+        <v>35</v>
       </c>
       <c r="K16" s="11"/>
       <c r="L16" s="7"/>
@@ -6600,7 +6542,7 @@
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="140" t="s">
+      <c r="A17" s="151" t="s">
         <v>3</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -6645,7 +6587,7 @@
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="141"/>
+      <c r="A18" s="152"/>
       <c r="B18" s="8" t="s">
         <v>5</v>
       </c>
@@ -6709,7 +6651,7 @@
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="141"/>
+      <c r="A19" s="152"/>
       <c r="B19" s="8" t="s">
         <v>115</v>
       </c>
@@ -6763,13 +6705,14 @@
       </c>
       <c r="Y19" s="34">
         <f>+U19*2.5</f>
+        <v>37500000</v>
       </c>
       <c r="Z19" s="35">
         <v>2.5</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="141"/>
+      <c r="A20" s="152"/>
       <c r="B20" s="8" t="s">
         <v>113</v>
       </c>
@@ -6804,7 +6747,7 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="142"/>
+      <c r="A21" s="153"/>
       <c r="B21" s="8" t="s">
         <v>114</v>
       </c>
@@ -6847,7 +6790,7 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="143" t="s">
+      <c r="A22" s="154" t="s">
         <v>12</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -6878,7 +6821,7 @@
       <c r="K22" s="11"/>
       <c r="L22" s="7"/>
       <c r="N22" s="69" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O22" s="17" t="s">
         <v>41</v>
@@ -6893,7 +6836,7 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="141"/>
+      <c r="A23" s="152"/>
       <c r="B23" s="6" t="s">
         <v>5</v>
       </c>
@@ -6903,26 +6846,32 @@
       </c>
       <c r="E23" s="46">
         <f>IF(E18=FALSE,0,E15*$P$18*0.08*0.08+(E14-E15)*$P$19*0.12*0.12)</f>
+        <v>104.76576</v>
       </c>
       <c r="F23" s="46">
         <f>IF(F18=FALSE,0,F15*$P$18*0.08*0.08+(F14-F15)*$P$19*0.12*0.12)</f>
+        <v>104.76576</v>
       </c>
       <c r="G23" s="63">
         <f t="shared" ref="G23:J24" si="3">F23*1.01</f>
+        <v>105.81341760000001</v>
       </c>
       <c r="H23" s="63">
         <f t="shared" si="3"/>
+        <v>106.871551776</v>
       </c>
       <c r="I23" s="63">
         <f t="shared" si="3"/>
+        <v>107.94026729376</v>
       </c>
       <c r="J23" s="63">
         <f t="shared" si="3"/>
+        <v>109.01966996669761</v>
       </c>
       <c r="K23" s="11"/>
       <c r="L23" s="7"/>
       <c r="N23" s="69" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O23" s="17" t="s">
         <v>42</v>
@@ -6940,7 +6889,7 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="141"/>
+      <c r="A24" s="152"/>
       <c r="B24" s="6" t="s">
         <v>115</v>
       </c>
@@ -6950,28 +6899,32 @@
       </c>
       <c r="E24" s="46">
         <f>+IF(E19=FALSE,0,SUM(H10:H11)*0.15)</f>
+        <v>0</v>
       </c>
       <c r="F24" s="63">
         <f>E24*1.01</f>
+        <v>0</v>
       </c>
       <c r="G24" s="63">
         <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="H24" s="63">
         <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I24" s="63">
         <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="J24" s="63">
         <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="K24" s="11"/>
       <c r="L24" s="7"/>
-      <c r="N24" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B_サンクス無：サンクスLINE誘導は入れない（オプション。Aのシートを参照）</t>
-        </is>
+      <c r="N24" s="69" t="s">
+        <v>196</v>
       </c>
       <c r="O24" s="22" t="s">
         <v>44</v>
@@ -6989,7 +6942,7 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="142"/>
+      <c r="A25" s="153"/>
       <c r="B25" s="6" t="s">
         <v>69</v>
       </c>
@@ -6999,21 +6952,27 @@
       </c>
       <c r="E25" s="46">
         <f>+IF(E20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
+        <v>0</v>
       </c>
       <c r="F25" s="46">
         <f t="shared" ref="F25:J25" si="4">+IF(F20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
+        <v>0</v>
       </c>
       <c r="G25" s="46">
         <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="H25" s="46">
         <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="I25" s="46">
         <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="J25" s="46">
         <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="K25" s="11"/>
       <c r="L25" s="7"/>
@@ -7031,36 +6990,42 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="144" t="s">
+      <c r="A26" s="138" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="145"/>
+      <c r="B26" s="139"/>
       <c r="C26" s="23"/>
       <c r="D26" s="44" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="46">
         <f>+SUM(E22:E25)+$H$9*$P$16+($H$8-$H$9)*$P$15+IF(P9=FALSE,0,$K$8*0.15*0.08)</f>
+        <v>170.90575999999999</v>
       </c>
       <c r="F26" s="46">
         <f t="shared" ref="F26:J26" si="5">+SUM(F22:F25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
+        <v>170.90575999999999</v>
       </c>
       <c r="G26" s="46">
         <f>+SUM(G22:G25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
+        <v>171.95341760000002</v>
       </c>
       <c r="H26" s="46">
         <f t="shared" si="5"/>
+        <v>173.011551776</v>
       </c>
       <c r="I26" s="46">
         <f t="shared" si="5"/>
+        <v>174.08026729376002</v>
       </c>
       <c r="J26" s="46">
         <f t="shared" si="5"/>
+        <v>175.15966996669761</v>
       </c>
       <c r="K26" s="11"/>
       <c r="L26" s="7"/>
       <c r="N26" s="72" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="O26" s="17" t="s">
         <v>41</v>
@@ -7075,10 +7040,10 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="144" t="s">
+      <c r="A27" s="138" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="145"/>
+      <c r="B27" s="139"/>
       <c r="C27" s="23"/>
       <c r="D27" s="107">
         <v>0.28000000000000003</v>
@@ -7088,23 +7053,28 @@
       </c>
       <c r="F27" s="47">
         <f>ROUND(E27*1.02,3)</f>
+        <v>0.28599999999999998</v>
       </c>
       <c r="G27" s="47">
         <f>ROUND(F27*1.02,3)</f>
+        <v>0.29199999999999998</v>
       </c>
       <c r="H27" s="47">
         <f>ROUND(G27*1.02,3)</f>
+        <v>0.29799999999999999</v>
       </c>
       <c r="I27" s="47">
         <f>ROUND(H27*1.02,3)</f>
+        <v>0.30399999999999999</v>
       </c>
       <c r="J27" s="47">
         <f>ROUND(I27*1.02,3)</f>
+        <v>0.31</v>
       </c>
       <c r="K27" s="11"/>
       <c r="L27" s="7"/>
       <c r="N27" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O27" s="17" t="s">
         <v>42</v>
@@ -7122,31 +7092,37 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="146" t="s">
+      <c r="A28" s="155" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="147"/>
+      <c r="B28" s="156"/>
       <c r="C28" s="101"/>
       <c r="D28" s="106">
         <v>417</v>
       </c>
       <c r="E28" s="49">
         <f>+D28+E26</f>
+        <v>587.90575999999999</v>
       </c>
       <c r="F28" s="49">
         <f t="shared" ref="F28:J28" si="6">+E28+F26</f>
+        <v>758.81151999999997</v>
       </c>
       <c r="G28" s="49">
         <f t="shared" si="6"/>
+        <v>930.76493759999994</v>
       </c>
       <c r="H28" s="49">
         <f t="shared" si="6"/>
+        <v>1103.776489376</v>
       </c>
       <c r="I28" s="49">
         <f t="shared" si="6"/>
+        <v>1277.85675666976</v>
       </c>
       <c r="J28" s="49">
         <f t="shared" si="6"/>
+        <v>1453.0164266364577</v>
       </c>
       <c r="K28" s="12"/>
       <c r="L28" s="7"/>
@@ -7166,31 +7142,38 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="148" t="s">
+      <c r="A29" s="144" t="s">
         <v>14</v>
       </c>
-      <c r="B29" s="149"/>
+      <c r="B29" s="145"/>
       <c r="C29" s="102"/>
       <c r="D29" s="108">
         <f>+D28*(1-D27)</f>
+        <v>300.24</v>
       </c>
       <c r="E29" s="50">
         <f>+E28*(1-E27)</f>
+        <v>423.29214719999999</v>
       </c>
       <c r="F29" s="50">
         <f t="shared" ref="F29:J29" si="7">+F28*(1-F27)</f>
+        <v>541.79142528</v>
       </c>
       <c r="G29" s="50">
         <f t="shared" si="7"/>
+        <v>658.98157582079989</v>
       </c>
       <c r="H29" s="50">
         <f t="shared" si="7"/>
+        <v>774.85109554195196</v>
       </c>
       <c r="I29" s="50">
         <f t="shared" si="7"/>
+        <v>889.38830264215289</v>
       </c>
       <c r="J29" s="50">
         <f t="shared" si="7"/>
+        <v>1002.5813343791557</v>
       </c>
       <c r="K29" s="12"/>
       <c r="L29" s="7"/>
@@ -7204,10 +7187,10 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="135" t="s">
+      <c r="A30" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="B30" s="136"/>
+      <c r="B30" s="143"/>
       <c r="C30" s="30"/>
       <c r="D30" s="48">
         <v>0</v>
@@ -7233,7 +7216,7 @@
       <c r="K30" s="11"/>
       <c r="L30" s="7"/>
       <c r="N30" s="69" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="O30" s="17" t="s">
         <v>120</v>
@@ -7246,31 +7229,38 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="144" t="s">
+      <c r="A31" s="138" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="145"/>
+      <c r="B31" s="139"/>
       <c r="C31" s="23"/>
       <c r="D31" s="108">
         <f>+D30*D29*0.41*0.07</f>
+        <v>0</v>
       </c>
       <c r="E31" s="63">
         <f>+E29*E30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>133.59384617954925</v>
       </c>
       <c r="F31" s="63">
         <f>+F29*F30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>170.99301465674591</v>
       </c>
       <c r="G31" s="63">
         <f>+G29*G30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>207.97901368523404</v>
       </c>
       <c r="H31" s="63">
         <f>+H29*H30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>195.63857020192177</v>
       </c>
       <c r="I31" s="63">
         <f>+I29*I30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>224.55754000260586</v>
       </c>
       <c r="J31" s="63">
         <f>+J29*J30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>253.13712518130293</v>
       </c>
       <c r="K31" s="11"/>
       <c r="L31" s="7"/>
@@ -7281,10 +7271,10 @@
       <c r="Z31" s="35"/>
     </row>
     <row r="32" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="135" t="s">
+      <c r="A32" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="136"/>
+      <c r="B32" s="143"/>
       <c r="C32" s="30"/>
       <c r="D32" s="48">
         <v>0</v>
@@ -7310,7 +7300,7 @@
       <c r="K32" s="11"/>
       <c r="L32" s="7"/>
       <c r="N32" s="69" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="O32" s="17" t="s">
         <v>123</v>
@@ -7320,6 +7310,7 @@
       </c>
       <c r="Q32" s="73">
         <f>+IF(P32=TRUE,1.1,0.95)</f>
+        <v>1.1000000000000001</v>
       </c>
       <c r="S32" s="34"/>
       <c r="U32" s="34"/>
@@ -7327,31 +7318,37 @@
       <c r="Z32" s="35"/>
     </row>
     <row r="33" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="144" t="s">
+      <c r="A33" s="138" t="s">
         <v>31</v>
       </c>
-      <c r="B33" s="145"/>
+      <c r="B33" s="139"/>
       <c r="C33" s="23"/>
       <c r="D33" s="44">
         <v>0</v>
       </c>
       <c r="E33" s="63">
         <f t="shared" ref="E33:J33" si="8">+E26*E32*$P$26*$P$27*$P$36</f>
+        <v>94.004277880920014</v>
       </c>
       <c r="F33" s="63">
         <f t="shared" si="8"/>
+        <v>94.004277880920014</v>
       </c>
       <c r="G33" s="63">
         <f t="shared" si="8"/>
+        <v>94.580527014679234</v>
       </c>
       <c r="H33" s="63">
         <f t="shared" si="8"/>
+        <v>95.162538639776017</v>
       </c>
       <c r="I33" s="63">
         <f t="shared" si="8"/>
+        <v>95.750370381123787</v>
       </c>
       <c r="J33" s="63">
         <f t="shared" si="8"/>
+        <v>96.344080439885019</v>
       </c>
       <c r="K33" s="11"/>
       <c r="L33" s="7"/>
@@ -7363,34 +7360,42 @@
       </c>
       <c r="Q33" s="73">
         <f t="shared" ref="Q33:Q35" si="9">+IF(P33=TRUE,1.1,0.95)</f>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="148" t="s">
+      <c r="A34" s="144" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="149"/>
+      <c r="B34" s="145"/>
       <c r="C34" s="102"/>
       <c r="D34" s="108">
         <f>+D29*D30</f>
+        <v>0</v>
       </c>
       <c r="E34" s="46">
         <f>+E29*E30*$P$24+E26*E32</f>
+        <v>2209.0636710399999</v>
       </c>
       <c r="F34" s="46">
         <f>+F29*F30*$P$24+F26*F32</f>
+        <v>2588.261360896</v>
       </c>
       <c r="G34" s="46">
         <f>+G29*G30*$P$24+G26*G32</f>
+        <v>2968.5081306265597</v>
       </c>
       <c r="H34" s="46">
         <f>+H29*H30*$P$24*$Q$24+H26*H32</f>
+        <v>2848.6765634673975</v>
       </c>
       <c r="I34" s="46">
         <f>+I29*I30*$P$24*$Q$24+I26*I32</f>
+        <v>3147.2353912327117</v>
       </c>
       <c r="J34" s="46">
         <f>+J29*J30*$P$24*$Q$24+J26*J32</f>
+        <v>3442.4065658441268</v>
       </c>
       <c r="K34" s="11"/>
       <c r="L34" s="7"/>
@@ -7402,34 +7407,42 @@
       </c>
       <c r="Q34" s="73">
         <f t="shared" si="9"/>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="148" t="s">
+      <c r="A35" s="144" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="149"/>
+      <c r="B35" s="145"/>
       <c r="C35" s="102"/>
       <c r="D35" s="109">
         <f>+D31*1.02</f>
+        <v>0</v>
       </c>
       <c r="E35" s="50">
         <f>+E31+E33+1.05*(E31+E33)</f>
+        <v>466.57615432396199</v>
       </c>
       <c r="F35" s="50">
         <f t="shared" ref="F35:J35" si="10">+F31+F33+1.05*(F31+F33)</f>
+        <v>543.24444970221521</v>
       </c>
       <c r="G35" s="50">
         <f t="shared" si="10"/>
+        <v>620.24705843482229</v>
       </c>
       <c r="H35" s="50">
         <f t="shared" si="10"/>
+        <v>596.14227312548041</v>
       </c>
       <c r="I35" s="50">
         <f t="shared" si="10"/>
+        <v>656.63121628664589</v>
       </c>
       <c r="J35" s="50">
         <f t="shared" si="10"/>
+        <v>716.43647152343533</v>
       </c>
       <c r="K35" s="11"/>
       <c r="L35" s="7"/>
@@ -7441,95 +7454,100 @@
       </c>
       <c r="Q35" s="73">
         <f t="shared" si="9"/>
+        <v>0.95</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="150" t="s">
+      <c r="A36" s="146" t="s">
         <v>6</v>
       </c>
-      <c r="B36" s="6">
+      <c r="B36" s="6" t="str">
         <f>+C8</f>
+        <v>資料請求</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="11">
         <v>0</v>
       </c>
-      <c r="E36" s="156">
+      <c r="E36" s="135">
         <v>4</v>
       </c>
-      <c r="F36" s="156">
+      <c r="F36" s="135">
         <v>6</v>
       </c>
-      <c r="G36" s="156">
+      <c r="G36" s="135">
         <v>6</v>
       </c>
-      <c r="H36" s="156">
+      <c r="H36" s="135">
         <v>8</v>
       </c>
-      <c r="I36" s="156">
+      <c r="I36" s="135">
         <v>9</v>
       </c>
-      <c r="J36" s="156">
+      <c r="J36" s="135">
         <v>11</v>
       </c>
       <c r="K36" s="115">
         <f>SUM(E36:J36)</f>
+        <v>44</v>
       </c>
       <c r="L36" s="7"/>
-      <c r="N36" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CVの件数はAと同じ（サンクスLINEの効果＝来場予約した方のキャンセルを減らす＝「来場」の数なので、SIMには出さない）</t>
-        </is>
+      <c r="N36" s="69" t="s">
+        <v>197</v>
       </c>
       <c r="O36" s="17" t="s">
         <v>124</v>
       </c>
       <c r="P36" s="74">
         <f>1*(Q32*Q33*Q34*Q35)</f>
+        <v>1.2644500000000003</v>
       </c>
       <c r="Q36" s="73"/>
     </row>
     <row r="37" spans="1:17" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="151"/>
-      <c r="B37" s="6">
+      <c r="A37" s="147"/>
+      <c r="B37" s="6" t="str">
         <f>+C9</f>
+        <v>来場予約</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="11">
         <v>0</v>
       </c>
-      <c r="E37" s="156">
+      <c r="E37" s="135">
         <v>2</v>
       </c>
-      <c r="F37" s="156">
+      <c r="F37" s="135">
         <v>3</v>
       </c>
-      <c r="G37" s="156">
+      <c r="G37" s="135">
         <v>4</v>
       </c>
-      <c r="H37" s="156">
+      <c r="H37" s="135">
         <v>6</v>
       </c>
-      <c r="I37" s="156">
+      <c r="I37" s="135">
         <v>7</v>
       </c>
-      <c r="J37" s="156">
+      <c r="J37" s="135">
         <v>8</v>
       </c>
       <c r="K37" s="115">
         <f>SUM(E37:J37)</f>
+        <v>30</v>
       </c>
       <c r="L37" s="7"/>
       <c r="N37" s="69" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="150" t="s">
+      <c r="A38" s="146" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="6">
+      <c r="B38" s="6" t="str">
         <f>+C10</f>
+        <v>-</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="11">
@@ -7555,6 +7573,7 @@
       </c>
       <c r="K38" s="115">
         <f>SUM(E38:J38)</f>
+        <v>0</v>
       </c>
       <c r="L38" s="7"/>
       <c r="N38" s="69" t="s">
@@ -7565,9 +7584,10 @@
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="151"/>
-      <c r="B39" s="6">
+      <c r="A39" s="147"/>
+      <c r="B39" s="6" t="str">
         <f>+C11</f>
+        <v>-</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="11">
@@ -7593,6 +7613,7 @@
       </c>
       <c r="K39" s="115">
         <f>SUM(E39:J39)</f>
+        <v>0</v>
       </c>
       <c r="L39" s="7"/>
       <c r="N39" s="69" t="s">
@@ -7603,34 +7624,42 @@
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="152" t="s">
+      <c r="A40" s="140" t="s">
         <v>53</v>
       </c>
-      <c r="B40" s="153"/>
+      <c r="B40" s="141"/>
       <c r="C40" s="97"/>
       <c r="D40" s="11">
         <f>SUM(D36:D39)</f>
+        <v>0</v>
       </c>
       <c r="E40" s="10">
         <f>SUM(E36:E39)</f>
+        <v>6</v>
       </c>
       <c r="F40" s="10">
         <f t="shared" ref="F40:J40" si="11">SUM(F36:F39)</f>
+        <v>9</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="11"/>
+        <v>10</v>
       </c>
       <c r="H40" s="10">
         <f t="shared" si="11"/>
+        <v>14</v>
       </c>
       <c r="I40" s="10">
         <f t="shared" si="11"/>
+        <v>16</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="11"/>
+        <v>19</v>
       </c>
       <c r="K40" s="115">
         <f>SUM(E40:J40)</f>
+        <v>74</v>
       </c>
       <c r="L40" s="7"/>
       <c r="O40" s="17"/>
@@ -7641,24 +7670,31 @@
       </c>
       <c r="D41" s="18">
         <f t="shared" ref="D41" si="12">+IFERROR(D40/D35,0)</f>
+        <v>0</v>
       </c>
       <c r="E41" s="18">
         <f>IFERROR(E40/E35,0)</f>
+        <v>1.2859637048304801E-2</v>
       </c>
       <c r="F41" s="18">
         <f t="shared" ref="F41:J41" si="13">IFERROR(F40/F35,0)</f>
+        <v>1.6567127386084551E-2</v>
       </c>
       <c r="G41" s="18">
         <f t="shared" si="13"/>
+        <v>1.6122607699639472E-2</v>
       </c>
       <c r="H41" s="18">
         <f t="shared" si="13"/>
+        <v>2.3484326864793861E-2</v>
       </c>
       <c r="I41" s="18">
         <f t="shared" si="13"/>
+        <v>2.4366797683610823E-2</v>
       </c>
       <c r="J41" s="18">
         <f t="shared" si="13"/>
+        <v>2.6520146244925626E-2</v>
       </c>
       <c r="N41" s="69" t="s">
         <v>117</v>
@@ -7686,245 +7722,297 @@
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="144" t="s">
+      <c r="A44" s="138" t="s">
         <v>27</v>
       </c>
-      <c r="B44" s="145"/>
+      <c r="B44" s="139"/>
       <c r="C44" s="103"/>
       <c r="D44" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E44" s="31">
         <f>+E75*E76</f>
+        <v>0</v>
       </c>
       <c r="F44" s="31">
         <f t="shared" ref="F44:J44" si="14">+F75*F76</f>
+        <v>0</v>
       </c>
       <c r="G44" s="31">
         <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="H44" s="31">
         <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="I44" s="31">
         <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="J44" s="31">
         <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="K44" s="11"/>
       <c r="L44" s="7"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="144" t="s">
+      <c r="A45" s="138" t="s">
         <v>129</v>
       </c>
-      <c r="B45" s="145"/>
+      <c r="B45" s="139"/>
       <c r="C45" s="104">
         <f>+SUM(C65:C72)</f>
+        <v>0</v>
       </c>
       <c r="D45" s="80">
         <f>+SUM(D65:D72)</f>
+        <v>165000</v>
       </c>
       <c r="E45" s="27">
         <f>SUM(E65:E69)+SUM(E71:E72)</f>
+        <v>235000</v>
       </c>
       <c r="F45" s="27">
         <f t="shared" ref="F45:J45" si="15">SUM(F65:F69)+SUM(F71:F72)</f>
+        <v>235000</v>
       </c>
       <c r="G45" s="27">
         <f t="shared" si="15"/>
+        <v>235000</v>
       </c>
       <c r="H45" s="27">
         <f t="shared" si="15"/>
+        <v>235000</v>
       </c>
       <c r="I45" s="27">
         <f t="shared" si="15"/>
+        <v>235000</v>
       </c>
       <c r="J45" s="27">
         <f t="shared" si="15"/>
+        <v>235000</v>
       </c>
       <c r="K45" s="11"/>
       <c r="L45" s="7"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="144" t="s">
+      <c r="A46" s="138" t="s">
         <v>17</v>
       </c>
-      <c r="B46" s="145"/>
+      <c r="B46" s="139"/>
       <c r="C46" s="103"/>
       <c r="D46" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E46" s="28">
         <f t="shared" ref="E46:J46" si="16">SUM(E65:E67)/(E28-D28)</f>
+        <v>175.53533596527117</v>
       </c>
       <c r="F46" s="28">
         <f t="shared" si="16"/>
+        <v>175.53533596527117</v>
       </c>
       <c r="G46" s="28">
         <f t="shared" si="16"/>
+        <v>174.46585487347713</v>
       </c>
       <c r="H46" s="28">
         <f t="shared" si="16"/>
+        <v>173.39882621734606</v>
       </c>
       <c r="I46" s="28">
         <f t="shared" si="16"/>
+        <v>172.33429421023968</v>
       </c>
       <c r="J46" s="28">
         <f t="shared" si="16"/>
+        <v>171.27230261226092</v>
       </c>
       <c r="K46" s="11"/>
       <c r="L46" s="7"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="144" t="s">
+      <c r="A47" s="138" t="s">
         <v>18</v>
       </c>
-      <c r="B47" s="145"/>
+      <c r="B47" s="139"/>
       <c r="C47" s="103"/>
       <c r="D47" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E47" s="28">
         <f t="shared" ref="E47:I47" si="17">+E51/E35</f>
+        <v>503.66911772527141</v>
       </c>
       <c r="F47" s="28">
         <f t="shared" si="17"/>
+        <v>432.58610396998546</v>
       </c>
       <c r="G47" s="28">
         <f t="shared" si="17"/>
+        <v>378.88128094152762</v>
       </c>
       <c r="H47" s="28">
         <f t="shared" si="17"/>
+        <v>394.20120094475413</v>
       </c>
       <c r="I47" s="28">
         <f t="shared" si="17"/>
+        <v>357.88734097803393</v>
       </c>
       <c r="J47" s="28">
         <f>+J51/J35</f>
+        <v>328.01233513460647</v>
       </c>
       <c r="K47" s="11"/>
       <c r="L47" s="7"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="144" t="s">
+      <c r="A48" s="138" t="s">
         <v>20</v>
       </c>
-      <c r="B48" s="145"/>
+      <c r="B48" s="139"/>
       <c r="C48" s="103"/>
       <c r="D48" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E48" s="32">
         <f>IFERROR(E40/E35,0)</f>
+        <v>1.2859637048304801E-2</v>
       </c>
       <c r="F48" s="32">
         <f t="shared" ref="F48:J48" si="18">IFERROR(F40/F35,0)</f>
+        <v>1.6567127386084551E-2</v>
       </c>
       <c r="G48" s="32">
         <f t="shared" si="18"/>
+        <v>1.6122607699639472E-2</v>
       </c>
       <c r="H48" s="32">
         <f t="shared" si="18"/>
+        <v>2.3484326864793861E-2</v>
       </c>
       <c r="I48" s="32">
         <f t="shared" si="18"/>
+        <v>2.4366797683610823E-2</v>
       </c>
       <c r="J48" s="32">
         <f t="shared" si="18"/>
+        <v>2.6520146244925626E-2</v>
       </c>
       <c r="K48" s="11"/>
       <c r="L48" s="7"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="152" t="s">
+      <c r="A49" s="140" t="s">
         <v>19</v>
       </c>
-      <c r="B49" s="153"/>
+      <c r="B49" s="141"/>
       <c r="C49" s="105"/>
       <c r="D49" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E49" s="28">
         <f>IFERROR(E51/E40,0)</f>
+        <v>39166.666666666664</v>
       </c>
       <c r="F49" s="28">
         <f t="shared" ref="F49:J49" si="19">IFERROR(F51/F40,0)</f>
+        <v>26111.111111111109</v>
       </c>
       <c r="G49" s="28">
         <f t="shared" si="19"/>
+        <v>23500</v>
       </c>
       <c r="H49" s="28">
         <f t="shared" si="19"/>
+        <v>16785.714285714286</v>
       </c>
       <c r="I49" s="28">
         <f t="shared" si="19"/>
+        <v>14687.5</v>
       </c>
       <c r="J49" s="28">
         <f t="shared" si="19"/>
+        <v>12368.421052631578</v>
       </c>
       <c r="K49" s="11"/>
       <c r="L49" s="7"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="152" t="s">
+      <c r="A50" s="140" t="s">
         <v>116</v>
       </c>
-      <c r="B50" s="153"/>
+      <c r="B50" s="141"/>
       <c r="C50" s="105"/>
       <c r="D50" s="64" t="s">
         <v>22</v>
       </c>
       <c r="E50" s="65">
         <f>+E36*$D$8+E38*$D$10</f>
+        <v>0</v>
       </c>
       <c r="F50" s="65">
         <f t="shared" ref="F50:J50" si="20">+F36*$D$8+F38*$D$10</f>
+        <v>0</v>
       </c>
       <c r="G50" s="65">
         <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="H50" s="65">
         <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="I50" s="65">
         <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="J50" s="65">
         <f t="shared" si="20"/>
+        <v>0</v>
       </c>
       <c r="K50" s="11"/>
       <c r="L50" s="7"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="154" t="s">
+      <c r="A51" s="136" t="s">
         <v>70</v>
       </c>
-      <c r="B51" s="155"/>
+      <c r="B51" s="137"/>
       <c r="C51" s="110">
         <f>+C45</f>
+        <v>0</v>
       </c>
       <c r="D51" s="40">
         <f>+D45</f>
+        <v>165000</v>
       </c>
       <c r="E51" s="40">
         <f>SUM(E45,E50)+E44</f>
+        <v>235000</v>
       </c>
       <c r="F51" s="40">
         <f t="shared" ref="F51:I51" si="21">SUM(F45,F50)+F44</f>
+        <v>235000</v>
       </c>
       <c r="G51" s="40">
         <f t="shared" si="21"/>
+        <v>235000</v>
       </c>
       <c r="H51" s="40">
         <f t="shared" si="21"/>
+        <v>235000</v>
       </c>
       <c r="I51" s="40">
         <f t="shared" si="21"/>
+        <v>235000</v>
       </c>
       <c r="J51" s="40">
         <f>SUM(J45,J50)+J44</f>
+        <v>235000</v>
       </c>
       <c r="K51" s="11"/>
       <c r="L51" s="7"/>
@@ -7947,188 +8035,226 @@
       </c>
     </row>
     <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="144" t="s">
+      <c r="A54" s="138" t="s">
         <v>27</v>
       </c>
-      <c r="B54" s="145"/>
+      <c r="B54" s="139"/>
       <c r="C54" s="96"/>
       <c r="D54" s="28">
         <f>+D75*D76</f>
+        <v>0</v>
       </c>
       <c r="E54" s="28">
         <f t="shared" ref="E54:J54" si="22">+E75*E76</f>
+        <v>0</v>
       </c>
       <c r="F54" s="28">
         <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="G54" s="28">
         <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="H54" s="28">
         <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="I54" s="28">
         <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="J54" s="28">
         <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="K54" s="11"/>
       <c r="L54" s="7"/>
     </row>
     <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="144" t="s">
+      <c r="A55" s="138" t="s">
         <v>129</v>
       </c>
-      <c r="B55" s="145"/>
+      <c r="B55" s="139"/>
       <c r="C55" s="96"/>
       <c r="D55" s="27">
         <f>+SUM(D65:D72)</f>
+        <v>165000</v>
       </c>
       <c r="E55" s="27">
         <f>SUM(E65:E72)+E54</f>
+        <v>235000</v>
       </c>
       <c r="F55" s="27">
         <f t="shared" ref="F55:J55" si="23">SUM(F65:F72)+F54</f>
+        <v>235000</v>
       </c>
       <c r="G55" s="27">
         <f t="shared" si="23"/>
+        <v>235000</v>
       </c>
       <c r="H55" s="27">
         <f t="shared" si="23"/>
+        <v>235000</v>
       </c>
       <c r="I55" s="27">
         <f t="shared" si="23"/>
+        <v>235000</v>
       </c>
       <c r="J55" s="27">
         <f t="shared" si="23"/>
+        <v>235000</v>
       </c>
       <c r="K55" s="11"/>
       <c r="L55" s="7"/>
     </row>
     <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="144" t="s">
+      <c r="A56" s="138" t="s">
         <v>17</v>
       </c>
-      <c r="B56" s="145"/>
+      <c r="B56" s="139"/>
       <c r="C56" s="96"/>
       <c r="D56" s="39" t="s">
         <v>22</v>
       </c>
       <c r="E56" s="28">
         <f t="shared" ref="E56:J56" si="24">SUM(E65:E67)/(E28-D28)</f>
+        <v>175.53533596527117</v>
       </c>
       <c r="F56" s="28">
         <f t="shared" si="24"/>
+        <v>175.53533596527117</v>
       </c>
       <c r="G56" s="28">
         <f t="shared" si="24"/>
+        <v>174.46585487347713</v>
       </c>
       <c r="H56" s="28">
         <f t="shared" si="24"/>
+        <v>173.39882621734606</v>
       </c>
       <c r="I56" s="28">
         <f t="shared" si="24"/>
+        <v>172.33429421023968</v>
       </c>
       <c r="J56" s="28">
         <f t="shared" si="24"/>
+        <v>171.27230261226092</v>
       </c>
       <c r="K56" s="11"/>
       <c r="L56" s="7"/>
     </row>
     <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="144" t="s">
+      <c r="A57" s="138" t="s">
         <v>18</v>
       </c>
-      <c r="B57" s="145"/>
+      <c r="B57" s="139"/>
       <c r="C57" s="96"/>
       <c r="D57" s="39" t="s">
         <v>22</v>
       </c>
       <c r="E57" s="28">
         <f>+E61/E35</f>
+        <v>503.66911772527141</v>
       </c>
       <c r="F57" s="28">
         <f t="shared" ref="F57:J57" si="25">+F61/F35</f>
+        <v>432.58610396998546</v>
       </c>
       <c r="G57" s="28">
         <f t="shared" si="25"/>
+        <v>378.88128094152762</v>
       </c>
       <c r="H57" s="28">
         <f t="shared" si="25"/>
+        <v>394.20120094475413</v>
       </c>
       <c r="I57" s="28">
         <f t="shared" si="25"/>
+        <v>357.88734097803393</v>
       </c>
       <c r="J57" s="28">
         <f t="shared" si="25"/>
+        <v>328.01233513460647</v>
       </c>
       <c r="K57" s="11"/>
       <c r="L57" s="7"/>
     </row>
     <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="144" t="s">
+      <c r="A58" s="138" t="s">
         <v>20</v>
       </c>
-      <c r="B58" s="145"/>
+      <c r="B58" s="139"/>
       <c r="C58" s="96"/>
       <c r="D58" s="39" t="s">
         <v>22</v>
       </c>
       <c r="E58" s="32">
         <f t="shared" ref="E58:J58" si="26">+IFERROR(E36/E35,0)</f>
+        <v>8.5730913655365348E-3</v>
       </c>
       <c r="F58" s="32">
         <f t="shared" si="26"/>
+        <v>1.1044751590723033E-2</v>
       </c>
       <c r="G58" s="32">
         <f t="shared" si="26"/>
+        <v>9.6735646197836835E-3</v>
       </c>
       <c r="H58" s="32">
         <f t="shared" si="26"/>
+        <v>1.3419615351310778E-2</v>
       </c>
       <c r="I58" s="32">
         <f t="shared" si="26"/>
+        <v>1.3706323697031087E-2</v>
       </c>
       <c r="J58" s="32">
         <f t="shared" si="26"/>
+        <v>1.5353768878641153E-2</v>
       </c>
       <c r="K58" s="11"/>
       <c r="L58" s="7"/>
     </row>
     <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="152" t="s">
+      <c r="A59" s="140" t="s">
         <v>19</v>
       </c>
-      <c r="B59" s="153"/>
+      <c r="B59" s="141"/>
       <c r="C59" s="97"/>
       <c r="D59" s="28"/>
       <c r="E59" s="28">
         <f t="shared" ref="E59:J59" si="27">+IFERROR(E55/E36,0)</f>
+        <v>58750</v>
       </c>
       <c r="F59" s="28">
         <f t="shared" si="27"/>
+        <v>39166.666666666664</v>
       </c>
       <c r="G59" s="28">
         <f t="shared" si="27"/>
+        <v>39166.666666666664</v>
       </c>
       <c r="H59" s="28">
         <f t="shared" si="27"/>
+        <v>29375</v>
       </c>
       <c r="I59" s="28">
         <f t="shared" si="27"/>
+        <v>26111.111111111109</v>
       </c>
       <c r="J59" s="28">
         <f t="shared" si="27"/>
+        <v>21363.636363636364</v>
       </c>
       <c r="K59" s="11"/>
       <c r="L59" s="7"/>
     </row>
     <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="152" t="s">
+      <c r="A60" s="140" t="s">
         <v>116</v>
       </c>
-      <c r="B60" s="153"/>
+      <c r="B60" s="141"/>
       <c r="C60" s="97"/>
       <c r="D60" s="28"/>
       <c r="E60" s="28"/>
@@ -8141,31 +8267,38 @@
       <c r="L60" s="7"/>
     </row>
     <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="154" t="s">
+      <c r="A61" s="136" t="s">
         <v>70</v>
       </c>
-      <c r="B61" s="155"/>
+      <c r="B61" s="137"/>
       <c r="C61" s="98"/>
       <c r="D61" s="40">
         <f>+D55</f>
+        <v>165000</v>
       </c>
       <c r="E61" s="40">
         <f>+SUM(E65:E72)+E54</f>
+        <v>235000</v>
       </c>
       <c r="F61" s="40">
         <f t="shared" ref="F61:J61" si="28">+SUM(F65:F72)+F54</f>
+        <v>235000</v>
       </c>
       <c r="G61" s="40">
         <f t="shared" si="28"/>
+        <v>235000</v>
       </c>
       <c r="H61" s="40">
         <f t="shared" si="28"/>
+        <v>235000</v>
       </c>
       <c r="I61" s="40">
         <f t="shared" si="28"/>
+        <v>235000</v>
       </c>
       <c r="J61" s="40">
         <f t="shared" si="28"/>
+        <v>235000</v>
       </c>
       <c r="K61" s="11"/>
       <c r="L61" s="7"/>
@@ -8211,7 +8344,7 @@
         <v>0</v>
       </c>
       <c r="N65" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -8246,12 +8379,12 @@
         <v>30000</v>
       </c>
       <c r="N66" s="69" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C67" s="90">
         <v>0</v>
@@ -8277,10 +8410,8 @@
       <c r="J67" s="28">
         <v>0</v>
       </c>
-      <c r="N67" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サンクスLINE誘導：入れない（オプション：初期15万・月3万〜）</t>
-        </is>
+      <c r="N67" s="69" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -8296,24 +8427,30 @@
       </c>
       <c r="E68" s="28">
         <f t="shared" ref="E68:J68" si="29">IF(E34&lt;5000,5000,15000)</f>
+        <v>5000</v>
       </c>
       <c r="F68" s="28">
         <f t="shared" si="29"/>
+        <v>5000</v>
       </c>
       <c r="G68" s="28">
         <f t="shared" si="29"/>
+        <v>5000</v>
       </c>
       <c r="H68" s="28">
         <f t="shared" si="29"/>
+        <v>5000</v>
       </c>
       <c r="I68" s="28">
         <f t="shared" si="29"/>
+        <v>5000</v>
       </c>
       <c r="J68" s="28">
         <f t="shared" si="29"/>
+        <v>5000</v>
       </c>
       <c r="N68" s="69" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="O68" s="17" t="s">
         <v>128</v>
@@ -8325,13 +8462,13 @@
     <row r="69" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="15"/>
       <c r="B69" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C69" s="90">
         <v>0</v>
       </c>
       <c r="D69" s="51">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="E69" s="28">
         <v>200000</v>
@@ -8352,7 +8489,7 @@
         <v>200000</v>
       </c>
       <c r="N69" s="69" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="O69" s="5" t="s">
         <v>52</v>
@@ -8464,24 +8601,31 @@
       </c>
       <c r="D73" s="114">
         <f>SUM(D65:D72)</f>
+        <v>165000</v>
       </c>
       <c r="E73" s="114">
         <f t="shared" ref="E73:J73" si="30">SUM(E65:E72)+E54</f>
+        <v>235000</v>
       </c>
       <c r="F73" s="114">
         <f t="shared" si="30"/>
+        <v>235000</v>
       </c>
       <c r="G73" s="114">
         <f t="shared" si="30"/>
+        <v>235000</v>
       </c>
       <c r="H73" s="114">
         <f t="shared" si="30"/>
+        <v>235000</v>
       </c>
       <c r="I73" s="114">
         <f t="shared" si="30"/>
+        <v>235000</v>
       </c>
       <c r="J73" s="114">
         <f t="shared" si="30"/>
+        <v>235000</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -8502,24 +8646,31 @@
       </c>
       <c r="D75" s="41">
         <f t="shared" ref="D75:J75" si="31">+IF(D34&lt;30001,0,D34-30000)</f>
+        <v>0</v>
       </c>
       <c r="E75" s="41">
         <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="F75" s="41">
         <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="G75" s="41">
         <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="H75" s="41">
         <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="I75" s="41">
         <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="J75" s="41">
         <f t="shared" si="31"/>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -8528,28 +8679,58 @@
       </c>
       <c r="D76" s="5">
         <f t="shared" ref="D76:J76" si="32">+IF(D75&lt;=$U$18,$Z$18,IF(D75&lt;=$U$19,$Z$19,IF(D75&lt;=$U$20,$Z$20,IF(D75&lt;=$U$21,$Z$21,IF(D75&lt;=$U$22,$Z$22,IF(D75&lt;=$U$23,$Z$23,IF(D75&lt;=$U$24,$Z$24,IF(D75&lt;=$U$25,$Z$25,IF(D75&lt;=$U$26,$Z$26,IF(D75&lt;=$U$27,$Z$27,IF(D75&lt;=$U$28,$Z$28,IF(D75&lt;=$U$29,$Z$29,IF(D75&lt;=$U$30,$Z$30,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="E76" s="5">
         <f t="shared" si="32"/>
+        <v>3</v>
       </c>
       <c r="F76" s="5">
         <f t="shared" si="32"/>
+        <v>3</v>
       </c>
       <c r="G76" s="5">
         <f t="shared" si="32"/>
+        <v>3</v>
       </c>
       <c r="H76" s="5">
         <f t="shared" si="32"/>
+        <v>3</v>
       </c>
       <c r="I76" s="5">
         <f t="shared" si="32"/>
+        <v>3</v>
       </c>
       <c r="J76" s="5">
         <f t="shared" si="32"/>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A49:B49"/>
@@ -8562,36 +8743,13 @@
     <mergeCell ref="A58:B58"/>
     <mergeCell ref="A59:B59"/>
     <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3D322F6-2076-57E9-875D-3D967EDA726D}">
   <dimension ref="A1:Y35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.5" x14ac:dyDescent="0.55000000000000004"/>
@@ -8635,14 +8793,17 @@
         <v>137</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="86">
-        <f>+'B_サンクス無'!D24</f>
+      <c r="C4" s="86" t="str">
+        <f>+B_サンクス無!D24</f>
+        <v>--</v>
       </c>
       <c r="D4" s="28">
-        <f>+'B_サンクス無'!G51</f>
+        <f>+B_サンクス無!G51</f>
+        <v>235000</v>
       </c>
       <c r="E4" s="28">
-        <f>+'B_サンクス無'!J51</f>
+        <f>+B_サンクス無!J51</f>
+        <v>235000</v>
       </c>
       <c r="F4" s="28"/>
     </row>
@@ -8651,14 +8812,17 @@
         <v>138</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="86">
-        <f>+'B_サンクス無'!D25</f>
+      <c r="C5" s="86" t="str">
+        <f>+B_サンクス無!D25</f>
+        <v>--</v>
       </c>
       <c r="D5" s="28">
-        <f>+'B_サンクス無'!G61</f>
+        <f>+B_サンクス無!G61</f>
+        <v>235000</v>
       </c>
       <c r="E5" s="28">
-        <f>+'B_サンクス無'!J61</f>
+        <f>+B_サンクス無!J61</f>
+        <v>235000</v>
       </c>
       <c r="F5" s="27"/>
     </row>
@@ -8668,13 +8832,16 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="117">
-        <f>+'B_サンクス無'!D28</f>
+        <f>+B_サンクス無!D28</f>
+        <v>417</v>
       </c>
       <c r="D6" s="87">
-        <f>+'B_サンクス無'!G28</f>
+        <f>+B_サンクス無!G28</f>
+        <v>930.76493759999994</v>
       </c>
       <c r="E6" s="87">
-        <f>+'B_サンクス無'!J28</f>
+        <f>+B_サンクス無!J28</f>
+        <v>1453.0164266364577</v>
       </c>
       <c r="F6" s="10"/>
     </row>
@@ -8684,13 +8851,16 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="88">
-        <f>+'B_サンクス無'!D27</f>
+        <f>+B_サンクス無!D27</f>
+        <v>0.28000000000000003</v>
       </c>
       <c r="D7" s="89">
-        <f>+'B_サンクス無'!G27</f>
+        <f>+B_サンクス無!G27</f>
+        <v>0.29199999999999998</v>
       </c>
       <c r="E7" s="89">
-        <f>+'B_サンクス無'!J27</f>
+        <f>+B_サンクス無!J27</f>
+        <v>0.31</v>
       </c>
       <c r="F7" s="89"/>
     </row>
@@ -8700,13 +8870,16 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="117">
-        <f>+'B_サンクス無'!D29</f>
+        <f>+B_サンクス無!D29</f>
+        <v>300.24</v>
       </c>
       <c r="D8" s="10">
-        <f>+'B_サンクス無'!G29</f>
+        <f>+B_サンクス無!G29</f>
+        <v>658.98157582079989</v>
       </c>
       <c r="E8" s="10">
-        <f>+'B_サンクス無'!J29</f>
+        <f>+B_サンクス無!J29</f>
+        <v>1002.5813343791557</v>
       </c>
       <c r="F8" s="10"/>
     </row>
@@ -8724,13 +8897,16 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="117">
-        <f>+'B_サンクス無'!D34</f>
+        <f>+B_サンクス無!D34</f>
+        <v>0</v>
       </c>
       <c r="D10" s="10">
-        <f>+'B_サンクス無'!G34</f>
+        <f>+B_サンクス無!G34</f>
+        <v>2968.5081306265597</v>
       </c>
       <c r="E10" s="10">
-        <f>+'B_サンクス無'!J34</f>
+        <f>+B_サンクス無!J34</f>
+        <v>3442.4065658441268</v>
       </c>
       <c r="F10" s="10"/>
     </row>
@@ -8740,13 +8916,16 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="117">
-        <f>+'B_サンクス無'!D35</f>
+        <f>+B_サンクス無!D35</f>
+        <v>0</v>
       </c>
       <c r="D11" s="10">
-        <f>+'B_サンクス無'!G35</f>
+        <f>+B_サンクス無!G35</f>
+        <v>620.24705843482229</v>
       </c>
       <c r="E11" s="10">
-        <f>+'B_サンクス無'!J35</f>
+        <f>+B_サンクス無!J35</f>
+        <v>716.43647152343533</v>
       </c>
       <c r="F11" s="10"/>
     </row>
@@ -8757,12 +8936,15 @@
       <c r="B12" s="7"/>
       <c r="C12" s="28">
         <f>+IFERROR(C5/C11,0)</f>
+        <v>0</v>
       </c>
       <c r="D12" s="28">
         <f>+D4/D11</f>
+        <v>378.88128094152762</v>
       </c>
       <c r="E12" s="28">
         <f t="shared" ref="E12" si="0">+E4/E11</f>
+        <v>328.01233513460647</v>
       </c>
       <c r="F12" s="28"/>
     </row>
@@ -8773,12 +8955,15 @@
       <c r="B13" s="7"/>
       <c r="C13" s="28">
         <f>+IFERROR(C6/C12,0)</f>
+        <v>0</v>
       </c>
       <c r="D13" s="28">
         <f>+D5/D11</f>
+        <v>378.88128094152762</v>
       </c>
       <c r="E13" s="28">
         <f t="shared" ref="E13" si="1">+E5/E11</f>
+        <v>328.01233513460647</v>
       </c>
       <c r="F13" s="28"/>
     </row>
@@ -8795,17 +8980,20 @@
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="85" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="87">
-        <f>+'B_サンクス無'!D16</f>
+        <f>+B_サンクス無!D16</f>
+        <v>35</v>
       </c>
       <c r="D15" s="87">
-        <f>+'B_サンクス無'!G16</f>
+        <f>+B_サンクス無!G16</f>
+        <v>35</v>
       </c>
       <c r="E15" s="87">
-        <f>+'B_サンクス無'!J16</f>
+        <f>+B_サンクス無!J16</f>
+        <v>35</v>
       </c>
       <c r="F15" s="87"/>
       <c r="R15" s="5" t="s">
@@ -8814,17 +9002,20 @@
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="85" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="87">
         <f>+C17</f>
+        <v>0</v>
       </c>
       <c r="D16" s="87">
         <f>+D17</f>
+        <v>6</v>
       </c>
       <c r="E16" s="87">
         <f>+E17</f>
+        <v>11</v>
       </c>
       <c r="F16" s="87"/>
       <c r="R16" s="5" t="s">
@@ -8839,17 +9030,20 @@
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="85" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="87">
-        <f>+'B_サンクス無'!D36</f>
+        <f>+B_サンクス無!D36</f>
+        <v>0</v>
       </c>
       <c r="D17" s="87">
-        <f>+'B_サンクス無'!G36</f>
+        <f>+B_サンクス無!G36</f>
+        <v>6</v>
       </c>
       <c r="E17" s="87">
-        <f>+'B_サンクス無'!J36</f>
+        <f>+B_サンクス無!J36</f>
+        <v>11</v>
       </c>
       <c r="F17" s="10"/>
       <c r="R17" s="5">
@@ -8876,17 +9070,20 @@
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="85" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="87">
-        <f>+'B_サンクス無'!D37</f>
+        <f>+B_サンクス無!D37</f>
+        <v>0</v>
       </c>
       <c r="D18" s="87">
-        <f>+'B_サンクス無'!G37</f>
+        <f>+B_サンクス無!G37</f>
+        <v>4</v>
       </c>
       <c r="E18" s="87">
-        <f>+'B_サンクス無'!J37</f>
+        <f>+B_サンクス無!J37</f>
+        <v>8</v>
       </c>
       <c r="F18" s="10"/>
       <c r="R18" s="34">
@@ -8906,6 +9103,7 @@
       </c>
       <c r="X18" s="34">
         <f>+T18*2.5</f>
+        <v>37500000</v>
       </c>
       <c r="Y18" s="35">
         <v>2.5</v>
@@ -8917,13 +9115,16 @@
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="87">
-        <f>+'B_サンクス無'!D38</f>
+        <f>+B_サンクス無!D38</f>
+        <v>0</v>
       </c>
       <c r="D19" s="87">
-        <f>+'B_サンクス無'!G38</f>
+        <f>+B_サンクス無!G38</f>
+        <v>0</v>
       </c>
       <c r="E19" s="87">
-        <f>+'B_サンクス無'!J38</f>
+        <f>+B_サンクス無!J38</f>
+        <v>0</v>
       </c>
       <c r="F19" s="10"/>
       <c r="R19" s="34"/>
@@ -8938,13 +9139,16 @@
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="87">
-        <f>+'B_サンクス無'!D39</f>
+        <f>+B_サンクス無!D39</f>
+        <v>0</v>
       </c>
       <c r="D20" s="87">
-        <f>+'B_サンクス無'!G39</f>
+        <f>+B_サンクス無!G39</f>
+        <v>0</v>
       </c>
       <c r="E20" s="87">
-        <f>+'B_サンクス無'!J39</f>
+        <f>+B_サンクス無!J39</f>
+        <v>0</v>
       </c>
       <c r="F20" s="10"/>
       <c r="R20" s="34"/>
@@ -8971,14 +9175,17 @@
         <v>139</v>
       </c>
       <c r="B22" s="7"/>
-      <c r="C22" s="90">
+      <c r="C22" s="90" t="str">
         <f>+IFERROR(C4/C16,"--")</f>
+        <v>--</v>
       </c>
       <c r="D22" s="90">
         <f t="shared" ref="D22:E22" si="2">+IFERROR(D4/D16,"--")</f>
+        <v>39166.666666666664</v>
       </c>
       <c r="E22" s="90">
         <f t="shared" si="2"/>
+        <v>21363.636363636364</v>
       </c>
       <c r="F22" s="90"/>
       <c r="R22" s="34"/>
@@ -8992,14 +9199,17 @@
         <v>140</v>
       </c>
       <c r="B23" s="7"/>
-      <c r="C23" s="90">
+      <c r="C23" s="90" t="str">
         <f>+IFERROR(C5/C16,"--")</f>
+        <v>--</v>
       </c>
       <c r="D23" s="90">
         <f t="shared" ref="D23" si="3">+IFERROR(D5/D16,"--")</f>
+        <v>39166.666666666664</v>
       </c>
       <c r="E23" s="90">
         <f t="shared" ref="E23" si="4">+IFERROR(E5/E16,"--")</f>
+        <v>21363.636363636364</v>
       </c>
       <c r="F23" s="90"/>
       <c r="R23" s="34"/>
@@ -9027,13 +9237,16 @@
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="10">
-        <f>+'B_サンクス無'!E68+C29*C30</f>
+        <f>+B_サンクス無!E68+C29*C30</f>
+        <v>5000</v>
       </c>
       <c r="D25" s="10">
-        <f>+'B_サンクス無'!G68+D29*D30</f>
+        <f>+B_サンクス無!G68+D29*D30</f>
+        <v>5000</v>
       </c>
       <c r="E25" s="10">
-        <f>+'B_サンクス無'!J68+E29*E30</f>
+        <f>+B_サンクス無!J68+E29*E30</f>
+        <v>5000</v>
       </c>
       <c r="F25" s="10"/>
       <c r="R25" s="34"/>
@@ -9069,12 +9282,15 @@
       </c>
       <c r="C29" s="5">
         <f>+IF(C10&lt;=30000,0,C10-30000)</f>
+        <v>0</v>
       </c>
       <c r="D29" s="91">
         <f>+IF(D10&lt;=30000,0,D10-30000)</f>
+        <v>0</v>
       </c>
       <c r="E29" s="91">
         <f>+IF(E10&lt;=30000,0,E10-30000)</f>
+        <v>0</v>
       </c>
       <c r="F29" s="91"/>
       <c r="R29" s="34"/>
@@ -9089,12 +9305,15 @@
       </c>
       <c r="C30" s="5">
         <f>+IF(C29&lt;=$T$17,$Y$17,IF(C29&lt;=$T$18,$Y$18,IF(C29&lt;=$T$19,$Y$19,IF(C29&lt;=$T$20,$Y$20,IF(C29&lt;=$T$21,$Y$21,IF(C29&lt;=$T$22,$Y$22,IF(C29&lt;=$T$23,$Y$23,IF(C29&lt;=$T$24,$Y$24,IF(C29&lt;=$T$25,$Y$25,IF(C29&lt;=$T$26,$Y$26,IF(C29&lt;=$T$27,$Y$27,IF(C29&lt;=$T$28,$Y$28,IF(C29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="D30" s="5">
         <f>+IF(D29&lt;=$T$17,$Y$17,IF(D29&lt;=$T$18,$Y$18,IF(D29&lt;=$T$19,$Y$19,IF(D29&lt;=$T$20,$Y$20,IF(D29&lt;=$T$21,$Y$21,IF(D29&lt;=$T$22,$Y$22,IF(D29&lt;=$T$23,$Y$23,IF(D29&lt;=$T$24,$Y$24,IF(D29&lt;=$T$25,$Y$25,IF(D29&lt;=$T$26,$Y$26,IF(D29&lt;=$T$27,$Y$27,IF(D29&lt;=$T$28,$Y$28,IF(D29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="E30" s="5">
         <f>+IF(E29&lt;=$T$17,$Y$17,IF(E29&lt;=$T$18,$Y$18,IF(E29&lt;=$T$19,$Y$19,IF(E29&lt;=$T$20,$Y$20,IF(E29&lt;=$T$21,$Y$21,IF(E29&lt;=$T$22,$Y$22,IF(E29&lt;=$T$23,$Y$23,IF(E29&lt;=$T$24,$Y$24,IF(E29&lt;=$T$25,$Y$25,IF(E29&lt;=$T$26,$Y$26,IF(E29&lt;=$T$27,$Y$27,IF(E29&lt;=$T$28,$Y$28,IF(E29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="R30" s="34"/>
       <c r="T30" s="34"/>
@@ -9125,6 +9344,399 @@
       <c r="F35" s="94" t="s">
         <v>136</v>
       </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1CA14B7-1E76-4B86-9C33-BD8F21953694}">
+  <dimension ref="A2:J42"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="14.25" customWidth="1"/>
+    <col min="5" max="5" width="14.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="59" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="54" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="60">
+        <v>8.5000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="60">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="E7">
+        <f>+E4*B5*B6</f>
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="54" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="60">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="60">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="E12">
+        <f>+E9*B10*B11</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="54" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="60">
+        <v>0.9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="60">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="E17">
+        <f>+E14*B15*B16</f>
+        <v>315</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" s="60">
+        <v>0.7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="60">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="E22">
+        <f>+E19*B20*B21</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="59" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="59"/>
+      <c r="C23" s="59" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="59"/>
+      <c r="I23" s="67" t="s">
+        <v>102</v>
+      </c>
+      <c r="J23" s="68"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="54" t="s">
+        <v>84</v>
+      </c>
+      <c r="I24" s="66">
+        <v>1</v>
+      </c>
+      <c r="J24" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="61">
+        <v>0.8</v>
+      </c>
+      <c r="I25" s="66">
+        <v>2</v>
+      </c>
+      <c r="J25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="61">
+        <v>0.06</v>
+      </c>
+      <c r="I26" s="66">
+        <v>3</v>
+      </c>
+      <c r="J26" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="61">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="I27" s="66">
+        <v>4</v>
+      </c>
+      <c r="J27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="I29" s="67" t="s">
+        <v>107</v>
+      </c>
+      <c r="J29" s="68"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="61">
+        <v>0.75</v>
+      </c>
+      <c r="I30" s="66">
+        <v>1</v>
+      </c>
+      <c r="J30" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="61">
+        <v>0.08</v>
+      </c>
+      <c r="I31" s="66">
+        <v>2</v>
+      </c>
+      <c r="J31" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="61">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="I32" s="66">
+        <v>3</v>
+      </c>
+      <c r="J32" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="I33" s="66">
+        <v>4</v>
+      </c>
+      <c r="J33" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="54" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="62" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="61">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="61">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="E39" s="54" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="62">
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
+        <v>41</v>
+      </c>
+      <c r="F40" s="62" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="61">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="E41" t="s">
+        <v>100</v>
+      </c>
+      <c r="F41" s="61">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>85</v>
+      </c>
+      <c r="B42" s="61">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="F42" s="61"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -9133,6 +9745,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="79deb97c-193b-473b-ac92-dc976e68b6a4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100C357D3FFD3874644B9B63D306D91E343" ma:contentTypeVersion="5" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="bfcf90751a1be541a10eb2cf2bfdf12b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="79deb97c-193b-473b-ac92-dc976e68b6a4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9df8bde209fb52400f7491d2ba74e6ee" ns3:_="">
     <xsd:import namespace="79deb97c-193b-473b-ac92-dc976e68b6a4"/>
@@ -9282,24 +9911,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{010C7DA8-EA1E-4EA4-BD5C-CCDDE9E9CCA3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="79deb97c-193b-473b-ac92-dc976e68b6a4"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="79deb97c-193b-473b-ac92-dc976e68b6a4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CA9CD83-13A7-4B09-B9AB-AAF5EBC76B43}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2519B170-E350-4E75-B7A7-F72CE5062C7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9315,28 +9951,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CA9CD83-13A7-4B09-B9AB-AAF5EBC76B43}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{010C7DA8-EA1E-4EA4-BD5C-CCDDE9E9CCA3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="79deb97c-193b-473b-ac92-dc976e68b6a4"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>